--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F84698-20C7-4B61-9F13-CA7C9B1BB28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24DC26B-C73D-4A35-9678-14131689761D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="661" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -1144,10 +1144,10 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J3">
         <v>1</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24DC26B-C73D-4A35-9678-14131689761D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4A94B1-AB45-4DEB-8E59-0DCA0A66610F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="746" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -2023,7 +2023,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3">
         <v>5</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB996A43-889C-4BEC-89CC-A8BFFC20D8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E092AE-A918-4B43-9500-BF35C1BF4E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="102">
   <si>
     <t>Id</t>
   </si>
@@ -363,19 +363,35 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ターン終了コマンド操作</t>
+    <t>チュートリアル開始</t>
+    <rPh sb="7" eb="9">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ターン終了コマンド操作有効</t>
     <rPh sb="3" eb="5">
       <t>シュウリョウ</t>
     </rPh>
     <rPh sb="9" eb="11">
       <t>ソウサ</t>
     </rPh>
+    <rPh sb="11" eb="13">
+      <t>ユウコウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>チュートリアル開始</t>
-    <rPh sb="7" eb="9">
-      <t>カイシ</t>
+    <t>ターン終了コマンド操作無効</t>
+    <rPh sb="3" eb="5">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ムコウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -956,7 +972,7 @@
         <v>8</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -991,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="22.08984375" customWidth="1"/>
@@ -1035,7 +1051,7 @@
         <v>1010</v>
       </c>
       <c r="E2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1058,9 +1074,49 @@
         <v>1010</v>
       </c>
       <c r="G3">
+        <v>400</v>
+      </c>
+      <c r="H3" t="b">
         <v>1</v>
       </c>
-      <c r="H3" t="b">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1010</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1010</v>
+      </c>
+      <c r="E4">
+        <v>1011</v>
+      </c>
+      <c r="G4">
+        <v>500</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1010</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1010</v>
+      </c>
+      <c r="E5">
+        <v>1010</v>
+      </c>
+      <c r="G5">
+        <v>600</v>
+      </c>
+      <c r="H5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1072,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -1511,10 +1567,10 @@
         <v>1010</v>
       </c>
       <c r="C10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10">
         <v>1000</v>
@@ -1596,6 +1652,246 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10030</v>
+      </c>
+      <c r="B12">
+        <v>1010</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+      <c r="F12" t="str">
+        <f>INDEX(Define!L:L,MATCH(E12,Define!K:K))</f>
+        <v>Basement</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>100</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>10040</v>
+      </c>
+      <c r="B13">
+        <v>1010</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="str">
+        <f>INDEX(Define!L:L,MATCH(E13,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>10050</v>
+      </c>
+      <c r="B14">
+        <v>1010</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="str">
+        <f>INDEX(Define!L:L,MATCH(E14,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>100</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>10060</v>
+      </c>
+      <c r="B15">
+        <v>1010</v>
+      </c>
+      <c r="C15">
+        <v>9</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="str">
+        <f>INDEX(Define!L:L,MATCH(E15,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>100</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>10070</v>
+      </c>
+      <c r="B16">
+        <v>1010</v>
+      </c>
+      <c r="C16">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" t="str">
+        <f>INDEX(Define!L:L,MATCH(E16,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>100</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2238,7 +2534,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
@@ -2338,7 +2634,7 @@
         <v>1010</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -2628,7 +2924,15 @@
         <v>1010</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D28">
+        <v>1011</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E092AE-A918-4B43-9500-BF35C1BF4E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB4EA97-505E-4868-854F-9C6B3F6D3DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="103">
   <si>
     <t>Id</t>
   </si>
@@ -49,9 +49,6 @@
     <t>StageNo</t>
   </si>
   <si>
-    <t>AchieveTextId</t>
-  </si>
-  <si>
     <t>Selectable</t>
   </si>
   <si>
@@ -71,9 +68,6 @@
   </si>
   <si>
     <t>BackGround</t>
-  </si>
-  <si>
-    <t>3,5</t>
   </si>
   <si>
     <t>-</t>
@@ -393,6 +387,18 @@
     <rPh sb="11" eb="13">
       <t>ムコウ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>AchieveTextId</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>AchieveType</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>EnemyBasementId</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -743,15 +749,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="8.453125" customWidth="1"/>
-    <col min="5" max="5" width="10.36328125" customWidth="1"/>
-    <col min="20" max="20" width="32" customWidth="1"/>
+    <col min="5" max="6" width="8.453125" customWidth="1"/>
+    <col min="7" max="7" width="10.36328125" customWidth="1"/>
+    <col min="22" max="22" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -761,59 +767,65 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>7</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>8</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -824,35 +836,35 @@
         <v>0</v>
       </c>
       <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>10001</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2" t="s">
-        <v>11</v>
+      <c r="G2">
+        <v>0</v>
       </c>
       <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <v>6</v>
       </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
       <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
         <v>6</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
       <c r="N2">
         <v>0</v>
       </c>
@@ -860,22 +872,28 @@
         <v>0</v>
       </c>
       <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
         <v>30</v>
       </c>
-      <c r="Q2">
+      <c r="S2">
         <v>1010</v>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>2010</v>
       </c>
-      <c r="S2">
+      <c r="U2">
         <v>100</v>
       </c>
-      <c r="T2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="V2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>10</v>
       </c>
@@ -886,58 +904,64 @@
         <v>1</v>
       </c>
       <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>10001</v>
       </c>
-      <c r="E3">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
       <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>30</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>1</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>29</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>20</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>19</v>
       </c>
       <c r="N3">
         <v>1</v>
       </c>
       <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
         <v>5</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>30</v>
       </c>
-      <c r="Q3">
+      <c r="S3">
         <v>1010</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>2010</v>
       </c>
-      <c r="S3">
+      <c r="U3">
         <v>100</v>
       </c>
-      <c r="T3" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="V3" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1010</v>
       </c>
@@ -948,55 +972,61 @@
         <v>101</v>
       </c>
       <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>10001</v>
       </c>
-      <c r="E4">
+      <c r="F4">
+        <v>10030</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
       <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>16</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>5</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>12</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>8</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>3</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>6</v>
       </c>
-      <c r="N4">
+      <c r="P4">
         <v>4</v>
       </c>
-      <c r="O4">
+      <c r="Q4">
         <v>4</v>
       </c>
-      <c r="P4">
+      <c r="R4">
         <v>30</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>1010</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>2010</v>
       </c>
-      <c r="S4">
+      <c r="U4">
         <v>100</v>
       </c>
-      <c r="T4" s="2" t="s">
-        <v>77</v>
+      <c r="V4" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1019,25 +1049,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
         <v>16</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -1133,46 +1163,46 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
@@ -1220,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -1268,7 +1298,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
@@ -1316,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
@@ -1364,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -1412,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -1460,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -1508,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -1556,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -1604,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -1652,7 +1682,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -1700,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -1748,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -1796,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -1844,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
@@ -1892,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1911,10 +1941,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -1999,25 +2029,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>21</v>
-      </c>
-      <c r="F1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -2396,25 +2426,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>32</v>
-      </c>
-      <c r="G1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -2463,10 +2493,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -2474,10 +2504,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -2485,10 +2515,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -2497,10 +2527,10 @@
         <v>1010</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D4" s="1"/>
     </row>
@@ -2539,16 +2569,16 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
-        <v>16</v>
-      </c>
       <c r="I1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -2556,25 +2586,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -2582,25 +2612,25 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -2608,25 +2638,25 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -2634,25 +2664,25 @@
         <v>1010</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -2660,19 +2690,19 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -2680,19 +2710,19 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -2700,19 +2730,19 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -2720,19 +2750,19 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -2740,19 +2770,19 @@
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -2760,19 +2790,19 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -2780,19 +2810,19 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K12">
         <v>99</v>
       </c>
       <c r="L12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -2800,19 +2830,19 @@
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K13">
         <v>1000</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
@@ -2820,7 +2850,7 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -2828,7 +2858,7 @@
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
@@ -2836,7 +2866,7 @@
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.2">
@@ -2844,7 +2874,7 @@
         <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.2">
@@ -2852,7 +2882,7 @@
         <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.2">
@@ -2860,7 +2890,7 @@
         <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="4:5" x14ac:dyDescent="0.2">
@@ -2868,7 +2898,7 @@
         <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="4:5" x14ac:dyDescent="0.2">
@@ -2876,7 +2906,7 @@
         <v>51</v>
       </c>
       <c r="E21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="4:5" x14ac:dyDescent="0.2">
@@ -2884,7 +2914,7 @@
         <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="4:5" x14ac:dyDescent="0.2">
@@ -2892,7 +2922,7 @@
         <v>62</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="4:5" x14ac:dyDescent="0.2">
@@ -2900,7 +2930,7 @@
         <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="4:5" x14ac:dyDescent="0.2">
@@ -2908,7 +2938,7 @@
         <v>110</v>
       </c>
       <c r="E25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="4:5" x14ac:dyDescent="0.2">
@@ -2916,7 +2946,7 @@
         <v>201</v>
       </c>
       <c r="E26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="4:5" x14ac:dyDescent="0.2">
@@ -2924,7 +2954,7 @@
         <v>1010</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="4:5" x14ac:dyDescent="0.2">
@@ -2932,7 +2962,7 @@
         <v>1011</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB4EA97-505E-4868-854F-9C6B3F6D3DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB5B736-DAB8-4836-8BE5-EA21197FA1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="104">
   <si>
     <t>Id</t>
   </si>
@@ -399,6 +399,19 @@
   </si>
   <si>
     <t>EnemyBasementId</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>有利なバトルの進め方</t>
+    <rPh sb="0" eb="2">
+      <t>ユウリ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カタ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -749,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="6" width="8.453125" customWidth="1"/>
@@ -1026,6 +1039,74 @@
         <v>100</v>
       </c>
       <c r="V4" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1020</v>
+      </c>
+      <c r="B5">
+        <v>1020</v>
+      </c>
+      <c r="C5">
+        <v>101</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>10001</v>
+      </c>
+      <c r="F5">
+        <v>10030</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>20</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <v>16</v>
+      </c>
+      <c r="M5">
+        <v>8</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>6</v>
+      </c>
+      <c r="P5">
+        <v>10</v>
+      </c>
+      <c r="Q5">
+        <v>4</v>
+      </c>
+      <c r="R5">
+        <v>30</v>
+      </c>
+      <c r="S5">
+        <v>1010</v>
+      </c>
+      <c r="T5">
+        <v>2010</v>
+      </c>
+      <c r="U5">
+        <v>100</v>
+      </c>
+      <c r="V5" s="2" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1158,7 +1239,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -1922,6 +2003,582 @@
         <v>0</v>
       </c>
       <c r="O16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>11000</v>
+      </c>
+      <c r="B17">
+        <v>1020</v>
+      </c>
+      <c r="C17">
+        <v>-1</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>70</v>
+      </c>
+      <c r="F17" t="str">
+        <f>INDEX(Define!L:L,MATCH(E17,Define!K:K))</f>
+        <v>SelectActor</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>100</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>1001</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>11010</v>
+      </c>
+      <c r="B18">
+        <v>1020</v>
+      </c>
+      <c r="C18">
+        <v>-1</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>70</v>
+      </c>
+      <c r="F18" t="str">
+        <f>INDEX(Define!L:L,MATCH(E18,Define!K:K))</f>
+        <v>SelectActor</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>1002</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>10020</v>
+      </c>
+      <c r="B19">
+        <v>1020</v>
+      </c>
+      <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19">
+        <v>20</v>
+      </c>
+      <c r="F19" t="str">
+        <f>INDEX(Define!L:L,MATCH(E19,Define!K:K))</f>
+        <v>Basement</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>100</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>10030</v>
+      </c>
+      <c r="B20">
+        <v>1020</v>
+      </c>
+      <c r="C20">
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20">
+        <v>20</v>
+      </c>
+      <c r="F20" t="str">
+        <f>INDEX(Define!L:L,MATCH(E20,Define!K:K))</f>
+        <v>Basement</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>100</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>10040</v>
+      </c>
+      <c r="B21">
+        <v>1020</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21" t="str">
+        <f>INDEX(Define!L:L,MATCH(E21,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>100</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>10050</v>
+      </c>
+      <c r="B22">
+        <v>1020</v>
+      </c>
+      <c r="C22">
+        <v>7</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" t="str">
+        <f>INDEX(Define!L:L,MATCH(E22,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>100</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>10060</v>
+      </c>
+      <c r="B23">
+        <v>1020</v>
+      </c>
+      <c r="C23">
+        <v>9</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23" t="str">
+        <f>INDEX(Define!L:L,MATCH(E23,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>100</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>10070</v>
+      </c>
+      <c r="B24">
+        <v>1020</v>
+      </c>
+      <c r="C24">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24" t="str">
+        <f>INDEX(Define!L:L,MATCH(E24,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>100</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>11020</v>
+      </c>
+      <c r="B25">
+        <v>1020</v>
+      </c>
+      <c r="C25">
+        <v>13</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" t="str">
+        <f>INDEX(Define!L:L,MATCH(E25,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>100</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>11030</v>
+      </c>
+      <c r="B26">
+        <v>1020</v>
+      </c>
+      <c r="C26">
+        <v>15</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26" t="str">
+        <f>INDEX(Define!L:L,MATCH(E26,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>100</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>11040</v>
+      </c>
+      <c r="B27">
+        <v>1020</v>
+      </c>
+      <c r="C27">
+        <v>14</v>
+      </c>
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27">
+        <v>20</v>
+      </c>
+      <c r="F27" t="str">
+        <f>INDEX(Define!L:L,MATCH(E27,Define!K:K))</f>
+        <v>Basement</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+      <c r="H27">
+        <v>100</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>11050</v>
+      </c>
+      <c r="B28">
+        <v>1020</v>
+      </c>
+      <c r="C28">
+        <v>14</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28">
+        <v>1000</v>
+      </c>
+      <c r="F28" t="str">
+        <f>INDEX(Define!L:L,MATCH(E28,Define!K:K))</f>
+        <v>Battler</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
+      <c r="H28">
+        <v>100</v>
+      </c>
+      <c r="I28">
+        <v>1011</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>1011</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2535,7 +3192,15 @@
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C5" s="1"/>
+      <c r="A5">
+        <v>1020</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB5B736-DAB8-4836-8BE5-EA21197FA1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2AC5D53-DD8E-466B-8407-D057755F4E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="104">
   <si>
     <t>Id</t>
   </si>
@@ -1239,7 +1239,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -2497,17 +2497,17 @@
         <v>14</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F27" t="str">
         <f>INDEX(Define!L:L,MATCH(E27,Define!K:K))</f>
-        <v>Basement</v>
+        <v>None</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>100</v>
@@ -2545,40 +2545,232 @@
         <v>14</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F28" t="str">
         <f>INDEX(Define!L:L,MATCH(E28,Define!K:K))</f>
-        <v>Battler</v>
+        <v>None</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>100</v>
       </c>
       <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>11060</v>
+      </c>
+      <c r="B29">
+        <v>1020</v>
+      </c>
+      <c r="C29">
+        <v>15</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29" t="str">
+        <f>INDEX(Define!L:L,MATCH(E29,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>100</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>11070</v>
+      </c>
+      <c r="B30">
+        <v>1020</v>
+      </c>
+      <c r="C30">
+        <v>15</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30" t="str">
+        <f>INDEX(Define!L:L,MATCH(E30,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>100</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>11080</v>
+      </c>
+      <c r="B31">
+        <v>1020</v>
+      </c>
+      <c r="C31">
+        <v>14</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>20</v>
+      </c>
+      <c r="F31" t="str">
+        <f>INDEX(Define!L:L,MATCH(E31,Define!K:K))</f>
+        <v>Basement</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+      <c r="H31">
+        <v>100</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>11090</v>
+      </c>
+      <c r="B32">
+        <v>1020</v>
+      </c>
+      <c r="C32">
+        <v>14</v>
+      </c>
+      <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="E32">
+        <v>1000</v>
+      </c>
+      <c r="F32" t="str">
+        <f>INDEX(Define!L:L,MATCH(E32,Define!K:K))</f>
+        <v>Battler</v>
+      </c>
+      <c r="G32">
+        <v>2</v>
+      </c>
+      <c r="H32">
+        <v>100</v>
+      </c>
+      <c r="I32">
         <v>1011</v>
       </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
         <v>1011</v>
       </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28" t="s">
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
         <v>24</v>
       </c>
     </row>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2AC5D53-DD8E-466B-8407-D057755F4E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA8DCE6-B3D2-40B3-8E10-E18EA57384CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="TextData" sheetId="5" r:id="rId7"/>
     <sheet name="Define" sheetId="6" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="106">
   <si>
     <t>Id</t>
   </si>
@@ -411,6 +411,22 @@
     </rPh>
     <rPh sb="9" eb="10">
       <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>NA_background image_3D like_894</t>
+  </si>
+  <si>
+    <t>敵拠点を制圧する</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>キョテン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セイアツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -852,7 +868,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>10001</v>
+        <v>10010</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -920,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>10001</v>
+        <v>10010</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -971,7 +987,7 @@
         <v>100</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
@@ -988,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>10001</v>
+        <v>10010</v>
       </c>
       <c r="F4">
         <v>10030</v>
@@ -1039,7 +1055,7 @@
         <v>100</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
@@ -1056,7 +1072,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>10001</v>
+        <v>10010</v>
       </c>
       <c r="F5">
         <v>10030</v>
@@ -3396,7 +3412,15 @@
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C6" s="1"/>
+      <c r="A6">
+        <v>10010</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA8DCE6-B3D2-40B3-8E10-E18EA57384CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F75DCD6-8C63-4A88-A517-47C84F762AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="108">
   <si>
     <t>Id</t>
   </si>
@@ -427,6 +427,17 @@
     </rPh>
     <rPh sb="4" eb="6">
       <t>セイアツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Alcana</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ユニットの強化</t>
+    <rPh sb="5" eb="7">
+      <t>キョウカ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -778,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="6" width="8.453125" customWidth="1"/>
@@ -1123,6 +1134,74 @@
         <v>100</v>
       </c>
       <c r="V5" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1030</v>
+      </c>
+      <c r="B6">
+        <v>1030</v>
+      </c>
+      <c r="C6">
+        <v>101</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>10010</v>
+      </c>
+      <c r="F6">
+        <v>10030</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>16</v>
+      </c>
+      <c r="M6">
+        <v>8</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>6</v>
+      </c>
+      <c r="P6">
+        <v>10</v>
+      </c>
+      <c r="Q6">
+        <v>4</v>
+      </c>
+      <c r="R6">
+        <v>30</v>
+      </c>
+      <c r="S6">
+        <v>1010</v>
+      </c>
+      <c r="T6">
+        <v>2010</v>
+      </c>
+      <c r="U6">
+        <v>100</v>
+      </c>
+      <c r="V6" s="2" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1255,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -2787,6 +2866,774 @@
         <v>0</v>
       </c>
       <c r="O32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>11000</v>
+      </c>
+      <c r="B33">
+        <v>1030</v>
+      </c>
+      <c r="C33">
+        <v>-1</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>70</v>
+      </c>
+      <c r="F33" t="str">
+        <f>INDEX(Define!L:L,MATCH(E33,Define!K:K))</f>
+        <v>SelectActor</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>100</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>1001</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>11010</v>
+      </c>
+      <c r="B34">
+        <v>1030</v>
+      </c>
+      <c r="C34">
+        <v>-1</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>70</v>
+      </c>
+      <c r="F34" t="str">
+        <f>INDEX(Define!L:L,MATCH(E34,Define!K:K))</f>
+        <v>SelectActor</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>100</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>1002</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>10020</v>
+      </c>
+      <c r="B35">
+        <v>1030</v>
+      </c>
+      <c r="C35">
+        <v>6</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <v>20</v>
+      </c>
+      <c r="F35" t="str">
+        <f>INDEX(Define!L:L,MATCH(E35,Define!K:K))</f>
+        <v>Basement</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>100</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>10030</v>
+      </c>
+      <c r="B36">
+        <v>1030</v>
+      </c>
+      <c r="C36">
+        <v>10</v>
+      </c>
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36">
+        <v>30</v>
+      </c>
+      <c r="F36" t="str">
+        <f>INDEX(Define!L:L,MATCH(E36,Define!K:K))</f>
+        <v>Alcana</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>100</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>11010</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>10040</v>
+      </c>
+      <c r="B37">
+        <v>1030</v>
+      </c>
+      <c r="C37">
+        <v>5</v>
+      </c>
+      <c r="D37">
+        <v>5</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37" t="str">
+        <f>INDEX(Define!L:L,MATCH(E37,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>100</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>10050</v>
+      </c>
+      <c r="B38">
+        <v>1030</v>
+      </c>
+      <c r="C38">
+        <v>7</v>
+      </c>
+      <c r="D38">
+        <v>5</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38" t="str">
+        <f>INDEX(Define!L:L,MATCH(E38,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>100</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>10060</v>
+      </c>
+      <c r="B39">
+        <v>1030</v>
+      </c>
+      <c r="C39">
+        <v>9</v>
+      </c>
+      <c r="D39">
+        <v>5</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39" t="str">
+        <f>INDEX(Define!L:L,MATCH(E39,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>100</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>10070</v>
+      </c>
+      <c r="B40">
+        <v>1030</v>
+      </c>
+      <c r="C40">
+        <v>11</v>
+      </c>
+      <c r="D40">
+        <v>5</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40" t="str">
+        <f>INDEX(Define!L:L,MATCH(E40,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>100</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>11020</v>
+      </c>
+      <c r="B41">
+        <v>1030</v>
+      </c>
+      <c r="C41">
+        <v>13</v>
+      </c>
+      <c r="D41">
+        <v>5</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41" t="str">
+        <f>INDEX(Define!L:L,MATCH(E41,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>100</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>11030</v>
+      </c>
+      <c r="B42">
+        <v>1030</v>
+      </c>
+      <c r="C42">
+        <v>15</v>
+      </c>
+      <c r="D42">
+        <v>5</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42" t="str">
+        <f>INDEX(Define!L:L,MATCH(E42,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>100</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>11040</v>
+      </c>
+      <c r="B43">
+        <v>1030</v>
+      </c>
+      <c r="C43">
+        <v>14</v>
+      </c>
+      <c r="D43">
+        <v>3</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43" t="str">
+        <f>INDEX(Define!L:L,MATCH(E43,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>100</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>11050</v>
+      </c>
+      <c r="B44">
+        <v>1030</v>
+      </c>
+      <c r="C44">
+        <v>14</v>
+      </c>
+      <c r="D44">
+        <v>5</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44" t="str">
+        <f>INDEX(Define!L:L,MATCH(E44,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>100</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>11060</v>
+      </c>
+      <c r="B45">
+        <v>1030</v>
+      </c>
+      <c r="C45">
+        <v>15</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45" t="str">
+        <f>INDEX(Define!L:L,MATCH(E45,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>100</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>11070</v>
+      </c>
+      <c r="B46">
+        <v>1030</v>
+      </c>
+      <c r="C46">
+        <v>15</v>
+      </c>
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46" t="str">
+        <f>INDEX(Define!L:L,MATCH(E46,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>100</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>11080</v>
+      </c>
+      <c r="B47">
+        <v>1030</v>
+      </c>
+      <c r="C47">
+        <v>14</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47">
+        <v>20</v>
+      </c>
+      <c r="F47" t="str">
+        <f>INDEX(Define!L:L,MATCH(E47,Define!K:K))</f>
+        <v>Basement</v>
+      </c>
+      <c r="G47">
+        <v>2</v>
+      </c>
+      <c r="H47">
+        <v>100</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>11090</v>
+      </c>
+      <c r="B48">
+        <v>1030</v>
+      </c>
+      <c r="C48">
+        <v>14</v>
+      </c>
+      <c r="D48">
+        <v>4</v>
+      </c>
+      <c r="E48">
+        <v>1000</v>
+      </c>
+      <c r="F48" t="str">
+        <f>INDEX(Define!L:L,MATCH(E48,Define!K:K))</f>
+        <v>Battler</v>
+      </c>
+      <c r="G48">
+        <v>2</v>
+      </c>
+      <c r="H48">
+        <v>100</v>
+      </c>
+      <c r="I48">
+        <v>1011</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>1011</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48" t="s">
         <v>24</v>
       </c>
     </row>
@@ -3413,10 +4260,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>10010</v>
+        <v>1030</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>95</v>
@@ -3424,7 +4271,15 @@
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C7" s="1"/>
+      <c r="A7">
+        <v>10010</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -3582,8 +4437,8 @@
       <c r="K6">
         <v>30</v>
       </c>
-      <c r="L6" t="s">
-        <v>48</v>
+      <c r="L6" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F75DCD6-8C63-4A88-A517-47C84F762AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C22525-974E-4125-81FC-F1A1E217B1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="108">
   <si>
     <t>Id</t>
   </si>
@@ -110,9 +110,6 @@
   </si>
   <si>
     <t>Seek=-1でステージ開始時に入手</t>
-  </si>
-  <si>
-    <t>Seek=0でランダム生成用</t>
   </si>
   <si>
     <t>EnemyId</t>
@@ -439,6 +436,10 @@
     <rPh sb="5" eb="7">
       <t>キョウカ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GetItem</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -808,13 +809,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
@@ -823,31 +824,31 @@
         <v>4</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="R1" t="s">
         <v>5</v>
@@ -998,7 +999,7 @@
         <v>100</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
@@ -1066,7 +1067,7 @@
         <v>100</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
@@ -1134,7 +1135,7 @@
         <v>100</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
@@ -1202,7 +1203,7 @@
         <v>100</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1231,13 +1232,13 @@
         <v>12</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E1" t="s">
         <v>14</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G1" t="s">
         <v>15</v>
@@ -1334,30 +1335,30 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="E1" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H1" t="s">
         <v>18</v>
@@ -1375,10 +1376,10 @@
         <v>22</v>
       </c>
       <c r="M1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
@@ -1473,9 +1474,6 @@
       <c r="N3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4">
@@ -1521,9 +1519,6 @@
       <c r="N4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5">
@@ -1569,9 +1564,6 @@
       <c r="N5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6">
@@ -1617,9 +1609,6 @@
       <c r="N6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7">
@@ -1665,9 +1654,6 @@
       <c r="N7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8">
@@ -1713,9 +1699,6 @@
       <c r="N8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9">
@@ -1809,9 +1792,6 @@
       <c r="N10">
         <v>0</v>
       </c>
-      <c r="O10" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11">
@@ -1857,9 +1837,6 @@
       <c r="N11">
         <v>0</v>
       </c>
-      <c r="O11" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12">
@@ -1905,9 +1882,6 @@
       <c r="N12">
         <v>0</v>
       </c>
-      <c r="O12" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13">
@@ -1953,9 +1927,6 @@
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="O13" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14">
@@ -2001,9 +1972,6 @@
       <c r="N14">
         <v>0</v>
       </c>
-      <c r="O14" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15">
@@ -2049,9 +2017,6 @@
       <c r="N15">
         <v>0</v>
       </c>
-      <c r="O15" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16">
@@ -2097,9 +2062,6 @@
       <c r="N16">
         <v>0</v>
       </c>
-      <c r="O16" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17">
@@ -2241,9 +2203,6 @@
       <c r="N19">
         <v>0</v>
       </c>
-      <c r="O19" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20">
@@ -2289,9 +2248,6 @@
       <c r="N20">
         <v>0</v>
       </c>
-      <c r="O20" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21">
@@ -2337,9 +2293,6 @@
       <c r="N21">
         <v>0</v>
       </c>
-      <c r="O21" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22">
@@ -2385,9 +2338,6 @@
       <c r="N22">
         <v>0</v>
       </c>
-      <c r="O22" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23">
@@ -2433,9 +2383,6 @@
       <c r="N23">
         <v>0</v>
       </c>
-      <c r="O23" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24">
@@ -2481,9 +2428,6 @@
       <c r="N24">
         <v>0</v>
       </c>
-      <c r="O24" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25">
@@ -2529,9 +2473,6 @@
       <c r="N25">
         <v>0</v>
       </c>
-      <c r="O25" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26">
@@ -2577,9 +2518,6 @@
       <c r="N26">
         <v>0</v>
       </c>
-      <c r="O26" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27">
@@ -2625,9 +2563,6 @@
       <c r="N27">
         <v>0</v>
       </c>
-      <c r="O27" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28">
@@ -2673,9 +2608,6 @@
       <c r="N28">
         <v>0</v>
       </c>
-      <c r="O28" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29">
@@ -2721,9 +2653,6 @@
       <c r="N29">
         <v>0</v>
       </c>
-      <c r="O29" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30">
@@ -2769,9 +2698,6 @@
       <c r="N30">
         <v>0</v>
       </c>
-      <c r="O30" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31">
@@ -2817,9 +2743,6 @@
       <c r="N31">
         <v>0</v>
       </c>
-      <c r="O31" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32">
@@ -2865,9 +2788,6 @@
       <c r="N32">
         <v>0</v>
       </c>
-      <c r="O32" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33">
@@ -3009,9 +2929,6 @@
       <c r="N35">
         <v>0</v>
       </c>
-      <c r="O35" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36">
@@ -3021,7 +2938,7 @@
         <v>1030</v>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -3057,9 +2974,6 @@
       <c r="N36">
         <v>0</v>
       </c>
-      <c r="O36" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37">
@@ -3069,20 +2983,20 @@
         <v>1030</v>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F37" t="str">
         <f>INDEX(Define!L:L,MATCH(E37,Define!K:K))</f>
-        <v>None</v>
+        <v>GetItem</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
         <v>100</v>
@@ -3094,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -3104,9 +3018,6 @@
       </c>
       <c r="N37">
         <v>0</v>
-      </c>
-      <c r="O37" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.2">
@@ -3117,7 +3028,7 @@
         <v>1030</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -3153,9 +3064,6 @@
       <c r="N38">
         <v>0</v>
       </c>
-      <c r="O38" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39">
@@ -3165,7 +3073,7 @@
         <v>1030</v>
       </c>
       <c r="C39">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -3201,9 +3109,6 @@
       <c r="N39">
         <v>0</v>
       </c>
-      <c r="O39" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40">
@@ -3213,7 +3118,7 @@
         <v>1030</v>
       </c>
       <c r="C40">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D40">
         <v>5</v>
@@ -3249,19 +3154,16 @@
       <c r="N40">
         <v>0</v>
       </c>
-      <c r="O40" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>11020</v>
+        <v>10080</v>
       </c>
       <c r="B41">
         <v>1030</v>
       </c>
       <c r="C41">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D41">
         <v>5</v>
@@ -3297,19 +3199,16 @@
       <c r="N41">
         <v>0</v>
       </c>
-      <c r="O41" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>11030</v>
+        <v>11020</v>
       </c>
       <c r="B42">
         <v>1030</v>
       </c>
       <c r="C42">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D42">
         <v>5</v>
@@ -3345,22 +3244,19 @@
       <c r="N42">
         <v>0</v>
       </c>
-      <c r="O42" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>11040</v>
+        <v>11030</v>
       </c>
       <c r="B43">
         <v>1030</v>
       </c>
       <c r="C43">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3393,13 +3289,10 @@
       <c r="N43">
         <v>0</v>
       </c>
-      <c r="O43" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>11050</v>
+        <v>11040</v>
       </c>
       <c r="B44">
         <v>1030</v>
@@ -3408,7 +3301,7 @@
         <v>14</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3441,22 +3334,19 @@
       <c r="N44">
         <v>0</v>
       </c>
-      <c r="O44" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>11060</v>
+        <v>11050</v>
       </c>
       <c r="B45">
         <v>1030</v>
       </c>
       <c r="C45">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3489,13 +3379,10 @@
       <c r="N45">
         <v>0</v>
       </c>
-      <c r="O45" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>11070</v>
+        <v>11060</v>
       </c>
       <c r="B46">
         <v>1030</v>
@@ -3504,7 +3391,7 @@
         <v>15</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3537,32 +3424,29 @@
       <c r="N46">
         <v>0</v>
       </c>
-      <c r="O46" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>11080</v>
+        <v>11070</v>
       </c>
       <c r="B47">
         <v>1030</v>
       </c>
       <c r="C47">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D47">
         <v>4</v>
       </c>
       <c r="E47">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F47" t="str">
         <f>INDEX(Define!L:L,MATCH(E47,Define!K:K))</f>
-        <v>Basement</v>
+        <v>None</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47">
         <v>100</v>
@@ -3584,14 +3468,11 @@
       </c>
       <c r="N47">
         <v>0</v>
-      </c>
-      <c r="O47" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>11090</v>
+        <v>11080</v>
       </c>
       <c r="B48">
         <v>1030</v>
@@ -3603,11 +3484,11 @@
         <v>4</v>
       </c>
       <c r="E48">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="F48" t="str">
         <f>INDEX(Define!L:L,MATCH(E48,Define!K:K))</f>
-        <v>Battler</v>
+        <v>Basement</v>
       </c>
       <c r="G48">
         <v>2</v>
@@ -3616,25 +3497,67 @@
         <v>100</v>
       </c>
       <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>11090</v>
+      </c>
+      <c r="B49">
+        <v>1030</v>
+      </c>
+      <c r="C49">
+        <v>14</v>
+      </c>
+      <c r="D49">
+        <v>4</v>
+      </c>
+      <c r="E49">
+        <v>1000</v>
+      </c>
+      <c r="F49" t="str">
+        <f>INDEX(Define!L:L,MATCH(E49,Define!K:K))</f>
+        <v>Battler</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49">
+        <v>100</v>
+      </c>
+      <c r="I49">
         <v>1011</v>
       </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
         <v>1011</v>
       </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48" t="s">
-        <v>24</v>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3653,10 +3576,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
         <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -3741,7 +3664,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
         <v>17</v>
@@ -4144,19 +4067,19 @@
         <v>12</v>
       </c>
       <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>31</v>
-      </c>
-      <c r="H1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -4205,10 +4128,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" t="s">
         <v>33</v>
-      </c>
-      <c r="C1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -4216,10 +4139,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -4227,10 +4150,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -4239,10 +4162,10 @@
         <v>1010</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D4" s="1"/>
     </row>
@@ -4251,10 +4174,10 @@
         <v>1020</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" s="1"/>
     </row>
@@ -4263,10 +4186,10 @@
         <v>1030</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" s="1"/>
     </row>
@@ -4275,10 +4198,10 @@
         <v>10010</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -4314,7 +4237,7 @@
         <v>17</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -4322,25 +4245,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -4348,25 +4271,25 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -4374,25 +4297,25 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -4400,25 +4323,25 @@
         <v>1010</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -4426,19 +4349,19 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -4446,19 +4369,19 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
-      <c r="L7" t="s">
-        <v>50</v>
+      <c r="L7" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -4466,19 +4389,19 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -4486,19 +4409,19 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -4506,19 +4429,19 @@
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -4526,19 +4449,19 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -4546,19 +4469,19 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K12">
         <v>99</v>
       </c>
       <c r="L12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -4566,19 +4489,19 @@
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K13">
         <v>1000</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
@@ -4586,7 +4509,7 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -4594,7 +4517,7 @@
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
@@ -4602,7 +4525,7 @@
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.2">
@@ -4610,7 +4533,7 @@
         <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.2">
@@ -4618,7 +4541,7 @@
         <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.2">
@@ -4626,7 +4549,7 @@
         <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="4:5" x14ac:dyDescent="0.2">
@@ -4634,7 +4557,7 @@
         <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="4:5" x14ac:dyDescent="0.2">
@@ -4642,7 +4565,7 @@
         <v>51</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="4:5" x14ac:dyDescent="0.2">
@@ -4650,7 +4573,7 @@
         <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="4:5" x14ac:dyDescent="0.2">
@@ -4658,7 +4581,7 @@
         <v>62</v>
       </c>
       <c r="E23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="4:5" x14ac:dyDescent="0.2">
@@ -4666,7 +4589,7 @@
         <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="4:5" x14ac:dyDescent="0.2">
@@ -4674,7 +4597,7 @@
         <v>110</v>
       </c>
       <c r="E25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="4:5" x14ac:dyDescent="0.2">
@@ -4682,7 +4605,7 @@
         <v>201</v>
       </c>
       <c r="E26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="4:5" x14ac:dyDescent="0.2">
@@ -4690,7 +4613,7 @@
         <v>1010</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="4:5" x14ac:dyDescent="0.2">
@@ -4698,7 +4621,7 @@
         <v>1011</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C22525-974E-4125-81FC-F1A1E217B1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A44BC6-852E-441E-B8EF-23A4F0B361E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="115">
   <si>
     <t>Id</t>
   </si>
@@ -440,6 +440,38 @@
   </si>
   <si>
     <t>GetItem</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>進撃</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>近くにいる敵に向かって移動し、射程に捉えれば攻撃してくる。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>固定</t>
+    <rPh sb="0" eb="2">
+      <t>コテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>迎撃</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>射程内に攻撃可能な敵がいれば攻撃、いなければその場で待機。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>警戒</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>射程内に攻撃可能な敵がいれば攻撃、
+いない場合は敵の射程に入っていれば射程外へ逃げる、入っていなければその場で待機。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3523,7 +3555,7 @@
         <v>1030</v>
       </c>
       <c r="C49">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D49">
         <v>4</v>
@@ -3554,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N49">
         <v>0</v>
@@ -4223,10 +4255,13 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="15" max="15" width="45.90625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -4239,8 +4274,11 @@
       <c r="K1" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M1" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4265,8 +4303,14 @@
       <c r="L2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>110</v>
       </c>
@@ -4291,8 +4335,17 @@
       <c r="L3" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M3">
+        <v>10</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>210</v>
       </c>
@@ -4317,8 +4370,17 @@
       <c r="L4" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M4">
+        <v>20</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="39" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1010</v>
       </c>
@@ -4343,8 +4405,17 @@
       <c r="L5" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M5">
+        <v>30</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D6">
         <v>4</v>
       </c>
@@ -4364,7 +4435,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D7">
         <v>5</v>
       </c>
@@ -4384,7 +4455,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D8">
         <v>6</v>
       </c>
@@ -4404,7 +4475,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D9">
         <v>7</v>
       </c>
@@ -4424,7 +4495,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D10">
         <v>8</v>
       </c>
@@ -4444,7 +4515,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D11">
         <v>9</v>
       </c>
@@ -4464,7 +4535,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D12">
         <v>12</v>
       </c>
@@ -4484,7 +4555,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D13">
         <v>13</v>
       </c>
@@ -4504,7 +4575,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D14">
         <v>14</v>
       </c>
@@ -4512,7 +4583,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D15">
         <v>15</v>
       </c>
@@ -4520,7 +4591,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16">
         <v>21</v>
       </c>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A44BC6-852E-441E-B8EF-23A4F0B361E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5309C123-2534-4C59-886F-28B5E819D2C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,10 @@
     <sheet name="StageSymbols" sheetId="8" r:id="rId3"/>
     <sheet name="StageEnemyRates" sheetId="9" r:id="rId4"/>
     <sheet name="SymbolGroup" sheetId="7" r:id="rId5"/>
-    <sheet name="Tutorials" sheetId="4" r:id="rId6"/>
-    <sheet name="TextData" sheetId="5" r:id="rId7"/>
-    <sheet name="Define" sheetId="6" r:id="rId8"/>
+    <sheet name="MoveParamType" sheetId="10" r:id="rId6"/>
+    <sheet name="Tutorials" sheetId="4" r:id="rId7"/>
+    <sheet name="TextData" sheetId="5" r:id="rId8"/>
+    <sheet name="Define" sheetId="6" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="130">
   <si>
     <t>Id</t>
   </si>
@@ -472,6 +473,71 @@
   <si>
     <t>射程内に攻撃可能な敵がいれば攻撃、
 いない場合は敵の射程に入っていれば射程外へ逃げる、入っていなければその場で待機。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>徘徊</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ランダムに移動。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>巡回</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>射程内に攻撃可能な敵がいれば攻撃、いなければ一定のルートを移動。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SymbolId</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Param1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Param2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Param3</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Param4</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>固定</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>その場を動かない。
+その場から攻撃可能なら攻撃する。
+隣接など攻撃可能でないと挑発は出来ない。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>移動</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>特定の目標に向かって移動。攻撃してこない。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>離脱</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>離脱ポイントへ向かう。攻撃してこない。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3555,7 +3621,7 @@
         <v>1030</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D49">
         <v>4</v>
@@ -3586,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="M49">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="N49">
         <v>0</v>
@@ -4084,6 +4150,51 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38DF549-830A-441A-B02B-F6F6904091C0}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>11090</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>13</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -4146,7 +4257,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -4253,7 +4364,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:O28"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -4434,6 +4545,15 @@
       <c r="L6" s="2" t="s">
         <v>105</v>
       </c>
+      <c r="M6">
+        <v>40</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D7">
@@ -4454,8 +4574,17 @@
       <c r="L7" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M7">
+        <v>50</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="39" x14ac:dyDescent="0.2">
       <c r="D8">
         <v>6</v>
       </c>
@@ -4473,6 +4602,15 @@
       </c>
       <c r="L8" t="s">
         <v>51</v>
+      </c>
+      <c r="M8">
+        <v>60</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -4494,6 +4632,15 @@
       <c r="L9" t="s">
         <v>53</v>
       </c>
+      <c r="M9">
+        <v>70</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D10">
@@ -4513,6 +4660,15 @@
       </c>
       <c r="L10" t="s">
         <v>55</v>
+      </c>
+      <c r="M10">
+        <v>80</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5309C123-2534-4C59-886F-28B5E819D2C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EB4C31-094B-4B4A-ABC7-FC8F80B3869F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="131">
   <si>
     <t>Id</t>
   </si>
@@ -538,6 +538,10 @@
   </si>
   <si>
     <t>離脱ポイントへ向かう。攻撃してこない。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Gacha</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1061,28 +1065,28 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="N3">
         <v>1</v>
       </c>
       <c r="O3">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R3">
         <v>30</v>
@@ -1433,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -1536,38 +1540,38 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="F3" t="str">
         <f>INDEX(Define!L:L,MATCH(E3,Define!K:K))</f>
-        <v>Battler</v>
+        <v>Basement</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>100</v>
       </c>
       <c r="I3">
-        <v>1011</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1011</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -1581,20 +1585,20 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>4</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="F4" t="str">
         <f>INDEX(Define!L:L,MATCH(E4,Define!K:K))</f>
-        <v>Basement</v>
+        <v>Gacha</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>100</v>
@@ -1620,23 +1624,23 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1030</v>
+        <v>10000</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>1010</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F5" t="str">
         <f>INDEX(Define!L:L,MATCH(E5,Define!K:K))</f>
-        <v>None</v>
+        <v>SelectActor</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1651,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1661,42 +1665,45 @@
       </c>
       <c r="N5">
         <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>1040</v>
+        <v>10010</v>
       </c>
       <c r="B6">
+        <v>1010</v>
+      </c>
+      <c r="C6">
         <v>10</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>4</v>
       </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
       <c r="E6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F6" t="str">
         <f>INDEX(Define!L:L,MATCH(E6,Define!K:K))</f>
-        <v>None</v>
+        <v>Battler</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1710,10 +1717,10 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>1050</v>
+        <v>10020</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>1010</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1722,14 +1729,14 @@
         <v>4</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F7" t="str">
         <f>INDEX(Define!L:L,MATCH(E7,Define!K:K))</f>
-        <v>None</v>
+        <v>Basement</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>100</v>
@@ -1755,26 +1762,26 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>1060</v>
+        <v>10030</v>
       </c>
       <c r="B8">
+        <v>1010</v>
+      </c>
+      <c r="C8">
         <v>10</v>
       </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
       <c r="D8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F8" t="str">
         <f>INDEX(Define!L:L,MATCH(E8,Define!K:K))</f>
-        <v>None</v>
+        <v>Basement</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
         <v>100</v>
@@ -1800,23 +1807,23 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>10000</v>
+        <v>10040</v>
       </c>
       <c r="B9">
         <v>1010</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E9">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F9" t="str">
         <f>INDEX(Define!L:L,MATCH(E9,Define!K:K))</f>
-        <v>SelectActor</v>
+        <v>None</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1831,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1841,45 +1848,42 @@
       </c>
       <c r="N9">
         <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>10010</v>
+        <v>10050</v>
       </c>
       <c r="B10">
         <v>1010</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F10" t="str">
         <f>INDEX(Define!L:L,MATCH(E10,Define!K:K))</f>
-        <v>Battler</v>
+        <v>None</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>100</v>
       </c>
       <c r="I10">
-        <v>1011</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>1011</v>
+        <v>0</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1893,26 +1897,26 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>10020</v>
+        <v>10060</v>
       </c>
       <c r="B11">
         <v>1010</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F11" t="str">
         <f>INDEX(Define!L:L,MATCH(E11,Define!K:K))</f>
-        <v>Basement</v>
+        <v>None</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>100</v>
@@ -1938,26 +1942,26 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>10030</v>
+        <v>10070</v>
       </c>
       <c r="B12">
         <v>1010</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F12" t="str">
         <f>INDEX(Define!L:L,MATCH(E12,Define!K:K))</f>
-        <v>Basement</v>
+        <v>None</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>100</v>
@@ -1983,23 +1987,23 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>10040</v>
+        <v>11000</v>
       </c>
       <c r="B13">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F13" t="str">
         <f>INDEX(Define!L:L,MATCH(E13,Define!K:K))</f>
-        <v>None</v>
+        <v>SelectActor</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2014,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -2024,27 +2028,30 @@
       </c>
       <c r="N13">
         <v>0</v>
+      </c>
+      <c r="O13" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>10050</v>
+        <v>11010</v>
       </c>
       <c r="B14">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F14" t="str">
         <f>INDEX(Define!L:L,MATCH(E14,Define!K:K))</f>
-        <v>None</v>
+        <v>SelectActor</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2059,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2069,30 +2076,33 @@
       </c>
       <c r="N14">
         <v>0</v>
+      </c>
+      <c r="O14" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>10060</v>
+        <v>10020</v>
       </c>
       <c r="B15">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F15" t="str">
         <f>INDEX(Define!L:L,MATCH(E15,Define!K:K))</f>
-        <v>None</v>
+        <v>Basement</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>100</v>
@@ -2118,26 +2128,26 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>10070</v>
+        <v>10030</v>
       </c>
       <c r="B16">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F16" t="str">
         <f>INDEX(Define!L:L,MATCH(E16,Define!K:K))</f>
-        <v>None</v>
+        <v>Basement</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>100</v>
@@ -2163,23 +2173,23 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>11000</v>
+        <v>10040</v>
       </c>
       <c r="B17">
         <v>1020</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E17">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F17" t="str">
         <f>INDEX(Define!L:L,MATCH(E17,Define!K:K))</f>
-        <v>SelectActor</v>
+        <v>None</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2194,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2204,30 +2214,27 @@
       </c>
       <c r="N17">
         <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>11010</v>
+        <v>10050</v>
       </c>
       <c r="B18">
         <v>1020</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E18">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F18" t="str">
         <f>INDEX(Define!L:L,MATCH(E18,Define!K:K))</f>
-        <v>SelectActor</v>
+        <v>None</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2242,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>1002</v>
+        <v>0</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -2252,33 +2259,30 @@
       </c>
       <c r="N18">
         <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>10020</v>
+        <v>10060</v>
       </c>
       <c r="B19">
         <v>1020</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F19" t="str">
         <f>INDEX(Define!L:L,MATCH(E19,Define!K:K))</f>
-        <v>Basement</v>
+        <v>None</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <v>100</v>
@@ -2304,26 +2308,26 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>10030</v>
+        <v>10070</v>
       </c>
       <c r="B20">
         <v>1020</v>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F20" t="str">
         <f>INDEX(Define!L:L,MATCH(E20,Define!K:K))</f>
-        <v>Basement</v>
+        <v>None</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>100</v>
@@ -2349,13 +2353,13 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>10040</v>
+        <v>11020</v>
       </c>
       <c r="B21">
         <v>1020</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -2394,13 +2398,13 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>10050</v>
+        <v>11030</v>
       </c>
       <c r="B22">
         <v>1020</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D22">
         <v>5</v>
@@ -2439,16 +2443,16 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>10060</v>
+        <v>11040</v>
       </c>
       <c r="B23">
         <v>1020</v>
       </c>
       <c r="C23">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2484,13 +2488,13 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>10070</v>
+        <v>11050</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -2529,16 +2533,16 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>11020</v>
+        <v>11060</v>
       </c>
       <c r="B25">
         <v>1020</v>
       </c>
       <c r="C25">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2574,7 +2578,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>11030</v>
+        <v>11070</v>
       </c>
       <c r="B26">
         <v>1020</v>
@@ -2583,7 +2587,7 @@
         <v>15</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2619,7 +2623,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>11040</v>
+        <v>11080</v>
       </c>
       <c r="B27">
         <v>1020</v>
@@ -2628,17 +2632,17 @@
         <v>14</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F27" t="str">
         <f>INDEX(Define!L:L,MATCH(E27,Define!K:K))</f>
-        <v>None</v>
+        <v>Basement</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27">
         <v>100</v>
@@ -2664,7 +2668,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>11050</v>
+        <v>11090</v>
       </c>
       <c r="B28">
         <v>1020</v>
@@ -2673,29 +2677,29 @@
         <v>14</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F28" t="str">
         <f>INDEX(Define!L:L,MATCH(E28,Define!K:K))</f>
-        <v>None</v>
+        <v>Battler</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28">
         <v>100</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -2709,23 +2713,23 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>11060</v>
+        <v>11000</v>
       </c>
       <c r="B29">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="C29">
-        <v>15</v>
+        <v>-1</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F29" t="str">
         <f>INDEX(Define!L:L,MATCH(E29,Define!K:K))</f>
-        <v>None</v>
+        <v>SelectActor</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -2740,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -2750,27 +2754,30 @@
       </c>
       <c r="N29">
         <v>0</v>
+      </c>
+      <c r="O29" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>11070</v>
+        <v>11010</v>
       </c>
       <c r="B30">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="C30">
-        <v>15</v>
+        <v>-1</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F30" t="str">
         <f>INDEX(Define!L:L,MATCH(E30,Define!K:K))</f>
-        <v>None</v>
+        <v>SelectActor</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -2785,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -2795,17 +2802,20 @@
       </c>
       <c r="N30">
         <v>0</v>
+      </c>
+      <c r="O30" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>11080</v>
+        <v>10020</v>
       </c>
       <c r="B31">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="C31">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D31">
         <v>4</v>
@@ -2818,7 +2828,7 @@
         <v>Basement</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>100</v>
@@ -2844,38 +2854,38 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>11090</v>
+        <v>10030</v>
       </c>
       <c r="B32">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="C32">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="F32" t="str">
         <f>INDEX(Define!L:L,MATCH(E32,Define!K:K))</f>
-        <v>Battler</v>
+        <v>Alcana</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>100</v>
       </c>
       <c r="I32">
-        <v>1011</v>
+        <v>0</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
-        <v>1011</v>
+        <v>11010</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -2887,28 +2897,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>11000</v>
+        <v>10040</v>
       </c>
       <c r="B33">
         <v>1030</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E33">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F33" t="str">
         <f>INDEX(Define!L:L,MATCH(E33,Define!K:K))</f>
-        <v>SelectActor</v>
+        <v>GetItem</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33">
         <v>100</v>
@@ -2920,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>1001</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -2931,29 +2941,26 @@
       <c r="N33">
         <v>0</v>
       </c>
-      <c r="O33" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>11010</v>
+        <v>10050</v>
       </c>
       <c r="B34">
         <v>1030</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E34">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F34" t="str">
         <f>INDEX(Define!L:L,MATCH(E34,Define!K:K))</f>
-        <v>SelectActor</v>
+        <v>None</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -2968,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>1002</v>
+        <v>0</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -2979,32 +2986,29 @@
       <c r="N34">
         <v>0</v>
       </c>
-      <c r="O34" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>10020</v>
+        <v>10060</v>
       </c>
       <c r="B35">
         <v>1030</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F35" t="str">
         <f>INDEX(Define!L:L,MATCH(E35,Define!K:K))</f>
-        <v>Basement</v>
+        <v>None</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35">
         <v>100</v>
@@ -3028,28 +3032,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>10030</v>
+        <v>10070</v>
       </c>
       <c r="B36">
         <v>1030</v>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F36" t="str">
         <f>INDEX(Define!L:L,MATCH(E36,Define!K:K))</f>
-        <v>Alcana</v>
+        <v>None</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36">
         <v>100</v>
@@ -3061,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>11010</v>
+        <v>0</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -3073,28 +3077,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>10040</v>
+        <v>10080</v>
       </c>
       <c r="B37">
         <v>1030</v>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F37" t="str">
         <f>INDEX(Define!L:L,MATCH(E37,Define!K:K))</f>
-        <v>GetItem</v>
+        <v>None</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37">
         <v>100</v>
@@ -3106,7 +3110,7 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -3118,15 +3122,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>10050</v>
+        <v>11020</v>
       </c>
       <c r="B38">
         <v>1030</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -3163,15 +3167,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>10060</v>
+        <v>11030</v>
       </c>
       <c r="B39">
         <v>1030</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -3208,18 +3212,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>10070</v>
+        <v>11040</v>
       </c>
       <c r="B40">
         <v>1030</v>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3253,15 +3257,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>10080</v>
+        <v>11050</v>
       </c>
       <c r="B41">
         <v>1030</v>
       </c>
       <c r="C41">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D41">
         <v>5</v>
@@ -3298,18 +3302,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>11020</v>
+        <v>11060</v>
       </c>
       <c r="B42">
         <v>1030</v>
       </c>
       <c r="C42">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3343,9 +3347,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>11030</v>
+        <v>11070</v>
       </c>
       <c r="B43">
         <v>1030</v>
@@ -3354,7 +3358,7 @@
         <v>15</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3388,9 +3392,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>11040</v>
+        <v>11080</v>
       </c>
       <c r="B44">
         <v>1030</v>
@@ -3399,17 +3403,17 @@
         <v>14</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F44" t="str">
         <f>INDEX(Define!L:L,MATCH(E44,Define!K:K))</f>
-        <v>None</v>
+        <v>Basement</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H44">
         <v>100</v>
@@ -3433,228 +3437,48 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>11050</v>
+        <v>11090</v>
       </c>
       <c r="B45">
         <v>1030</v>
       </c>
       <c r="C45">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F45" t="str">
         <f>INDEX(Define!L:L,MATCH(E45,Define!K:K))</f>
-        <v>None</v>
+        <v>Battler</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45">
         <v>100</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>11060</v>
-      </c>
-      <c r="B46">
-        <v>1030</v>
-      </c>
-      <c r="C46">
-        <v>15</v>
-      </c>
-      <c r="D46">
-        <v>3</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46" t="str">
-        <f>INDEX(Define!L:L,MATCH(E46,Define!K:K))</f>
-        <v>None</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>100</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>11070</v>
-      </c>
-      <c r="B47">
-        <v>1030</v>
-      </c>
-      <c r="C47">
-        <v>15</v>
-      </c>
-      <c r="D47">
-        <v>4</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47" t="str">
-        <f>INDEX(Define!L:L,MATCH(E47,Define!K:K))</f>
-        <v>None</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>100</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>11080</v>
-      </c>
-      <c r="B48">
-        <v>1030</v>
-      </c>
-      <c r="C48">
-        <v>14</v>
-      </c>
-      <c r="D48">
-        <v>4</v>
-      </c>
-      <c r="E48">
-        <v>20</v>
-      </c>
-      <c r="F48" t="str">
-        <f>INDEX(Define!L:L,MATCH(E48,Define!K:K))</f>
-        <v>Basement</v>
-      </c>
-      <c r="G48">
-        <v>2</v>
-      </c>
-      <c r="H48">
-        <v>100</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>11090</v>
-      </c>
-      <c r="B49">
-        <v>1030</v>
-      </c>
-      <c r="C49">
-        <v>9</v>
-      </c>
-      <c r="D49">
-        <v>4</v>
-      </c>
-      <c r="E49">
-        <v>1000</v>
-      </c>
-      <c r="F49" t="str">
-        <f>INDEX(Define!L:L,MATCH(E49,Define!K:K))</f>
-        <v>Battler</v>
-      </c>
-      <c r="G49">
-        <v>2</v>
-      </c>
-      <c r="H49">
-        <v>100</v>
-      </c>
-      <c r="I49">
-        <v>1011</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>1011</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>50</v>
-      </c>
-      <c r="N49">
         <v>0</v>
       </c>
     </row>
@@ -4705,10 +4529,10 @@
         <v>57</v>
       </c>
       <c r="K12">
-        <v>99</v>
-      </c>
-      <c r="L12" t="s">
-        <v>59</v>
+        <v>90</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -4725,10 +4549,10 @@
         <v>59</v>
       </c>
       <c r="K13">
-        <v>1000</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>81</v>
+        <v>99</v>
+      </c>
+      <c r="L13" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -4737,6 +4561,12 @@
       </c>
       <c r="E14" t="s">
         <v>60</v>
+      </c>
+      <c r="K14">
+        <v>1000</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EB4C31-094B-4B4A-ABC7-FC8F80B3869F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA53204-BF8B-4E40-ACED-4B3DAC098D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -1053,7 +1053,7 @@
         <v>10010</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1068,25 +1068,25 @@
         <v>16</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M3">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="O3">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="P3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q3">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="R3">
         <v>30</v>
@@ -1437,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -1540,10 +1540,10 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -1585,10 +1585,10 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="E4">
         <v>90</v>
@@ -1624,23 +1624,23 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>10000</v>
+        <v>1030</v>
       </c>
       <c r="B5">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E5">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="F5" t="str">
         <f>INDEX(Define!L:L,MATCH(E5,Define!K:K))</f>
-        <v>SelectActor</v>
+        <v>Basement</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1655,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1665,23 +1665,20 @@
       </c>
       <c r="N5">
         <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>10010</v>
+        <v>1040</v>
       </c>
       <c r="B6">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>1000</v>
@@ -1717,16 +1714,16 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>10020</v>
+        <v>1050</v>
       </c>
       <c r="B7">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>20</v>
@@ -1736,7 +1733,7 @@
         <v>Basement</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <v>100</v>
@@ -1762,26 +1759,26 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>10030</v>
+        <v>10000</v>
       </c>
       <c r="B8">
         <v>1010</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="F8" t="str">
         <f>INDEX(Define!L:L,MATCH(E8,Define!K:K))</f>
-        <v>Basement</v>
+        <v>SelectActor</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>100</v>
@@ -1793,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1803,42 +1800,45 @@
       </c>
       <c r="N8">
         <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>10040</v>
+        <v>10010</v>
       </c>
       <c r="B9">
         <v>1010</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F9" t="str">
         <f>INDEX(Define!L:L,MATCH(E9,Define!K:K))</f>
-        <v>None</v>
+        <v>Battler</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1852,26 +1852,26 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>10050</v>
+        <v>10020</v>
       </c>
       <c r="B10">
         <v>1010</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F10" t="str">
         <f>INDEX(Define!L:L,MATCH(E10,Define!K:K))</f>
-        <v>None</v>
+        <v>Basement</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>100</v>
@@ -1897,26 +1897,26 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>10060</v>
+        <v>10030</v>
       </c>
       <c r="B11">
         <v>1010</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F11" t="str">
         <f>INDEX(Define!L:L,MATCH(E11,Define!K:K))</f>
-        <v>None</v>
+        <v>Basement</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
         <v>100</v>
@@ -1942,13 +1942,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>10070</v>
+        <v>10040</v>
       </c>
       <c r="B12">
         <v>1010</v>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -1987,23 +1987,23 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>11000</v>
+        <v>10050</v>
       </c>
       <c r="B13">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E13">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F13" t="str">
         <f>INDEX(Define!L:L,MATCH(E13,Define!K:K))</f>
-        <v>SelectActor</v>
+        <v>None</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2018,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -2028,30 +2028,27 @@
       </c>
       <c r="N13">
         <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>11010</v>
+        <v>10060</v>
       </c>
       <c r="B14">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E14">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F14" t="str">
         <f>INDEX(Define!L:L,MATCH(E14,Define!K:K))</f>
-        <v>SelectActor</v>
+        <v>None</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2066,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>1002</v>
+        <v>0</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2076,33 +2073,30 @@
       </c>
       <c r="N14">
         <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>10020</v>
+        <v>10070</v>
       </c>
       <c r="B15">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F15" t="str">
         <f>INDEX(Define!L:L,MATCH(E15,Define!K:K))</f>
-        <v>Basement</v>
+        <v>None</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>100</v>
@@ -2128,26 +2122,26 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>10030</v>
+        <v>11000</v>
       </c>
       <c r="B16">
         <v>1020</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="F16" t="str">
         <f>INDEX(Define!L:L,MATCH(E16,Define!K:K))</f>
-        <v>Basement</v>
+        <v>SelectActor</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16">
         <v>100</v>
@@ -2159,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2169,27 +2163,30 @@
       </c>
       <c r="N16">
         <v>0</v>
+      </c>
+      <c r="O16" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>10040</v>
+        <v>11010</v>
       </c>
       <c r="B17">
         <v>1020</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F17" t="str">
         <f>INDEX(Define!L:L,MATCH(E17,Define!K:K))</f>
-        <v>None</v>
+        <v>SelectActor</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2204,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2214,30 +2211,33 @@
       </c>
       <c r="N17">
         <v>0</v>
+      </c>
+      <c r="O17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>10050</v>
+        <v>10020</v>
       </c>
       <c r="B18">
         <v>1020</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F18" t="str">
         <f>INDEX(Define!L:L,MATCH(E18,Define!K:K))</f>
-        <v>None</v>
+        <v>Basement</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
         <v>100</v>
@@ -2263,26 +2263,26 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>10060</v>
+        <v>10030</v>
       </c>
       <c r="B19">
         <v>1020</v>
       </c>
       <c r="C19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F19" t="str">
         <f>INDEX(Define!L:L,MATCH(E19,Define!K:K))</f>
-        <v>None</v>
+        <v>Basement</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
         <v>100</v>
@@ -2308,13 +2308,13 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>10070</v>
+        <v>10040</v>
       </c>
       <c r="B20">
         <v>1020</v>
       </c>
       <c r="C20">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>5</v>
@@ -2353,13 +2353,13 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>11020</v>
+        <v>10050</v>
       </c>
       <c r="B21">
         <v>1020</v>
       </c>
       <c r="C21">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -2398,13 +2398,13 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>11030</v>
+        <v>10060</v>
       </c>
       <c r="B22">
         <v>1020</v>
       </c>
       <c r="C22">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D22">
         <v>5</v>
@@ -2443,16 +2443,16 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>11040</v>
+        <v>10070</v>
       </c>
       <c r="B23">
         <v>1020</v>
       </c>
       <c r="C23">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2488,13 +2488,13 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>11050</v>
+        <v>11020</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -2533,7 +2533,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>11060</v>
+        <v>11030</v>
       </c>
       <c r="B25">
         <v>1020</v>
@@ -2542,7 +2542,7 @@
         <v>15</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2578,16 +2578,16 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>11070</v>
+        <v>11040</v>
       </c>
       <c r="B26">
         <v>1020</v>
       </c>
       <c r="C26">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>11080</v>
+        <v>11050</v>
       </c>
       <c r="B27">
         <v>1020</v>
@@ -2632,17 +2632,17 @@
         <v>14</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F27" t="str">
         <f>INDEX(Define!L:L,MATCH(E27,Define!K:K))</f>
-        <v>Basement</v>
+        <v>None</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>100</v>
@@ -2668,38 +2668,38 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>11090</v>
+        <v>11060</v>
       </c>
       <c r="B28">
         <v>1020</v>
       </c>
       <c r="C28">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F28" t="str">
         <f>INDEX(Define!L:L,MATCH(E28,Define!K:K))</f>
-        <v>Battler</v>
+        <v>None</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>100</v>
       </c>
       <c r="I28">
-        <v>1011</v>
+        <v>0</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <v>1011</v>
+        <v>0</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -2713,23 +2713,23 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>11000</v>
+        <v>11070</v>
       </c>
       <c r="B29">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F29" t="str">
         <f>INDEX(Define!L:L,MATCH(E29,Define!K:K))</f>
-        <v>SelectActor</v>
+        <v>None</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -2744,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -2754,33 +2754,30 @@
       </c>
       <c r="N29">
         <v>0</v>
-      </c>
-      <c r="O29" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>11010</v>
+        <v>11080</v>
       </c>
       <c r="B30">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E30">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="F30" t="str">
         <f>INDEX(Define!L:L,MATCH(E30,Define!K:K))</f>
-        <v>SelectActor</v>
+        <v>Basement</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30">
         <v>100</v>
@@ -2792,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>1002</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -2802,45 +2799,42 @@
       </c>
       <c r="N30">
         <v>0</v>
-      </c>
-      <c r="O30" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>10020</v>
+        <v>11090</v>
       </c>
       <c r="B31">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D31">
         <v>4</v>
       </c>
       <c r="E31">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="F31" t="str">
         <f>INDEX(Define!L:L,MATCH(E31,Define!K:K))</f>
-        <v>Basement</v>
+        <v>Battler</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31">
         <v>100</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -2854,26 +2848,26 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>10030</v>
+        <v>11000</v>
       </c>
       <c r="B32">
         <v>1030</v>
       </c>
       <c r="C32">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F32" t="str">
         <f>INDEX(Define!L:L,MATCH(E32,Define!K:K))</f>
-        <v>Alcana</v>
+        <v>SelectActor</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32">
         <v>100</v>
@@ -2885,40 +2879,43 @@
         <v>0</v>
       </c>
       <c r="K32">
+        <v>1001</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A33">
         <v>11010</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>10040</v>
       </c>
       <c r="B33">
         <v>1030</v>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="F33" t="str">
         <f>INDEX(Define!L:L,MATCH(E33,Define!K:K))</f>
-        <v>GetItem</v>
+        <v>SelectActor</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <v>100</v>
@@ -2930,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>10</v>
+        <v>1002</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -2941,29 +2938,32 @@
       <c r="N33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>10050</v>
+        <v>10020</v>
       </c>
       <c r="B34">
         <v>1030</v>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F34" t="str">
         <f>INDEX(Define!L:L,MATCH(E34,Define!K:K))</f>
-        <v>None</v>
+        <v>Basement</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <v>100</v>
@@ -2987,28 +2987,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>10060</v>
+        <v>10030</v>
       </c>
       <c r="B35">
         <v>1030</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F35" t="str">
         <f>INDEX(Define!L:L,MATCH(E35,Define!K:K))</f>
-        <v>None</v>
+        <v>Alcana</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35">
         <v>100</v>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>11010</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -3032,28 +3032,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>10070</v>
+        <v>10040</v>
       </c>
       <c r="B36">
         <v>1030</v>
       </c>
       <c r="C36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F36" t="str">
         <f>INDEX(Define!L:L,MATCH(E36,Define!K:K))</f>
-        <v>None</v>
+        <v>GetItem</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>100</v>
@@ -3065,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -3077,15 +3077,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>10080</v>
+        <v>10050</v>
       </c>
       <c r="B37">
         <v>1030</v>
       </c>
       <c r="C37">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -3122,15 +3122,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>11020</v>
+        <v>10060</v>
       </c>
       <c r="B38">
         <v>1030</v>
       </c>
       <c r="C38">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -3167,15 +3167,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>11030</v>
+        <v>10070</v>
       </c>
       <c r="B39">
         <v>1030</v>
       </c>
       <c r="C39">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -3212,18 +3212,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>11040</v>
+        <v>10080</v>
       </c>
       <c r="B40">
         <v>1030</v>
       </c>
       <c r="C40">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3257,15 +3257,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>11050</v>
+        <v>11020</v>
       </c>
       <c r="B41">
         <v>1030</v>
       </c>
       <c r="C41">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D41">
         <v>5</v>
@@ -3302,9 +3302,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>11060</v>
+        <v>11030</v>
       </c>
       <c r="B42">
         <v>1030</v>
@@ -3313,7 +3313,7 @@
         <v>15</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3347,18 +3347,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>11070</v>
+        <v>11040</v>
       </c>
       <c r="B43">
         <v>1030</v>
       </c>
       <c r="C43">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3392,9 +3392,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>11080</v>
+        <v>11050</v>
       </c>
       <c r="B44">
         <v>1030</v>
@@ -3403,17 +3403,17 @@
         <v>14</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E44">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F44" t="str">
         <f>INDEX(Define!L:L,MATCH(E44,Define!K:K))</f>
-        <v>Basement</v>
+        <v>None</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44">
         <v>100</v>
@@ -3437,48 +3437,183 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>11090</v>
+        <v>11060</v>
       </c>
       <c r="B45">
         <v>1030</v>
       </c>
       <c r="C45">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F45" t="str">
         <f>INDEX(Define!L:L,MATCH(E45,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>100</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>11070</v>
+      </c>
+      <c r="B46">
+        <v>1030</v>
+      </c>
+      <c r="C46">
+        <v>15</v>
+      </c>
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46" t="str">
+        <f>INDEX(Define!L:L,MATCH(E46,Define!K:K))</f>
+        <v>None</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>100</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>11080</v>
+      </c>
+      <c r="B47">
+        <v>1030</v>
+      </c>
+      <c r="C47">
+        <v>14</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47">
+        <v>20</v>
+      </c>
+      <c r="F47" t="str">
+        <f>INDEX(Define!L:L,MATCH(E47,Define!K:K))</f>
+        <v>Basement</v>
+      </c>
+      <c r="G47">
+        <v>2</v>
+      </c>
+      <c r="H47">
+        <v>100</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>11090</v>
+      </c>
+      <c r="B48">
+        <v>1030</v>
+      </c>
+      <c r="C48">
+        <v>9</v>
+      </c>
+      <c r="D48">
+        <v>4</v>
+      </c>
+      <c r="E48">
+        <v>1000</v>
+      </c>
+      <c r="F48" t="str">
+        <f>INDEX(Define!L:L,MATCH(E48,Define!K:K))</f>
         <v>Battler</v>
       </c>
-      <c r="G45">
+      <c r="G48">
         <v>2</v>
       </c>
-      <c r="H45">
-        <v>100</v>
-      </c>
-      <c r="I45">
+      <c r="H48">
+        <v>100</v>
+      </c>
+      <c r="I48">
         <v>1011</v>
       </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
         <v>1011</v>
       </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
         <v>50</v>
       </c>
-      <c r="N45">
+      <c r="N48">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA53204-BF8B-4E40-ACED-4B3DAC098D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF296AEF-2CC4-4D8A-9AAE-769188170459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="132">
   <si>
     <t>Id</t>
   </si>
@@ -542,6 +542,10 @@
   </si>
   <si>
     <t>Gacha</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ステージ2</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -892,7 +896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="6" width="8.453125" customWidth="1"/>
@@ -1106,13 +1110,13 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>1010</v>
+        <v>20</v>
       </c>
       <c r="B4">
-        <v>1010</v>
+        <v>20</v>
       </c>
       <c r="C4">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1121,7 +1125,7 @@
         <v>10010</v>
       </c>
       <c r="F4">
-        <v>10030</v>
+        <v>1050</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1136,25 +1140,25 @@
         <v>16</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="O4">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="P4">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Q4">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="R4">
         <v>30</v>
@@ -1174,10 +1178,10 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B5">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="C5">
         <v>101</v>
@@ -1201,13 +1205,13 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K5">
         <v>5</v>
       </c>
       <c r="L5">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M5">
         <v>8</v>
@@ -1219,7 +1223,7 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -1237,15 +1241,15 @@
         <v>100</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B6">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="C6">
         <v>101</v>
@@ -1305,6 +1309,74 @@
         <v>100</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1030</v>
+      </c>
+      <c r="B7">
+        <v>1030</v>
+      </c>
+      <c r="C7">
+        <v>101</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>10010</v>
+      </c>
+      <c r="F7">
+        <v>10030</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>5</v>
+      </c>
+      <c r="L7">
+        <v>16</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+      <c r="N7">
+        <v>3</v>
+      </c>
+      <c r="O7">
+        <v>6</v>
+      </c>
+      <c r="P7">
+        <v>10</v>
+      </c>
+      <c r="Q7">
+        <v>4</v>
+      </c>
+      <c r="R7">
+        <v>30</v>
+      </c>
+      <c r="S7">
+        <v>1010</v>
+      </c>
+      <c r="T7">
+        <v>2010</v>
+      </c>
+      <c r="U7">
+        <v>100</v>
+      </c>
+      <c r="V7" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4218,7 +4290,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34.1796875" customWidth="1"/>
@@ -4261,22 +4333,22 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>1010</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>94</v>
       </c>
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>94</v>
@@ -4285,10 +4357,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>94</v>
@@ -4297,10 +4369,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>10010</v>
+        <v>1030</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>94</v>
@@ -4308,14 +4380,26 @@
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C8" s="1"/>
+      <c r="A8">
+        <v>10010</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>94</v>
+      </c>
       <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C11" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF296AEF-2CC4-4D8A-9AAE-769188170459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E569B1F7-97FE-4CE0-820C-74B977895EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="128">
   <si>
     <t>Id</t>
   </si>
@@ -321,22 +321,6 @@
   </si>
   <si>
     <t>InitTeamId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MinX</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MaxX</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MinY</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MaxY</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -896,15 +880,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="6" width="8.453125" customWidth="1"/>
     <col min="7" max="7" width="10.36328125" customWidth="1"/>
-    <col min="22" max="22" width="32" customWidth="1"/>
+    <col min="18" max="18" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -915,13 +899,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
@@ -936,43 +920,31 @@
         <v>75</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q1" s="2" t="s">
         <v>78</v>
       </c>
+      <c r="N1" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>8</v>
+      </c>
       <c r="R1" t="s">
-        <v>5</v>
-      </c>
-      <c r="S1" t="s">
-        <v>6</v>
-      </c>
-      <c r="T1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U1" t="s">
-        <v>8</v>
-      </c>
-      <c r="V1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1004,43 +976,31 @@
         <v>6</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2010</v>
       </c>
       <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>30</v>
-      </c>
-      <c r="S2">
-        <v>1010</v>
-      </c>
-      <c r="T2">
-        <v>2010</v>
-      </c>
-      <c r="U2">
-        <v>100</v>
-      </c>
-      <c r="V2" t="s">
+        <v>100</v>
+      </c>
+      <c r="R2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>10</v>
       </c>
@@ -1069,46 +1029,34 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L3">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="M3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N3">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="O3">
-        <v>38</v>
+        <v>1010</v>
       </c>
       <c r="P3">
-        <v>14</v>
+        <v>2010</v>
       </c>
       <c r="Q3">
-        <v>36</v>
-      </c>
-      <c r="R3">
-        <v>30</v>
-      </c>
-      <c r="S3">
-        <v>1010</v>
-      </c>
-      <c r="T3">
-        <v>2010</v>
-      </c>
-      <c r="U3">
-        <v>100</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>20</v>
       </c>
@@ -1137,46 +1085,34 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="N4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O4">
-        <v>38</v>
+        <v>1010</v>
       </c>
       <c r="P4">
-        <v>14</v>
+        <v>2010</v>
       </c>
       <c r="Q4">
-        <v>36</v>
-      </c>
-      <c r="R4">
-        <v>30</v>
-      </c>
-      <c r="S4">
-        <v>1010</v>
-      </c>
-      <c r="T4">
-        <v>2010</v>
-      </c>
-      <c r="U4">
-        <v>100</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1010</v>
       </c>
@@ -1208,43 +1144,31 @@
         <v>16</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="O5">
-        <v>6</v>
+        <v>1010</v>
       </c>
       <c r="P5">
-        <v>4</v>
+        <v>2010</v>
       </c>
       <c r="Q5">
-        <v>4</v>
-      </c>
-      <c r="R5">
-        <v>30</v>
-      </c>
-      <c r="S5">
-        <v>1010</v>
-      </c>
-      <c r="T5">
-        <v>2010</v>
-      </c>
-      <c r="U5">
-        <v>100</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1020</v>
       </c>
@@ -1276,43 +1200,31 @@
         <v>20</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="O6">
-        <v>6</v>
+        <v>1010</v>
       </c>
       <c r="P6">
-        <v>10</v>
+        <v>2010</v>
       </c>
       <c r="Q6">
-        <v>4</v>
-      </c>
-      <c r="R6">
-        <v>30</v>
-      </c>
-      <c r="S6">
-        <v>1010</v>
-      </c>
-      <c r="T6">
-        <v>2010</v>
-      </c>
-      <c r="U6">
-        <v>100</v>
-      </c>
-      <c r="V6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1030</v>
       </c>
@@ -1344,39 +1256,27 @@
         <v>20</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="O7">
-        <v>6</v>
+        <v>1010</v>
       </c>
       <c r="P7">
-        <v>10</v>
+        <v>2010</v>
       </c>
       <c r="Q7">
-        <v>4</v>
-      </c>
-      <c r="R7">
-        <v>30</v>
-      </c>
-      <c r="S7">
-        <v>1010</v>
-      </c>
-      <c r="T7">
-        <v>2010</v>
-      </c>
-      <c r="U7">
-        <v>100</v>
-      </c>
-      <c r="V7" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="R7" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4187,19 +4087,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -4324,10 +4224,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -4336,10 +4236,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D4" s="1"/>
     </row>
@@ -4348,10 +4248,10 @@
         <v>1010</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D5" s="1"/>
     </row>
@@ -4360,10 +4260,10 @@
         <v>1020</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D6" s="1"/>
     </row>
@@ -4372,10 +4272,10 @@
         <v>1030</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -4384,10 +4284,10 @@
         <v>10010</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D8" s="1"/>
     </row>
@@ -4461,7 +4361,7 @@
         <v>0</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -4493,10 +4393,10 @@
         <v>10</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
@@ -4528,10 +4428,10 @@
         <v>20</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="39" x14ac:dyDescent="0.2">
@@ -4539,7 +4439,7 @@
         <v>1010</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -4563,10 +4463,10 @@
         <v>30</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -4586,16 +4486,16 @@
         <v>30</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -4615,16 +4515,16 @@
         <v>40</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="39" x14ac:dyDescent="0.2">
@@ -4650,10 +4550,10 @@
         <v>60</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -4679,10 +4579,10 @@
         <v>70</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -4708,10 +4608,10 @@
         <v>80</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -4751,7 +4651,7 @@
         <v>90</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -4889,7 +4789,7 @@
         <v>1010</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="4:5" x14ac:dyDescent="0.2">
@@ -4897,7 +4797,7 @@
         <v>1011</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E569B1F7-97FE-4CE0-820C-74B977895EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="802" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -23,23 +17,12 @@
     <sheet name="TextData" sheetId="5" r:id="rId8"/>
     <sheet name="Define" sheetId="6" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="119">
   <si>
     <t>Id</t>
   </si>
@@ -50,12 +33,36 @@
     <t>StageNo</t>
   </si>
   <si>
+    <t>AchieveType</t>
+  </si>
+  <si>
+    <t>AchieveTextId</t>
+  </si>
+  <si>
+    <t>EnemyBasementId</t>
+  </si>
+  <si>
     <t>Selectable</t>
   </si>
   <si>
     <t>StageLv</t>
   </si>
   <si>
+    <t>PartyMemberIds</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>InitX</t>
+  </si>
+  <si>
+    <t>InitY</t>
+  </si>
+  <si>
     <t>RandomTroopWeight</t>
   </si>
   <si>
@@ -71,7 +78,7 @@
     <t>BackGround</t>
   </si>
   <si>
-    <t>-</t>
+    <t>NA_background image_3D like_894</t>
   </si>
   <si>
     <t>Turns</t>
@@ -80,46 +87,73 @@
     <t>Timing</t>
   </si>
   <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Param</t>
+  </si>
+  <si>
+    <t>ReadFlag</t>
+  </si>
+  <si>
+    <t>StageId</t>
+  </si>
+  <si>
+    <t>UnitType</t>
+  </si>
+  <si>
+    <t>InitTeamId</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
+    <t>Param1</t>
+  </si>
+  <si>
+    <t>Param2</t>
+  </si>
+  <si>
+    <t>PrizeSetId</t>
+  </si>
+  <si>
+    <t>ClearCount</t>
+  </si>
+  <si>
+    <t>MoveType</t>
+  </si>
+  <si>
+    <t>MoveParam</t>
+  </si>
+  <si>
+    <t>Seek=-1でステージ開始時に入手</t>
+  </si>
+  <si>
+    <t>EnemyId</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>GroupId</t>
+  </si>
+  <si>
+    <t>SymbolType</t>
+  </si>
+  <si>
     <t>_</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Param</t>
-  </si>
-  <si>
-    <t>ReadFlag</t>
-  </si>
-  <si>
-    <t>SymbolType</t>
-  </si>
-  <si>
-    <t>Rate</t>
-  </si>
-  <si>
-    <t>Param1</t>
-  </si>
-  <si>
-    <t>Param2</t>
-  </si>
-  <si>
-    <t>PrizeSetId</t>
-  </si>
-  <si>
-    <t>ClearCount</t>
-  </si>
-  <si>
-    <t>Seek=-1でステージ開始時に入手</t>
-  </si>
-  <si>
-    <t>EnemyId</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>GroupId</t>
+    <t>SymbolId</t>
+  </si>
+  <si>
+    <t>Param3</t>
+  </si>
+  <si>
+    <t>Param4</t>
   </si>
   <si>
     <t>SceneType</t>
@@ -131,19 +165,34 @@
     <t>Y</t>
   </si>
   <si>
-    <t>Width</t>
-  </si>
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
     <t>Text</t>
   </si>
   <si>
     <t>Help</t>
   </si>
   <si>
-    <t>ダミー</t>
+    <t>準備画面</t>
+  </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
+    <t>ステージ1</t>
+  </si>
+  <si>
+    <t>ステージ2</t>
+  </si>
+  <si>
+    <t>ゲームの流れ</t>
+  </si>
+  <si>
+    <t>有利なバトルの進め方</t>
+  </si>
+  <si>
+    <t>ユニットの強化</t>
+  </si>
+  <si>
+    <t>敵拠点を制圧する</t>
   </si>
   <si>
     <t>なし</t>
@@ -152,12 +201,24 @@
     <t>Random</t>
   </si>
   <si>
+    <t>固定</t>
+  </si>
+  <si>
     <t>Tactics開始(UI表示前)</t>
   </si>
   <si>
     <t>コマンドを制限する</t>
   </si>
   <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>進撃</t>
+  </si>
+  <si>
+    <t>近くにいる敵に向かって移動し、射程に捉えれば攻撃してくる。</t>
+  </si>
+  <si>
     <t>Battle勝利後</t>
   </si>
   <si>
@@ -167,377 +228,173 @@
     <t>Battle</t>
   </si>
   <si>
+    <t>Boss</t>
+  </si>
+  <si>
+    <t>迎撃</t>
+  </si>
+  <si>
+    <t>射程内に攻撃可能な敵がいれば攻撃、いなければその場で待機。</t>
+  </si>
+  <si>
+    <t>チュートリアル開始</t>
+  </si>
+  <si>
     <t>全員コマンドを選ばないと進まない</t>
   </si>
   <si>
-    <t>Boss</t>
-  </si>
-  <si>
-    <t>隷従属度フラグを管理</t>
-  </si>
-  <si>
-    <t>Event</t>
-  </si>
-  <si>
-    <t>アルカナフラグを管理</t>
-  </si>
-  <si>
-    <t>Alcana</t>
-  </si>
-  <si>
-    <t>仲間を選んで加入する</t>
-  </si>
-  <si>
-    <t>Actor</t>
-  </si>
-  <si>
-    <t>セーブを行う</t>
-  </si>
-  <si>
-    <t>Resource</t>
-  </si>
-  <si>
-    <t>ボスの選択番号を設定する</t>
-  </si>
-  <si>
-    <t>Rebirth</t>
-  </si>
-  <si>
-    <t>SPを消費しないと進まない</t>
-  </si>
-  <si>
-    <t>SelectActor</t>
-  </si>
-  <si>
-    <t>IDにActorIDを加算してADV再生</t>
-  </si>
-  <si>
-    <t>Shop</t>
-  </si>
-  <si>
-    <t>ルート分岐イベント</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>ルート分岐パラメータ設定</t>
-  </si>
-  <si>
-    <t>ルート分岐ステージ移動</t>
-  </si>
-  <si>
-    <t>ステージクリア</t>
-  </si>
-  <si>
-    <t>ルート分岐でステージに移動</t>
-  </si>
-  <si>
-    <t>ルート分岐敵グループを生成</t>
-  </si>
-  <si>
-    <t>表示残りターンをマスターから取得</t>
-  </si>
-  <si>
-    <t>継承スキル演出開始</t>
-  </si>
-  <si>
-    <t>ステージ移動</t>
-  </si>
-  <si>
-    <t>中ボスを設置する(コマンド制限判定あり)</t>
-  </si>
-  <si>
-    <t>上位者ボスを設置する(コマンド制限判定あり)</t>
-  </si>
-  <si>
-    <t>ADV再生</t>
-  </si>
-  <si>
-    <t>今のステージシンボルの〇SeekIndexのバトルを開始</t>
-  </si>
-  <si>
-    <t>サバイバルモードにする</t>
-  </si>
-  <si>
-    <t>*</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>NA_background image_3D like_894</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Width</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Height</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>InitX</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>InitY</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>PartyMemberIds</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>UnitType</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Battler</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Basement</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>StageId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Id</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MoveType</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MoveParam</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>InitTeamId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ステージ1</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>""</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ゲームの流れ</t>
-    <rPh sb="4" eb="5">
-      <t>ナガ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>チュートリアル開始</t>
-    <rPh sb="7" eb="9">
-      <t>カイシ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ターン終了コマンド操作有効</t>
-    <rPh sb="3" eb="5">
-      <t>シュウリョウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ユウコウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ターン終了コマンド操作無効</t>
-    <rPh sb="3" eb="5">
-      <t>シュウリョウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ムコウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>AchieveTextId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>AchieveType</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>EnemyBasementId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>有利なバトルの進め方</t>
-    <rPh sb="0" eb="2">
-      <t>ユウリ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>スス</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>カタ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>NA_background image_3D like_894</t>
-  </si>
-  <si>
-    <t>敵拠点を制圧する</t>
-    <rPh sb="0" eb="1">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>キョテン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>セイアツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Alcana</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ユニットの強化</t>
-    <rPh sb="5" eb="7">
-      <t>キョウカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>GetItem</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>進撃</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>近くにいる敵に向かって移動し、射程に捉えれば攻撃してくる。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>固定</t>
-    <rPh sb="0" eb="2">
-      <t>コテイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>迎撃</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>射程内に攻撃可能な敵がいれば攻撃、いなければその場で待機。</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>警戒</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>射程内に攻撃可能な敵がいれば攻撃、
 いない場合は敵の射程に入っていれば射程外へ逃げる、入っていなければその場で待機。</t>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>隷従属度フラグを管理</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>Alcana</t>
   </si>
   <si>
     <t>徘徊</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ランダムに移動。</t>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルカナフラグを管理</t>
+  </si>
+  <si>
+    <t>GetItem</t>
   </si>
   <si>
     <t>巡回</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>射程内に攻撃可能な敵がいれば攻撃、いなければ一定のルートを移動。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>SymbolId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Param1</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Param2</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Param3</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Param4</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>固定</t>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仲間を選んで加入する</t>
+  </si>
+  <si>
+    <t>Actor</t>
+  </si>
+  <si>
+    <t>Resource</t>
   </si>
   <si>
     <t>その場を動かない。
 その場から攻撃可能なら攻撃する。
 隣接など攻撃可能でないと挑発は出来ない。</t>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>セーブを行う</t>
+  </si>
+  <si>
+    <t>Rebirth</t>
   </si>
   <si>
     <t>移動</t>
-    <rPh sb="0" eb="2">
-      <t>イドウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>特定の目標に向かって移動。攻撃してこない。</t>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ボスの選択番号を設定する</t>
+  </si>
+  <si>
+    <t>SelectActor</t>
   </si>
   <si>
     <t>離脱</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>離脱ポイントへ向かう。攻撃してこない。</t>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SPを消費しないと進まない</t>
+  </si>
+  <si>
+    <t>Shop</t>
+  </si>
+  <si>
+    <t>IDにActorIDを加算してADV再生</t>
   </si>
   <si>
     <t>Gacha</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ステージ2</t>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ルート分岐イベント</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>ルート分岐パラメータ設定</t>
+  </si>
+  <si>
+    <t>Battler</t>
+  </si>
+  <si>
+    <t>ルート分岐ステージ移動</t>
+  </si>
+  <si>
+    <t>ステージクリア</t>
+  </si>
+  <si>
+    <t>ルート分岐でステージに移動</t>
+  </si>
+  <si>
+    <t>ルート分岐敵グループを生成</t>
+  </si>
+  <si>
+    <t>表示残りターンをマスターから取得</t>
+  </si>
+  <si>
+    <t>継承スキル演出開始</t>
+  </si>
+  <si>
+    <t>ステージ移動</t>
+  </si>
+  <si>
+    <t>中ボスを設置する(コマンド制限判定あり)</t>
+  </si>
+  <si>
+    <t>上位者ボスを設置する(コマンド制限判定あり)</t>
+  </si>
+  <si>
+    <t>ADV再生</t>
+  </si>
+  <si>
+    <t>今のステージシンボルの〇SeekIndexのバトルを開始</t>
+  </si>
+  <si>
+    <t>サバイバルモードにする</t>
+  </si>
+  <si>
+    <t>ターン終了コマンド操作有効</t>
+  </si>
+  <si>
+    <t>ターン終了コマンド操作無効</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -549,33 +406,354 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -583,9 +761,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -593,30 +1013,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
+    <cellStyle name="入力" xfId="2" builtinId="20"/>
+    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
+    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
+    <cellStyle name="通貨" xfId="6" builtinId="4"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="良い" xfId="13" builtinId="26"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11"/>
+    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
+    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
+    <cellStyle name="説明文" xfId="17" builtinId="53"/>
+    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
+    <cellStyle name="出力" xfId="19" builtinId="21"/>
+    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
+    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
+    <cellStyle name="計算" xfId="22" builtinId="22"/>
+    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
+    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
+    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
+    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
+    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
+    <cellStyle name="集計" xfId="28" builtinId="25"/>
+    <cellStyle name="悪い" xfId="29" builtinId="27"/>
+    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
+    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
+    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
+    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
+    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
+    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
+    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
+    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
+    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
+    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
+    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -874,21 +1338,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:R7"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="6"/>
   <cols>
-    <col min="5" max="6" width="8.453125" customWidth="1"/>
-    <col min="7" max="7" width="10.36328125" customWidth="1"/>
+    <col min="5" max="6" width="8.45454545454546" customWidth="1"/>
+    <col min="7" max="7" width="10.3636363636364" customWidth="1"/>
     <col min="18" max="18" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -898,55 +1362,55 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>97</v>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>78</v>
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -955,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>10010</v>
@@ -973,16 +1437,16 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N2">
         <v>30</v>
@@ -996,11 +1460,11 @@
       <c r="Q2">
         <v>100</v>
       </c>
-      <c r="R2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>10</v>
       </c>
@@ -1052,11 +1516,11 @@
       <c r="Q3">
         <v>100</v>
       </c>
-      <c r="R3" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>20</v>
       </c>
@@ -1108,11 +1572,11 @@
       <c r="Q4">
         <v>100</v>
       </c>
-      <c r="R4" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>1010</v>
       </c>
@@ -1164,11 +1628,11 @@
       <c r="Q5">
         <v>100</v>
       </c>
-      <c r="R5" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>1020</v>
       </c>
@@ -1220,11 +1684,11 @@
       <c r="Q6">
         <v>100</v>
       </c>
-      <c r="R6" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>1030</v>
       </c>
@@ -1276,52 +1740,53 @@
       <c r="Q7">
         <v>100</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>74</v>
+      <c r="R7" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="4" outlineLevelCol="7"/>
   <cols>
-    <col min="4" max="4" width="22.08984375" customWidth="1"/>
-    <col min="6" max="6" width="18.36328125" customWidth="1"/>
+    <col min="4" max="4" width="22.0909090909091" customWidth="1"/>
+    <col min="6" max="6" width="18.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>73</v>
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>73</v>
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1010</v>
       </c>
@@ -1341,7 +1806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>1010</v>
       </c>
@@ -1361,7 +1826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>1010</v>
       </c>
@@ -1381,7 +1846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>1010</v>
       </c>
@@ -1402,61 +1867,62 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O48"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>88</v>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="H1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>1000</v>
       </c>
@@ -1501,10 +1967,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>1010</v>
       </c>
@@ -1549,7 +2015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>1020</v>
       </c>
@@ -1594,7 +2060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>1030</v>
       </c>
@@ -1639,7 +2105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>1040</v>
       </c>
@@ -1684,7 +2150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>1050</v>
       </c>
@@ -1729,7 +2195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>10000</v>
       </c>
@@ -1774,10 +2240,10 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>10010</v>
       </c>
@@ -1822,7 +2288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>10020</v>
       </c>
@@ -1867,7 +2333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>10030</v>
       </c>
@@ -1912,7 +2378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>10040</v>
       </c>
@@ -1957,7 +2423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14">
       <c r="A13">
         <v>10050</v>
       </c>
@@ -2002,7 +2468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14">
       <c r="A14">
         <v>10060</v>
       </c>
@@ -2047,7 +2513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14">
       <c r="A15">
         <v>10070</v>
       </c>
@@ -2092,7 +2558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15">
       <c r="A16">
         <v>11000</v>
       </c>
@@ -2137,10 +2603,10 @@
         <v>0</v>
       </c>
       <c r="O16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17">
         <v>11010</v>
       </c>
@@ -2185,10 +2651,10 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18">
         <v>10020</v>
       </c>
@@ -2233,7 +2699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14">
       <c r="A19">
         <v>10030</v>
       </c>
@@ -2278,7 +2744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14">
       <c r="A20">
         <v>10040</v>
       </c>
@@ -2323,7 +2789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14">
       <c r="A21">
         <v>10050</v>
       </c>
@@ -2368,7 +2834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14">
       <c r="A22">
         <v>10060</v>
       </c>
@@ -2413,7 +2879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14">
       <c r="A23">
         <v>10070</v>
       </c>
@@ -2458,7 +2924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14">
       <c r="A24">
         <v>11020</v>
       </c>
@@ -2503,7 +2969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14">
       <c r="A25">
         <v>11030</v>
       </c>
@@ -2548,7 +3014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14">
       <c r="A26">
         <v>11040</v>
       </c>
@@ -2593,7 +3059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14">
       <c r="A27">
         <v>11050</v>
       </c>
@@ -2638,7 +3104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14">
       <c r="A28">
         <v>11060</v>
       </c>
@@ -2683,7 +3149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14">
       <c r="A29">
         <v>11070</v>
       </c>
@@ -2728,7 +3194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14">
       <c r="A30">
         <v>11080</v>
       </c>
@@ -2773,7 +3239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14">
       <c r="A31">
         <v>11090</v>
       </c>
@@ -2818,7 +3284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15">
       <c r="A32">
         <v>11000</v>
       </c>
@@ -2863,10 +3329,10 @@
         <v>0</v>
       </c>
       <c r="O32" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33">
         <v>11010</v>
       </c>
@@ -2911,10 +3377,10 @@
         <v>0</v>
       </c>
       <c r="O33" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34">
         <v>10020</v>
       </c>
@@ -2959,7 +3425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14">
       <c r="A35">
         <v>10030</v>
       </c>
@@ -3004,7 +3470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14">
       <c r="A36">
         <v>10040</v>
       </c>
@@ -3049,7 +3515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14">
       <c r="A37">
         <v>10050</v>
       </c>
@@ -3094,7 +3560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14">
       <c r="A38">
         <v>10060</v>
       </c>
@@ -3139,7 +3605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14">
       <c r="A39">
         <v>10070</v>
       </c>
@@ -3184,7 +3650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14">
       <c r="A40">
         <v>10080</v>
       </c>
@@ -3229,7 +3695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14">
       <c r="A41">
         <v>11020</v>
       </c>
@@ -3274,7 +3740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14">
       <c r="A42">
         <v>11030</v>
       </c>
@@ -3319,7 +3785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14">
       <c r="A43">
         <v>11040</v>
       </c>
@@ -3364,7 +3830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14">
       <c r="A44">
         <v>11050</v>
       </c>
@@ -3409,7 +3875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14">
       <c r="A45">
         <v>11060</v>
       </c>
@@ -3454,7 +3920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14">
       <c r="A46">
         <v>11070</v>
       </c>
@@ -3499,7 +3965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14">
       <c r="A47">
         <v>11080</v>
       </c>
@@ -3544,7 +4010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14">
       <c r="A48">
         <v>11090</v>
       </c>
@@ -3590,28 +4056,29 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="6" outlineLevelCol="2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>10</v>
       </c>
@@ -3622,7 +4089,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>10</v>
       </c>
@@ -3633,7 +4100,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>10</v>
       </c>
@@ -3644,7 +4111,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>10</v>
       </c>
@@ -3655,7 +4122,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>10</v>
       </c>
@@ -3666,7 +4133,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>10</v>
       </c>
@@ -3678,43 +4145,44 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="11.90625" customWidth="1"/>
+    <col min="2" max="2" width="11.9090909090909" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>201</v>
       </c>
@@ -3738,7 +4206,7 @@
         <v>11020</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>201</v>
       </c>
@@ -3762,7 +4230,7 @@
         <v>11030</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>201</v>
       </c>
@@ -3786,7 +4254,7 @@
         <v>11040</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>202</v>
       </c>
@@ -3810,7 +4278,7 @@
         <v>12020</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>202</v>
       </c>
@@ -3834,7 +4302,7 @@
         <v>12030</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>202</v>
       </c>
@@ -3858,7 +4326,7 @@
         <v>12040</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>203</v>
       </c>
@@ -3882,7 +4350,7 @@
         <v>13020</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>203</v>
       </c>
@@ -3906,7 +4374,7 @@
         <v>13030</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>203</v>
       </c>
@@ -3930,7 +4398,7 @@
         <v>13040</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>204</v>
       </c>
@@ -3954,7 +4422,7 @@
         <v>14010</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>204</v>
       </c>
@@ -3978,7 +4446,7 @@
         <v>14020</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>204</v>
       </c>
@@ -4002,7 +4470,7 @@
         <v>14030</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>205</v>
       </c>
@@ -4026,7 +4494,7 @@
         <v>15020</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>205</v>
       </c>
@@ -4050,7 +4518,7 @@
         <v>15030</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>205</v>
       </c>
@@ -4075,34 +4543,35 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38DF549-830A-441A-B02B-F6F6904091C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="1" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>11090</v>
       </c>
@@ -4120,43 +4589,44 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1" outlineLevelCol="7"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="G1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1010</v>
       </c>
@@ -4183,625 +4653,627 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="34.1796875" customWidth="1"/>
-    <col min="3" max="3" width="29.1796875" customWidth="1"/>
+    <col min="2" max="2" width="34.1818181818182" customWidth="1"/>
+    <col min="3" max="3" width="29.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>1010</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>91</v>
+      <c r="B5" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>1020</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>98</v>
+      <c r="B6" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>1030</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>102</v>
+      <c r="B7" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>10010</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>100</v>
+      <c r="B8" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C11" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="3:4">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O28"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
-    <col min="15" max="15" width="45.90625" customWidth="1"/>
+    <col min="15" max="15" width="45.9090909090909" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>83</v>
+      <c r="J3" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>83</v>
+      <c r="L3" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="39" x14ac:dyDescent="0.2">
+      <c r="N4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" ht="39" spans="1:15">
       <c r="A5">
         <v>1010</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>92</v>
+      <c r="B5" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>82</v>
+      <c r="L5" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="M5">
         <v>30</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="4:15">
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>101</v>
+      <c r="L6" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
-      <c r="N6" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="4:15">
       <c r="D7">
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>103</v>
+      <c r="L7" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="39" x14ac:dyDescent="0.2">
+      <c r="N7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" ht="39" spans="4:15">
       <c r="D8">
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="4:15">
       <c r="D9">
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="M9">
         <v>70</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="4:15">
       <c r="D10">
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
-      <c r="N10" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="4:12">
       <c r="D11">
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="4:12">
       <c r="D12">
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="K12">
         <v>90</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="L12" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="4:12">
       <c r="D13">
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="4:12">
       <c r="D14">
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="K14">
         <v>1000</v>
       </c>
-      <c r="L14" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="L14" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="4:5">
       <c r="D15">
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="4:5">
       <c r="D16">
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5">
       <c r="D17">
         <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="4:5">
       <c r="D18">
         <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="4:5">
       <c r="D19">
         <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="4:5">
       <c r="D20">
         <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="4:5">
       <c r="D21">
         <v>51</v>
       </c>
       <c r="E21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="4:5" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="4:5">
       <c r="D22">
         <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="4:5" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="4:5">
       <c r="D23">
         <v>62</v>
       </c>
       <c r="E23" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" spans="4:5" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="4:5">
       <c r="D24">
         <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="4:5" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="4:5">
       <c r="D25">
         <v>110</v>
       </c>
       <c r="E25" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="4:5" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="4:5">
       <c r="D26">
         <v>201</v>
       </c>
       <c r="E26" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="4:5" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="4:5">
       <c r="D27">
         <v>1010</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="28" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="E27" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="4:5">
       <c r="D28">
         <v>1011</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>94</v>
+      <c r="E28" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" firstSheet="2"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -389,10 +389,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -415,8 +415,30 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -430,7 +452,69 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -445,7 +529,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -453,62 +537,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -521,41 +552,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -568,7 +568,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,175 +748,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -762,17 +762,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -807,29 +803,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -851,10 +835,26 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -867,145 +867,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1537,7 +1537,7 @@
         <v>10010</v>
       </c>
       <c r="F4">
-        <v>1050</v>
+        <v>2020</v>
       </c>
       <c r="G4">
         <v>1</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -389,10 +389,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -415,7 +415,36 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -424,7 +453,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -438,23 +491,24 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -467,23 +521,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -499,63 +546,16 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -574,7 +574,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,169 +748,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,17 +759,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -789,6 +778,30 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -803,17 +816,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -835,26 +851,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -867,16 +867,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -885,127 +885,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L5">
         <v>4</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -389,10 +389,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -416,37 +416,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -459,11 +436,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -484,6 +460,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -492,13 +475,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -521,6 +497,22 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -529,10 +521,18 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -574,7 +574,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,103 +700,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,7 +712,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -706,49 +748,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,6 +759,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -773,6 +782,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -797,30 +821,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -867,16 +867,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -885,127 +885,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1499,10 +1499,10 @@
         <v>40</v>
       </c>
       <c r="L3">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="N3">
         <v>30</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="K5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L5">
         <v>4</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -389,10 +389,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -415,10 +415,11 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -429,13 +430,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -443,9 +438,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -460,7 +477,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -473,24 +513,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -506,25 +538,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -536,24 +552,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -574,37 +574,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -616,43 +592,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -670,37 +628,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -718,13 +664,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -736,19 +706,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,15 +759,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -786,17 +777,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -819,17 +815,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -851,11 +853,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -867,16 +867,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -885,127 +885,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1499,10 +1499,10 @@
         <v>40</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3">
         <v>30</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="119">
   <si>
     <t>Id</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t>MoveParam</t>
+  </si>
+  <si>
+    <t>Seek=-1でステージ開始時に入手</t>
   </si>
   <si>
     <t>EnemyId</t>
@@ -386,10 +389,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -412,6 +415,7 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -419,9 +423,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -436,36 +446,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -486,9 +475,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -502,8 +504,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -511,7 +514,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -526,10 +529,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -549,10 +552,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -565,25 +568,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -595,7 +580,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -607,61 +658,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -673,13 +670,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,6 +688,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -709,43 +742,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -756,6 +759,17 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -770,21 +784,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -822,26 +821,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -856,6 +835,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -864,145 +867,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1928,8 +1931,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
@@ -1973,6 +1976,294 @@
       </c>
       <c r="N1" s="1" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2">
+        <v>1000</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>-1</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>70</v>
+      </c>
+      <c r="F2" t="str">
+        <f>INDEX(Define!L:L,MATCH(E2,Define!K:K))</f>
+        <v>SelectActor</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>100</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>1001</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3">
+        <v>1000</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>-1</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>70</v>
+      </c>
+      <c r="F3" t="str">
+        <f>INDEX(Define!L:L,MATCH(E3,Define!K:K))</f>
+        <v>SelectActor</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>1002</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4">
+        <v>1000</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>-1</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>70</v>
+      </c>
+      <c r="F4" t="str">
+        <f>INDEX(Define!L:L,MATCH(E4,Define!K:K))</f>
+        <v>SelectActor</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>1003</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5">
+        <v>1000</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>-1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>70</v>
+      </c>
+      <c r="F5" t="str">
+        <f>INDEX(Define!L:L,MATCH(E5,Define!K:K))</f>
+        <v>SelectActor</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>1004</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6">
+        <v>1000</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>-1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>70</v>
+      </c>
+      <c r="F6" t="str">
+        <f>INDEX(Define!L:L,MATCH(E6,Define!K:K))</f>
+        <v>SelectActor</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1005</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>-1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>70</v>
+      </c>
+      <c r="F7" t="str">
+        <f>INDEX(Define!L:L,MATCH(E7,Define!K:K))</f>
+        <v>SelectActor</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1006</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1992,10 +2283,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2081,13 +2372,13 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
         <v>28</v>
@@ -2476,7 +2767,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>29</v>
@@ -2485,10 +2776,10 @@
         <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2531,13 +2822,13 @@
         <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" t="s">
         <v>9</v>
@@ -2593,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2604,10 +2895,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2615,10 +2906,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -2627,10 +2918,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -2639,10 +2930,10 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -2651,10 +2942,10 @@
         <v>1020</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -2663,10 +2954,10 @@
         <v>1030</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="3"/>
     </row>
@@ -2675,10 +2966,10 @@
         <v>10010</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="3"/>
     </row>
@@ -2715,7 +3006,7 @@
         <v>22</v>
       </c>
       <c r="I1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>26</v>
@@ -2729,31 +3020,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -2761,34 +3052,34 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -2796,34 +3087,34 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:15">
@@ -2831,34 +3122,34 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M5">
         <v>30</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="4:15">
@@ -2866,28 +3157,28 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="4:15">
@@ -2895,28 +3186,28 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" ht="39" spans="4:15">
@@ -2924,28 +3215,28 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="4:15">
@@ -2953,28 +3244,28 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M9">
         <v>70</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="4:15">
@@ -2982,28 +3273,28 @@
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="4:12">
@@ -3011,19 +3302,19 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="4:12">
@@ -3031,19 +3322,19 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K12">
         <v>90</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="4:12">
@@ -3051,19 +3342,19 @@
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="4:12">
@@ -3071,13 +3362,13 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K14">
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="4:5">
@@ -3085,7 +3376,7 @@
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="4:5">
@@ -3093,7 +3384,7 @@
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="4:5">
@@ -3101,7 +3392,7 @@
         <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="4:5">
@@ -3109,7 +3400,7 @@
         <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="4:5">
@@ -3117,7 +3408,7 @@
         <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="4:5">
@@ -3125,7 +3416,7 @@
         <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="4:5">
@@ -3133,7 +3424,7 @@
         <v>51</v>
       </c>
       <c r="E21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="4:5">
@@ -3141,7 +3432,7 @@
         <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="4:5">
@@ -3149,7 +3440,7 @@
         <v>62</v>
       </c>
       <c r="E23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="4:5">
@@ -3157,7 +3448,7 @@
         <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="4:5">
@@ -3165,7 +3456,7 @@
         <v>110</v>
       </c>
       <c r="E25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="4:5">
@@ -3173,7 +3464,7 @@
         <v>201</v>
       </c>
       <c r="E26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="4:5">
@@ -3181,7 +3472,7 @@
         <v>1010</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="4:5">
@@ -3189,7 +3480,7 @@
         <v>1011</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="119">
   <si>
     <t>Id</t>
   </si>
@@ -389,10 +389,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -415,9 +415,15 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -425,13 +431,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -445,13 +444,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -460,11 +452,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -482,6 +473,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -490,7 +482,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -536,8 +528,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -545,15 +546,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -568,7 +568,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,19 +580,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,7 +616,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -616,13 +628,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -640,37 +670,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,31 +688,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -724,19 +724,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -748,7 +736,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,17 +759,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -799,15 +788,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -845,6 +825,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -859,6 +848,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -867,145 +867,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1931,8 +1931,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O7"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="6"/>
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="5"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
@@ -2215,54 +2215,6 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7">
-        <v>1000</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>-1</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>70</v>
-      </c>
-      <c r="F7" t="str">
-        <f>INDEX(Define!L:L,MATCH(E7,Define!K:K))</f>
-        <v>SelectActor</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>100</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>1006</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
         <v>35</v>
       </c>
     </row>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="121">
   <si>
     <t>Id</t>
   </si>
@@ -81,79 +81,85 @@
     <t>NA_background image_3D like_894</t>
   </si>
   <si>
+    <t>PositionX</t>
+  </si>
+  <si>
+    <t>PositionY</t>
+  </si>
+  <si>
+    <t>Timing</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Param</t>
+  </si>
+  <si>
+    <t>ReadFlag</t>
+  </si>
+  <si>
+    <t>StageId</t>
+  </si>
+  <si>
+    <t>UnitType</t>
+  </si>
+  <si>
+    <t>InitTeamId</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
+    <t>Param1</t>
+  </si>
+  <si>
+    <t>Param2</t>
+  </si>
+  <si>
+    <t>PrizeSetId</t>
+  </si>
+  <si>
+    <t>ClearCount</t>
+  </si>
+  <si>
+    <t>MoveType</t>
+  </si>
+  <si>
+    <t>MoveParam</t>
+  </si>
+  <si>
+    <t>Seek=-1でステージ開始時に入手</t>
+  </si>
+  <si>
+    <t>EnemyId</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>GroupId</t>
+  </si>
+  <si>
+    <t>SymbolType</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
+  <si>
+    <t>SymbolId</t>
+  </si>
+  <si>
+    <t>Param3</t>
+  </si>
+  <si>
+    <t>Param4</t>
+  </si>
+  <si>
     <t>Turns</t>
-  </si>
-  <si>
-    <t>Timing</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Param</t>
-  </si>
-  <si>
-    <t>ReadFlag</t>
-  </si>
-  <si>
-    <t>StageId</t>
-  </si>
-  <si>
-    <t>UnitType</t>
-  </si>
-  <si>
-    <t>InitTeamId</t>
-  </si>
-  <si>
-    <t>Rate</t>
-  </si>
-  <si>
-    <t>Param1</t>
-  </si>
-  <si>
-    <t>Param2</t>
-  </si>
-  <si>
-    <t>PrizeSetId</t>
-  </si>
-  <si>
-    <t>ClearCount</t>
-  </si>
-  <si>
-    <t>MoveType</t>
-  </si>
-  <si>
-    <t>MoveParam</t>
-  </si>
-  <si>
-    <t>Seek=-1でステージ開始時に入手</t>
-  </si>
-  <si>
-    <t>EnemyId</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>GroupId</t>
-  </si>
-  <si>
-    <t>SymbolType</t>
-  </si>
-  <si>
-    <t>_</t>
-  </si>
-  <si>
-    <t>SymbolId</t>
-  </si>
-  <si>
-    <t>Param3</t>
-  </si>
-  <si>
-    <t>Param4</t>
   </si>
   <si>
     <t>SceneType</t>
@@ -389,8 +395,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -423,51 +429,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -481,15 +443,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -505,6 +460,22 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -512,19 +483,48 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -536,19 +536,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -568,7 +574,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,7 +664,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -592,85 +718,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,55 +742,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -742,13 +754,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -777,26 +783,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -812,24 +814,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -851,11 +835,33 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -867,7 +873,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -876,7 +882,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -885,127 +891,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1809,14 +1815,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="4" outlineLevelCol="7"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1"/>
   <cols>
-    <col min="4" max="4" width="22.0909090909091" customWidth="1"/>
-    <col min="6" max="6" width="18.3636363636364" customWidth="1"/>
+    <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
+    <col min="7" max="7" width="18.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1826,99 +1832,45 @@
       <c r="C1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="F1" t="s">
         <v>23</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="H1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1010</v>
-      </c>
-      <c r="E2">
-        <v>1011</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3">
-        <v>1010</v>
-      </c>
-      <c r="B3">
+      <c r="D2">
+        <v>3010</v>
+      </c>
+      <c r="F2">
+        <v>4010</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>1010</v>
-      </c>
-      <c r="E3">
-        <v>1010</v>
-      </c>
-      <c r="G3">
-        <v>400</v>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4">
-        <v>1010</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1010</v>
-      </c>
-      <c r="E4">
-        <v>1011</v>
-      </c>
-      <c r="G4">
-        <v>500</v>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5">
-        <v>1010</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1010</v>
-      </c>
-      <c r="E5">
-        <v>1010</v>
-      </c>
-      <c r="G5">
-        <v>600</v>
-      </c>
-      <c r="H5" t="b">
+      <c r="I2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1939,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
@@ -1948,34 +1900,34 @@
         <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -2023,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -2071,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -2119,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -2167,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -2215,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2235,10 +2187,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2324,25 +2276,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2719,19 +2671,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2768,19 +2720,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G1" t="s">
         <v>9</v>
@@ -2836,10 +2788,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2847,10 +2799,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2858,10 +2810,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -2870,10 +2822,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -2882,10 +2834,10 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -2894,10 +2846,10 @@
         <v>1020</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -2906,10 +2858,10 @@
         <v>1030</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" s="3"/>
     </row>
@@ -2918,10 +2870,10 @@
         <v>10010</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8" s="3"/>
     </row>
@@ -2952,19 +2904,19 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2972,31 +2924,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -3004,34 +2956,34 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -3039,34 +2991,34 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:15">
@@ -3074,34 +3026,34 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M5">
         <v>30</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="4:15">
@@ -3109,28 +3061,28 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="4:15">
@@ -3138,28 +3090,28 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" ht="39" spans="4:15">
@@ -3167,28 +3119,28 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="4:15">
@@ -3196,28 +3148,28 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M9">
         <v>70</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="4:15">
@@ -3225,28 +3177,28 @@
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="4:12">
@@ -3254,19 +3206,19 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="4:12">
@@ -3274,19 +3226,19 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>90</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="4:12">
@@ -3294,19 +3246,19 @@
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="4:12">
@@ -3314,13 +3266,13 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K14">
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="4:5">
@@ -3328,7 +3280,7 @@
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="4:5">
@@ -3336,7 +3288,7 @@
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="4:5">
@@ -3344,7 +3296,7 @@
         <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="4:5">
@@ -3352,7 +3304,7 @@
         <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="4:5">
@@ -3360,7 +3312,7 @@
         <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="4:5">
@@ -3368,7 +3320,7 @@
         <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="4:5">
@@ -3376,7 +3328,7 @@
         <v>51</v>
       </c>
       <c r="E21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="4:5">
@@ -3384,7 +3336,7 @@
         <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="4:5">
@@ -3392,7 +3344,7 @@
         <v>62</v>
       </c>
       <c r="E23" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="4:5">
@@ -3400,7 +3352,7 @@
         <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="4:5">
@@ -3408,7 +3360,7 @@
         <v>110</v>
       </c>
       <c r="E25" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="4:5">
@@ -3416,7 +3368,7 @@
         <v>201</v>
       </c>
       <c r="E26" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="4:5">
@@ -3424,7 +3376,7 @@
         <v>1010</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="4:5">
@@ -3432,7 +3384,7 @@
         <v>1011</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="3"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="107">
   <si>
     <t>Id</t>
   </si>
@@ -36,9 +36,6 @@
     <t>AchieveTextId</t>
   </si>
   <si>
-    <t>EnemyBasementId</t>
-  </si>
-  <si>
     <t>Selectable</t>
   </si>
   <si>
@@ -51,6 +48,12 @@
     <t>RandomTroopWeight</t>
   </si>
   <si>
+    <t>EncountMin</t>
+  </si>
+  <si>
+    <t>EncountMax</t>
+  </si>
+  <si>
     <t>BGMId</t>
   </si>
   <si>
@@ -123,7 +126,7 @@
     <t>""</t>
   </si>
   <si>
-    <t>ステージ1</t>
+    <t>始まりの時</t>
   </si>
   <si>
     <t>ステージ2</t>
@@ -206,6 +209,9 @@
   <si>
     <t>射程内に攻撃可能な敵がいれば攻撃、
 いない場合は敵の射程に入っていれば射程外へ逃げる、入っていなければその場で待機。</t>
+  </si>
+  <si>
+    <t>ダンジョン内</t>
   </si>
   <si>
     <t>隷従属度フラグを管理</t>
@@ -345,9 +351,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -370,8 +376,40 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -385,14 +423,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -405,11 +443,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -421,47 +466,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -476,22 +482,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -500,10 +490,18 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -513,6 +511,14 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -523,49 +529,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -577,133 +709,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -717,17 +723,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -760,16 +766,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -800,17 +806,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -822,16 +828,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -840,127 +846,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1299,15 +1305,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1"/>
   <cols>
-    <col min="5" max="6" width="8.45454545454546" customWidth="1"/>
-    <col min="7" max="7" width="10.3636363636364" customWidth="1"/>
-    <col min="14" max="14" width="32" customWidth="1"/>
+    <col min="5" max="5" width="8.45454545454546" customWidth="1"/>
+    <col min="6" max="6" width="10.3636363636364" customWidth="1"/>
+    <col min="15" max="15" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1323,16 +1329,16 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -1350,8 +1356,11 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>10</v>
       </c>
@@ -1368,31 +1377,34 @@
         <v>10010</v>
       </c>
       <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>0</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
+        <v>30</v>
+      </c>
+      <c r="J2">
         <v>0</v>
       </c>
-      <c r="J2">
-        <v>30</v>
-      </c>
       <c r="K2">
-        <v>1010</v>
+        <v>0</v>
       </c>
       <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
         <v>2010</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>100</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>14</v>
+      <c r="O2" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1404,8 +1416,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="2"/>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="4"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
     <col min="7" max="7" width="18.3636363636364" customWidth="1"/>
@@ -1416,33 +1428,33 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="H1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1468,10 +1480,10 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>3010</v>
@@ -1484,6 +1496,52 @@
       </c>
       <c r="I3" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>3010</v>
+      </c>
+      <c r="F4">
+        <v>5010</v>
+      </c>
+      <c r="H4">
+        <v>1010</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>3010</v>
+      </c>
+      <c r="F5">
+        <v>2010</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1503,10 +1561,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1592,25 +1650,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1660,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1671,10 +1729,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1682,10 +1740,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -1694,10 +1752,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -1706,10 +1764,10 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -1718,10 +1776,10 @@
         <v>1020</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -1730,10 +1788,10 @@
         <v>1030</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="3"/>
     </row>
@@ -1742,10 +1800,10 @@
         <v>10010</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" s="3"/>
     </row>
@@ -1776,19 +1834,19 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1796,31 +1854,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -1828,34 +1886,34 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1863,34 +1921,34 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:15">
@@ -1898,63 +1956,69 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M5">
         <v>30</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="4:15">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6">
+        <v>3010</v>
+      </c>
+      <c r="B6" t="s">
+        <v>63</v>
+      </c>
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="4:15">
@@ -1962,28 +2026,28 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" ht="39" spans="4:15">
@@ -1991,28 +2055,28 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="4:15">
@@ -2020,28 +2084,28 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M9">
         <v>70</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="4:15">
@@ -2049,28 +2113,28 @@
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="4:12">
@@ -2078,19 +2142,19 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="4:12">
@@ -2098,19 +2162,19 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K12">
         <v>90</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="4:12">
@@ -2118,19 +2182,19 @@
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="4:12">
@@ -2138,13 +2202,13 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K14">
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="4:5">
@@ -2152,7 +2216,7 @@
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="4:5">
@@ -2160,7 +2224,7 @@
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="4:5">
@@ -2168,7 +2232,7 @@
         <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="4:5">
@@ -2176,7 +2240,7 @@
         <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="4:5">
@@ -2184,7 +2248,7 @@
         <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="4:5">
@@ -2192,7 +2256,7 @@
         <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="4:5">
@@ -2200,7 +2264,7 @@
         <v>51</v>
       </c>
       <c r="E21" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="4:5">
@@ -2208,7 +2272,7 @@
         <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="4:5">
@@ -2216,7 +2280,7 @@
         <v>62</v>
       </c>
       <c r="E23" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="4:5">
@@ -2224,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="4:5">
@@ -2232,7 +2296,7 @@
         <v>110</v>
       </c>
       <c r="E25" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="4:5">
@@ -2240,7 +2304,7 @@
         <v>201</v>
       </c>
       <c r="E26" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="4:5">
@@ -2248,7 +2312,7 @@
         <v>1010</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="4:5">
@@ -2256,7 +2320,7 @@
         <v>1011</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="105">
   <si>
     <t>Id</t>
   </si>
@@ -30,19 +30,13 @@
     <t>StageNo</t>
   </si>
   <si>
-    <t>AchieveType</t>
-  </si>
-  <si>
-    <t>AchieveTextId</t>
-  </si>
-  <si>
     <t>Selectable</t>
   </si>
   <si>
     <t>StageLv</t>
   </si>
   <si>
-    <t>PartyMemberIds</t>
+    <t>DisplayRank</t>
   </si>
   <si>
     <t>RandomTroopWeight</t>
@@ -129,7 +123,7 @@
     <t>始まりの時</t>
   </si>
   <si>
-    <t>ステージ2</t>
+    <t>灰標の夕草原</t>
   </si>
   <si>
     <t>ゲームの流れ</t>
@@ -350,10 +344,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -376,9 +370,38 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -392,52 +415,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -458,24 +445,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -497,14 +499,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -512,9 +506,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -529,37 +523,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -577,139 +697,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -723,17 +717,32 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -743,6 +752,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -765,36 +789,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -806,17 +800,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -828,145 +822,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1305,15 +1299,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1"/>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="2"/>
   <cols>
-    <col min="5" max="5" width="8.45454545454546" customWidth="1"/>
-    <col min="6" max="6" width="10.3636363636364" customWidth="1"/>
-    <col min="15" max="15" width="32" customWidth="1"/>
+    <col min="4" max="4" width="10.3636363636364" customWidth="1"/>
+    <col min="13" max="13" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1323,19 +1316,19 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -1353,14 +1346,8 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>10</v>
       </c>
@@ -1371,40 +1358,75 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>10010</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>2010</v>
       </c>
       <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
+        <v>100</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>20</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>30</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>15</v>
+      </c>
+      <c r="J3">
+        <v>1010</v>
+      </c>
+      <c r="K3">
         <v>2010</v>
       </c>
-      <c r="N2">
+      <c r="L3">
         <v>100</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>15</v>
+      <c r="M3" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1428,28 +1450,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
         <v>19</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>20</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1561,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1650,25 +1672,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>27</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>28</v>
-      </c>
-      <c r="G1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1718,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1729,10 +1751,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1740,10 +1762,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -1752,10 +1774,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -1764,10 +1786,10 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -1776,10 +1798,10 @@
         <v>1020</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -1788,10 +1810,10 @@
         <v>1030</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7" s="3"/>
     </row>
@@ -1800,10 +1822,10 @@
         <v>10010</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" s="3"/>
     </row>
@@ -1834,19 +1856,19 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
       <c r="I1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1854,31 +1876,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -1886,34 +1908,34 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1921,34 +1943,34 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:15">
@@ -1956,34 +1978,34 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M5">
         <v>30</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1991,34 +2013,34 @@
         <v>3010</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="4:15">
@@ -2026,28 +2048,28 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" ht="39" spans="4:15">
@@ -2055,28 +2077,28 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="4:15">
@@ -2084,28 +2106,28 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M9">
         <v>70</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="4:15">
@@ -2113,28 +2135,28 @@
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="4:12">
@@ -2142,19 +2164,19 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="4:12">
@@ -2162,19 +2184,19 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K12">
         <v>90</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="4:12">
@@ -2182,19 +2204,19 @@
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="4:12">
@@ -2202,13 +2224,13 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K14">
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="4:5">
@@ -2216,7 +2238,7 @@
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="4:5">
@@ -2224,7 +2246,7 @@
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="4:5">
@@ -2232,7 +2254,7 @@
         <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="4:5">
@@ -2240,7 +2262,7 @@
         <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="4:5">
@@ -2248,7 +2270,7 @@
         <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="4:5">
@@ -2256,7 +2278,7 @@
         <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="4:5">
@@ -2264,7 +2286,7 @@
         <v>51</v>
       </c>
       <c r="E21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="4:5">
@@ -2272,7 +2294,7 @@
         <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="4:5">
@@ -2280,7 +2302,7 @@
         <v>62</v>
       </c>
       <c r="E23" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="4:5">
@@ -2288,7 +2310,7 @@
         <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="4:5">
@@ -2296,7 +2318,7 @@
         <v>110</v>
       </c>
       <c r="E25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="4:5">
@@ -2304,7 +2326,7 @@
         <v>201</v>
       </c>
       <c r="E26" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="4:5">
@@ -2312,7 +2334,7 @@
         <v>1010</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="4:5">
@@ -2320,7 +2342,7 @@
         <v>1011</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
     <t>BackGround</t>
   </si>
   <si>
-    <t>NA_background image_3D like_894</t>
+    <t>RockCave2</t>
   </si>
   <si>
     <t>PositionX</t>
@@ -123,7 +123,7 @@
     <t>始まりの時</t>
   </si>
   <si>
-    <t>灰標の夕草原</t>
+    <t>山岳遺跡</t>
   </si>
   <si>
     <t>ゲームの流れ</t>
@@ -344,10 +344,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -370,54 +370,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -437,9 +392,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -455,14 +416,14 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -477,6 +438,68 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -490,29 +513,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -523,13 +523,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -541,37 +643,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,19 +685,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -607,103 +697,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -714,21 +714,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -747,26 +732,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -789,13 +765,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -814,6 +794,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -822,145 +822,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="4"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -1575,8 +1575,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="6" outlineLevelCol="2"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="5" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
@@ -1591,7 +1591,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1613,7 +1613,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1624,7 +1624,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -1635,24 +1635,13 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>7</v>
       </c>
       <c r="C6">
         <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>16</v>
-      </c>
-      <c r="C7">
-        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -344,10 +344,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -370,9 +370,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -386,7 +386,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -399,21 +399,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -422,11 +407,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -445,21 +430,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -467,7 +437,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -491,10 +461,18 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -508,7 +486,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -523,187 +523,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -714,6 +714,17 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -750,15 +761,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -780,6 +782,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -794,26 +814,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -822,145 +822,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1438,8 +1438,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="4"/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="5"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
     <col min="7" max="7" width="18.3636363636364" customWidth="1"/>
@@ -1476,19 +1476,19 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>1010</v>
+        <v>3010</v>
       </c>
       <c r="F2">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1505,16 +1505,16 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>3010</v>
       </c>
       <c r="F3">
-        <v>4020</v>
+        <v>5010</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
@@ -1528,42 +1528,65 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>3010</v>
       </c>
       <c r="F4">
-        <v>5010</v>
+        <v>2010</v>
       </c>
       <c r="H4">
-        <v>1010</v>
+        <v>0</v>
       </c>
       <c r="I4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5">
+        <v>20</v>
+      </c>
+      <c r="B5">
         <v>10</v>
       </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
       <c r="C5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>3010</v>
       </c>
       <c r="F5">
-        <v>2010</v>
+        <v>6010</v>
       </c>
       <c r="H5">
+        <v>79</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>3010</v>
+      </c>
+      <c r="F6">
         <v>0</v>
       </c>
-      <c r="I5" t="b">
-        <v>0</v>
+      <c r="H6">
+        <v>79</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="108">
   <si>
     <t>Id</t>
   </si>
@@ -81,6 +81,12 @@
     <t>Param</t>
   </si>
   <si>
+    <t>Param2</t>
+  </si>
+  <si>
+    <t>Param3</t>
+  </si>
+  <si>
     <t>ReadFlag</t>
   </si>
   <si>
@@ -124,6 +130,9 @@
   </si>
   <si>
     <t>山岳遺跡</t>
+  </si>
+  <si>
+    <t>山岳遺跡・奥</t>
   </si>
   <si>
     <t>ゲームの流れ</t>
@@ -344,10 +353,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -372,7 +381,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -392,18 +416,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -416,37 +433,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -454,31 +441,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -501,7 +464,45 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -513,6 +514,14 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -523,187 +532,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -714,17 +723,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -743,49 +741,21 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -814,6 +784,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -822,145 +831,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1299,8 +1308,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="2"/>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="3"/>
   <cols>
     <col min="4" max="4" width="10.3636363636364" customWidth="1"/>
     <col min="13" max="13" width="32" customWidth="1"/>
@@ -1426,6 +1435,47 @@
         <v>100</v>
       </c>
       <c r="M3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>21</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>30</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>15</v>
+      </c>
+      <c r="J4">
+        <v>1010</v>
+      </c>
+      <c r="K4">
+        <v>2010</v>
+      </c>
+      <c r="L4">
+        <v>100</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1438,14 +1488,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="5"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="7"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
     <col min="7" max="7" width="18.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1473,8 +1523,14 @@
       <c r="I1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>10</v>
       </c>
@@ -1493,11 +1549,17 @@
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" t="b">
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>10</v>
       </c>
@@ -1516,11 +1578,17 @@
       <c r="H3">
         <v>1010</v>
       </c>
-      <c r="I3" t="b">
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>10</v>
       </c>
@@ -1539,11 +1607,17 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>20</v>
       </c>
@@ -1562,11 +1636,17 @@
       <c r="H5">
         <v>79</v>
       </c>
-      <c r="I5" t="b">
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>20</v>
       </c>
@@ -1585,8 +1665,72 @@
       <c r="H6">
         <v>79</v>
       </c>
-      <c r="I6" t="b">
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>20</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>3010</v>
+      </c>
+      <c r="F7">
+        <v>2020</v>
+      </c>
+      <c r="H7">
+        <v>21</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>14</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>21</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>3010</v>
+      </c>
+      <c r="F8">
+        <v>2020</v>
+      </c>
+      <c r="H8">
+        <v>20</v>
+      </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1598,18 +1742,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1664,6 +1808,61 @@
         <v>7</v>
       </c>
       <c r="C6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>21</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>21</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>21</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>21</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>21</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
         <v>20</v>
       </c>
     </row>
@@ -1684,25 +1883,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
         <v>16</v>
       </c>
       <c r="D1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1740,7 +1939,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="34.1818181818182" customWidth="1"/>
@@ -1752,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1763,10 +1962,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1774,10 +1973,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -1786,70 +1985,82 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <v>1010</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
+        <v>1030</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
         <v>10010</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="3:4">
-      <c r="C9" s="3"/>
+      <c r="B9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="3:3">
+    <row r="10" spans="3:4">
       <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1874,13 +2085,13 @@
         <v>18</v>
       </c>
       <c r="I1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1888,31 +2099,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -1920,34 +2131,34 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1955,34 +2166,34 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:15">
@@ -1990,34 +2201,34 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M5">
         <v>30</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -2025,34 +2236,34 @@
         <v>3010</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="4:15">
@@ -2060,28 +2271,28 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" ht="39" spans="4:15">
@@ -2089,28 +2300,28 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="4:15">
@@ -2118,28 +2329,28 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M9">
         <v>70</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="4:15">
@@ -2147,28 +2358,28 @@
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="4:12">
@@ -2176,19 +2387,19 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="4:12">
@@ -2196,19 +2407,19 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K12">
         <v>90</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="4:12">
@@ -2216,19 +2427,19 @@
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="4:12">
@@ -2236,13 +2447,13 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K14">
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="4:5">
@@ -2250,7 +2461,7 @@
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="4:5">
@@ -2258,7 +2469,7 @@
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="4:5">
@@ -2266,7 +2477,7 @@
         <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="4:5">
@@ -2274,7 +2485,7 @@
         <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="4:5">
@@ -2282,7 +2493,7 @@
         <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="4:5">
@@ -2290,7 +2501,7 @@
         <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="4:5">
@@ -2298,7 +2509,7 @@
         <v>51</v>
       </c>
       <c r="E21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="4:5">
@@ -2306,7 +2517,7 @@
         <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="4:5">
@@ -2314,7 +2525,7 @@
         <v>62</v>
       </c>
       <c r="E23" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="4:5">
@@ -2322,7 +2533,7 @@
         <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="4:5">
@@ -2330,7 +2541,7 @@
         <v>110</v>
       </c>
       <c r="E25" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="4:5">
@@ -2338,7 +2549,7 @@
         <v>201</v>
       </c>
       <c r="E26" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="4:5">
@@ -2346,7 +2557,7 @@
         <v>1010</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="4:5">
@@ -2354,7 +2565,7 @@
         <v>1011</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -353,8 +353,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -379,22 +379,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -402,44 +386,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -455,34 +401,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -500,6 +438,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -508,8 +461,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -522,6 +476,52 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -532,187 +532,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -741,11 +741,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -756,6 +771,30 @@
         <color theme="4"/>
       </top>
       <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -784,45 +823,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -831,7 +831,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -840,7 +840,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -849,127 +849,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1488,8 +1488,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="7"/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
     <col min="7" max="7" width="18.3636363636364" customWidth="1"/>
@@ -1731,6 +1731,35 @@
       </c>
       <c r="K8" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>21</v>
+      </c>
+      <c r="B9">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>3010</v>
+      </c>
+      <c r="F9">
+        <v>5020</v>
+      </c>
+      <c r="H9">
+        <v>1020</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -353,10 +353,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -379,6 +379,58 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -386,8 +438,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -402,44 +462,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -447,6 +470,14 @@
     <font>
       <b/>
       <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -463,46 +494,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -516,8 +508,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -532,187 +532,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -741,6 +741,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -759,19 +777,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -791,24 +798,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -823,6 +812,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -831,145 +831,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1420,16 +1420,16 @@
         <v>30</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J3">
         <v>1010</v>
       </c>
       <c r="K3">
-        <v>2010</v>
+        <v>3010</v>
       </c>
       <c r="L3">
         <v>100</v>
@@ -1461,16 +1461,16 @@
         <v>30</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>1010</v>
       </c>
       <c r="K4">
-        <v>2010</v>
+        <v>3010</v>
       </c>
       <c r="L4">
         <v>100</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="91">
   <si>
     <t>Id</t>
   </si>
@@ -168,7 +168,7 @@
     <t>Tactics開始(UI表示前)</t>
   </si>
   <si>
-    <t>コマンドを制限する</t>
+    <t>Adv再生</t>
   </si>
   <si>
     <t>None</t>
@@ -183,7 +183,7 @@
     <t>Battle勝利後</t>
   </si>
   <si>
-    <t>バトルをチュートリアルで固定する</t>
+    <t>ダンジョンから出る</t>
   </si>
   <si>
     <t>Battle</t>
@@ -201,7 +201,7 @@
     <t>チュートリアル開始</t>
   </si>
   <si>
-    <t>全員コマンドを選ばないと進まない</t>
+    <t>ダンジョン移動</t>
   </si>
   <si>
     <t>Basement</t>
@@ -217,7 +217,7 @@
     <t>ダンジョン内</t>
   </si>
   <si>
-    <t>隷従属度フラグを管理</t>
+    <t>アーティファクト取得</t>
   </si>
   <si>
     <t>Event</t>
@@ -232,7 +232,7 @@
     <t>ランダムに移動。</t>
   </si>
   <si>
-    <t>アルカナフラグを管理</t>
+    <t>仲間を増やす</t>
   </si>
   <si>
     <t>GetItem</t>
@@ -244,7 +244,7 @@
     <t>射程内に攻撃可能な敵がいれば攻撃、いなければ一定のルートを移動。</t>
   </si>
   <si>
-    <t>仲間を選んで加入する</t>
+    <t>選択して仲間を増やす</t>
   </si>
   <si>
     <t>Actor</t>
@@ -258,7 +258,7 @@
 隣接など攻撃可能でないと挑発は出来ない。</t>
   </si>
   <si>
-    <t>セーブを行う</t>
+    <t>強制戦闘</t>
   </si>
   <si>
     <t>Rebirth</t>
@@ -270,7 +270,7 @@
     <t>特定の目標に向かって移動。攻撃してこない。</t>
   </si>
   <si>
-    <t>ボスの選択番号を設定する</t>
+    <t>強制ボス戦闘</t>
   </si>
   <si>
     <t>SelectActor</t>
@@ -282,70 +282,19 @@
     <t>離脱ポイントへ向かう。攻撃してこない。</t>
   </si>
   <si>
-    <t>SPを消費しないと進まない</t>
+    <t>指定のイベントマスを消す</t>
   </si>
   <si>
     <t>Shop</t>
   </si>
   <si>
-    <t>IDにActorIDを加算してADV再生</t>
-  </si>
-  <si>
     <t>Gacha</t>
   </si>
   <si>
-    <t>ルート分岐イベント</t>
-  </si>
-  <si>
     <t>Group</t>
   </si>
   <si>
-    <t>ルート分岐パラメータ設定</t>
-  </si>
-  <si>
     <t>Battler</t>
-  </si>
-  <si>
-    <t>ルート分岐ステージ移動</t>
-  </si>
-  <si>
-    <t>ステージクリア</t>
-  </si>
-  <si>
-    <t>ルート分岐でステージに移動</t>
-  </si>
-  <si>
-    <t>ルート分岐敵グループを生成</t>
-  </si>
-  <si>
-    <t>表示残りターンをマスターから取得</t>
-  </si>
-  <si>
-    <t>継承スキル演出開始</t>
-  </si>
-  <si>
-    <t>ステージ移動</t>
-  </si>
-  <si>
-    <t>中ボスを設置する(コマンド制限判定あり)</t>
-  </si>
-  <si>
-    <t>上位者ボスを設置する(コマンド制限判定あり)</t>
-  </si>
-  <si>
-    <t>ADV再生</t>
-  </si>
-  <si>
-    <t>今のステージシンボルの〇SeekIndexのバトルを開始</t>
-  </si>
-  <si>
-    <t>サバイバルモードにする</t>
-  </si>
-  <si>
-    <t>ターン終了コマンド操作有効</t>
-  </si>
-  <si>
-    <t>ターン終了コマンド操作無効</t>
   </si>
 </sst>
 </file>
@@ -354,8 +303,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
@@ -379,22 +328,14 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -409,6 +350,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -425,6 +367,52 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -432,22 +420,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -455,29 +428,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -493,33 +443,32 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -532,6 +481,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -544,175 +505,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,42 +692,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -798,28 +731,44 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -831,16 +780,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -849,127 +798,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1488,7 +1437,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
@@ -1759,6 +1708,35 @@
         <v>0</v>
       </c>
       <c r="K9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>21</v>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>3010</v>
+      </c>
+      <c r="F10">
+        <v>3010</v>
+      </c>
+      <c r="H10">
+        <v>2010</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2103,6 +2081,8 @@
   <dimension ref="A1:O28"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
+    <col min="4" max="4" width="5.63636363636364" customWidth="1"/>
+    <col min="5" max="5" width="24.6363636363636" customWidth="1"/>
     <col min="15" max="15" width="45.9090909090909" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2163,7 +2143,7 @@
         <v>48</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="E3" t="s">
         <v>49</v>
@@ -2198,7 +2178,7 @@
         <v>53</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>2010</v>
       </c>
       <c r="E4" t="s">
         <v>54</v>
@@ -2233,7 +2213,7 @@
         <v>59</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2020</v>
       </c>
       <c r="E5" t="s">
         <v>60</v>
@@ -2268,7 +2248,7 @@
         <v>64</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>3010</v>
       </c>
       <c r="E6" t="s">
         <v>65</v>
@@ -2297,7 +2277,7 @@
     </row>
     <row r="7" spans="4:15">
       <c r="D7">
-        <v>5</v>
+        <v>4010</v>
       </c>
       <c r="E7" t="s">
         <v>70</v>
@@ -2326,7 +2306,7 @@
     </row>
     <row r="8" ht="39" spans="4:15">
       <c r="D8">
-        <v>6</v>
+        <v>4020</v>
       </c>
       <c r="E8" t="s">
         <v>74</v>
@@ -2355,7 +2335,7 @@
     </row>
     <row r="9" spans="4:15">
       <c r="D9">
-        <v>7</v>
+        <v>5010</v>
       </c>
       <c r="E9" t="s">
         <v>78</v>
@@ -2384,7 +2364,7 @@
     </row>
     <row r="10" spans="4:15">
       <c r="D10">
-        <v>8</v>
+        <v>5020</v>
       </c>
       <c r="E10" t="s">
         <v>82</v>
@@ -2413,7 +2393,7 @@
     </row>
     <row r="11" spans="4:12">
       <c r="D11">
-        <v>9</v>
+        <v>6010</v>
       </c>
       <c r="E11" t="s">
         <v>86</v>
@@ -2431,13 +2411,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="4:12">
-      <c r="D12">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
-        <v>88</v>
-      </c>
+    <row r="12" spans="9:12">
       <c r="I12">
         <v>80</v>
       </c>
@@ -2448,154 +2422,36 @@
         <v>90</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="4:12">
-      <c r="D13">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
-        <v>90</v>
-      </c>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="9:12">
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="4:12">
-      <c r="D14">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s">
-        <v>92</v>
-      </c>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="11:12">
       <c r="K14">
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="4:5">
-      <c r="D15">
-        <v>15</v>
-      </c>
-      <c r="E15" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="4:5">
-      <c r="D16">
-        <v>21</v>
-      </c>
-      <c r="E16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="4:5">
-      <c r="D17">
-        <v>31</v>
-      </c>
-      <c r="E17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="4:5">
-      <c r="D18">
-        <v>32</v>
-      </c>
-      <c r="E18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="4:5">
-      <c r="D19">
-        <v>33</v>
-      </c>
-      <c r="E19" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="20" spans="4:5">
-      <c r="D20">
-        <v>41</v>
-      </c>
-      <c r="E20" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="21" spans="4:5">
-      <c r="D21">
-        <v>51</v>
-      </c>
-      <c r="E21" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="4:5">
-      <c r="D22">
-        <v>61</v>
-      </c>
-      <c r="E22" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="4:5">
-      <c r="D23">
-        <v>62</v>
-      </c>
-      <c r="E23" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="4:5">
-      <c r="D24">
-        <v>100</v>
-      </c>
-      <c r="E24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="4:5">
-      <c r="D25">
-        <v>110</v>
-      </c>
-      <c r="E25" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="4:5">
-      <c r="D26">
-        <v>201</v>
-      </c>
-      <c r="E26" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="4:5">
-      <c r="D27">
-        <v>1010</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="28" spans="4:5">
-      <c r="D28">
-        <v>1011</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>107</v>
-      </c>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="5:5">
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="5:5">
+      <c r="E28" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="96">
   <si>
     <t>Id</t>
   </si>
@@ -63,6 +63,12 @@
     <t>RockCave2</t>
   </si>
   <si>
+    <t>002-Woods01</t>
+  </si>
+  <si>
+    <t>DirtCave</t>
+  </si>
+  <si>
     <t>PositionX</t>
   </si>
   <si>
@@ -133,6 +139,12 @@
   </si>
   <si>
     <t>山岳遺跡・奥</t>
+  </si>
+  <si>
+    <t>森</t>
+  </si>
+  <si>
+    <t>森・地下洞窟</t>
   </si>
   <si>
     <t>ゲームの流れ</t>
@@ -232,19 +244,19 @@
     <t>ランダムに移動。</t>
   </si>
   <si>
+    <t>アイテム取得</t>
+  </si>
+  <si>
+    <t>GetItem</t>
+  </si>
+  <si>
+    <t>巡回</t>
+  </si>
+  <si>
+    <t>射程内に攻撃可能な敵がいれば攻撃、いなければ一定のルートを移動。</t>
+  </si>
+  <si>
     <t>仲間を増やす</t>
-  </si>
-  <si>
-    <t>GetItem</t>
-  </si>
-  <si>
-    <t>巡回</t>
-  </si>
-  <si>
-    <t>射程内に攻撃可能な敵がいれば攻撃、いなければ一定のルートを移動。</t>
-  </si>
-  <si>
-    <t>選択して仲間を増やす</t>
   </si>
   <si>
     <t>Actor</t>
@@ -258,34 +270,37 @@
 隣接など攻撃可能でないと挑発は出来ない。</t>
   </si>
   <si>
+    <t>選択して仲間を増やす</t>
+  </si>
+  <si>
+    <t>Rebirth</t>
+  </si>
+  <si>
+    <t>移動</t>
+  </si>
+  <si>
+    <t>特定の目標に向かって移動。攻撃してこない。</t>
+  </si>
+  <si>
     <t>強制戦闘</t>
   </si>
   <si>
-    <t>Rebirth</t>
-  </si>
-  <si>
-    <t>移動</t>
-  </si>
-  <si>
-    <t>特定の目標に向かって移動。攻撃してこない。</t>
+    <t>SelectActor</t>
+  </si>
+  <si>
+    <t>離脱</t>
+  </si>
+  <si>
+    <t>離脱ポイントへ向かう。攻撃してこない。</t>
   </si>
   <si>
     <t>強制ボス戦闘</t>
   </si>
   <si>
-    <t>SelectActor</t>
-  </si>
-  <si>
-    <t>離脱</t>
-  </si>
-  <si>
-    <t>離脱ポイントへ向かう。攻撃してこない。</t>
+    <t>Shop</t>
   </si>
   <si>
     <t>指定のイベントマスを消す</t>
-  </si>
-  <si>
-    <t>Shop</t>
   </si>
   <si>
     <t>Gacha</t>
@@ -302,10 +317,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -329,7 +344,58 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -343,49 +409,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -396,38 +424,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -442,23 +440,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -471,6 +470,22 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -481,7 +496,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -493,19 +580,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -523,7 +616,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,7 +628,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -547,43 +640,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -595,73 +676,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,6 +705,39 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -697,6 +745,21 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -716,39 +779,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -757,21 +787,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -780,145 +795,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1257,8 +1272,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="3"/>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="5"/>
   <cols>
     <col min="4" max="4" width="10.3636363636364" customWidth="1"/>
     <col min="13" max="13" width="32" customWidth="1"/>
@@ -1322,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>30</v>
@@ -1426,6 +1441,88 @@
       </c>
       <c r="M4" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5">
+        <v>30</v>
+      </c>
+      <c r="B5">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>30</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>1020</v>
+      </c>
+      <c r="K5">
+        <v>3010</v>
+      </c>
+      <c r="L5">
+        <v>100</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>30</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>1020</v>
+      </c>
+      <c r="K6">
+        <v>3010</v>
+      </c>
+      <c r="L6">
+        <v>100</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1437,11 +1534,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
-    <col min="7" max="7" width="18.3636363636364" customWidth="1"/>
+    <col min="7" max="7" width="21.7272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1449,34 +1546,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1495,6 +1592,10 @@
       <c r="F2">
         <v>4020</v>
       </c>
+      <c r="G2" t="str">
+        <f>INDEX(Define!E:E,MATCH(F2,Define!D:D))</f>
+        <v>選択して仲間を増やす</v>
+      </c>
       <c r="H2">
         <v>1</v>
       </c>
@@ -1524,6 +1625,10 @@
       <c r="F3">
         <v>5010</v>
       </c>
+      <c r="G3" t="str">
+        <f>INDEX(Define!E:E,MATCH(F3,Define!D:D))</f>
+        <v>強制戦闘</v>
+      </c>
       <c r="H3">
         <v>1010</v>
       </c>
@@ -1553,6 +1658,10 @@
       <c r="F4">
         <v>2010</v>
       </c>
+      <c r="G4" t="str">
+        <f>INDEX(Define!E:E,MATCH(F4,Define!D:D))</f>
+        <v>ダンジョンから出る</v>
+      </c>
       <c r="H4">
         <v>0</v>
       </c>
@@ -1582,6 +1691,10 @@
       <c r="F5">
         <v>6010</v>
       </c>
+      <c r="G5" t="str">
+        <f>INDEX(Define!E:E,MATCH(F5,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
+      </c>
       <c r="H5">
         <v>79</v>
       </c>
@@ -1640,6 +1753,10 @@
       <c r="F7">
         <v>2020</v>
       </c>
+      <c r="G7" t="str">
+        <f>INDEX(Define!E:E,MATCH(F7,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
       <c r="H7">
         <v>21</v>
       </c>
@@ -1669,6 +1786,10 @@
       <c r="F8">
         <v>2020</v>
       </c>
+      <c r="G8" t="str">
+        <f>INDEX(Define!E:E,MATCH(F8,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
       <c r="H8">
         <v>20</v>
       </c>
@@ -1698,6 +1819,10 @@
       <c r="F9">
         <v>5020</v>
       </c>
+      <c r="G9" t="str">
+        <f>INDEX(Define!E:E,MATCH(F9,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
       <c r="H9">
         <v>1020</v>
       </c>
@@ -1727,6 +1852,10 @@
       <c r="F10">
         <v>3010</v>
       </c>
+      <c r="G10" t="str">
+        <f>INDEX(Define!E:E,MATCH(F10,Define!D:D))</f>
+        <v>アーティファクト取得</v>
+      </c>
       <c r="H10">
         <v>2010</v>
       </c>
@@ -1737,6 +1866,394 @@
         <v>0</v>
       </c>
       <c r="K10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>21</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>3010</v>
+      </c>
+      <c r="F11">
+        <v>3020</v>
+      </c>
+      <c r="G11" t="str">
+        <f>INDEX(Define!E:E,MATCH(F11,Define!D:D))</f>
+        <v>アイテム取得</v>
+      </c>
+      <c r="H11">
+        <v>1000</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>30</v>
+      </c>
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12">
+        <v>15</v>
+      </c>
+      <c r="D12">
+        <v>3010</v>
+      </c>
+      <c r="F12">
+        <v>2010</v>
+      </c>
+      <c r="G12" t="str">
+        <f>INDEX(Define!E:E,MATCH(F12,Define!D:D))</f>
+        <v>ダンジョンから出る</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>30</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>3010</v>
+      </c>
+      <c r="F13">
+        <v>2020</v>
+      </c>
+      <c r="G13" t="str">
+        <f>INDEX(Define!E:E,MATCH(F13,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H13">
+        <v>31</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>30</v>
+      </c>
+      <c r="B14">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>3010</v>
+      </c>
+      <c r="F14">
+        <v>2020</v>
+      </c>
+      <c r="G14" t="str">
+        <f>INDEX(Define!E:E,MATCH(F14,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H14">
+        <v>31</v>
+      </c>
+      <c r="I14">
+        <v>14</v>
+      </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>30</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <v>3010</v>
+      </c>
+      <c r="F15">
+        <v>6010</v>
+      </c>
+      <c r="G15" t="str">
+        <f>INDEX(Define!E:E,MATCH(F15,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
+      </c>
+      <c r="H15">
+        <v>612</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>30</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>12</v>
+      </c>
+      <c r="D16">
+        <v>3010</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>612</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17">
+        <v>30</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <v>3010</v>
+      </c>
+      <c r="F17">
+        <v>6010</v>
+      </c>
+      <c r="G17" t="str">
+        <f>INDEX(Define!E:E,MATCH(F17,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
+      </c>
+      <c r="H17">
+        <v>86</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18">
+        <v>30</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>3010</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>86</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19">
+        <v>31</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>3010</v>
+      </c>
+      <c r="F19">
+        <v>2020</v>
+      </c>
+      <c r="G19" t="str">
+        <f>INDEX(Define!E:E,MATCH(F19,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H19">
+        <v>30</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20">
+        <v>31</v>
+      </c>
+      <c r="B20">
+        <v>14</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>3010</v>
+      </c>
+      <c r="F20">
+        <v>2020</v>
+      </c>
+      <c r="G20" t="str">
+        <f>INDEX(Define!E:E,MATCH(F20,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H20">
+        <v>30</v>
+      </c>
+      <c r="I20">
+        <v>14</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21">
+        <v>31</v>
+      </c>
+      <c r="B21">
+        <v>11</v>
+      </c>
+      <c r="C21">
+        <v>7</v>
+      </c>
+      <c r="D21">
+        <v>3010</v>
+      </c>
+      <c r="F21">
+        <v>5020</v>
+      </c>
+      <c r="G21" t="str">
+        <f>INDEX(Define!E:E,MATCH(F21,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H21">
+        <v>2010</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22">
+        <v>31</v>
+      </c>
+      <c r="B22">
+        <v>8</v>
+      </c>
+      <c r="C22">
+        <v>13</v>
+      </c>
+      <c r="D22">
+        <v>3010</v>
+      </c>
+      <c r="F22">
+        <v>3010</v>
+      </c>
+      <c r="G22" t="str">
+        <f>INDEX(Define!E:E,MATCH(F22,Define!D:D))</f>
+        <v>アーティファクト取得</v>
+      </c>
+      <c r="H22">
+        <v>2020</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1749,7 +2266,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1757,10 +2274,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1870,6 +2387,116 @@
         <v>7</v>
       </c>
       <c r="C11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>30</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>30</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>30</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>30</v>
+      </c>
+      <c r="B15">
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>30</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>31</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>31</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>31</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>31</v>
+      </c>
+      <c r="B20">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>31</v>
+      </c>
+      <c r="B21">
+        <v>7</v>
+      </c>
+      <c r="C21">
         <v>20</v>
       </c>
     </row>
@@ -1890,25 +2517,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1946,7 +2573,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="34.1818181818182" customWidth="1"/>
@@ -1958,10 +2585,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1969,10 +2596,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1980,10 +2607,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -1992,10 +2619,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -2004,70 +2631,94 @@
         <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
-        <v>1010</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
-        <v>1020</v>
+        <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>34</v>
+        <v>41</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
+        <v>1020</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>1030</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
         <v>10010</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="3:4">
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="3:3">
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" spans="3:3">
+      <c r="B11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="3:4">
       <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2088,19 +2739,19 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2108,31 +2759,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -2140,34 +2791,34 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D3">
         <v>1010</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -2175,34 +2826,34 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D4">
         <v>2010</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:15">
@@ -2210,34 +2861,34 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D5">
         <v>2020</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M5">
         <v>30</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -2245,184 +2896,190 @@
         <v>3010</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="E6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="4:15">
       <c r="D7">
-        <v>4010</v>
+        <v>3020</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" ht="39" spans="4:15">
       <c r="D8">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="4:15">
       <c r="D9">
-        <v>5010</v>
+        <v>4020</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="M9">
         <v>70</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="4:15">
       <c r="D10">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="4:12">
       <c r="D11">
-        <v>6010</v>
+        <v>5020</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="9:12">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="4:12">
+      <c r="D12">
+        <v>6010</v>
+      </c>
+      <c r="E12" t="s">
+        <v>92</v>
+      </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K12">
         <v>90</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="9:12">
@@ -2430,13 +3087,13 @@
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="11:12">
@@ -2444,7 +3101,7 @@
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="5:5">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -135,16 +135,16 @@
     <t>始まりの時</t>
   </si>
   <si>
-    <t>山岳遺跡</t>
-  </si>
-  <si>
-    <t>山岳遺跡・奥</t>
-  </si>
-  <si>
-    <t>森</t>
-  </si>
-  <si>
-    <t>森・地下洞窟</t>
+    <t>忘れられた山岳遺跡</t>
+  </si>
+  <si>
+    <t>忘れられた山岳遺跡・奥</t>
+  </si>
+  <si>
+    <t>月影の森</t>
+  </si>
+  <si>
+    <t>月影の森・地下洞窟</t>
   </si>
   <si>
     <t>ゲームの流れ</t>
@@ -343,15 +343,23 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -365,15 +373,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -387,8 +403,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -401,47 +426,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -457,7 +443,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -473,14 +473,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -496,7 +496,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -508,13 +550,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -526,31 +634,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -562,67 +652,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -634,49 +670,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -722,44 +722,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -782,6 +749,39 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
@@ -795,7 +795,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -804,7 +804,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -813,127 +813,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2285,7 +2285,7 @@
         <v>20</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>15</v>
@@ -2296,7 +2296,7 @@
         <v>20</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>15</v>
@@ -2307,7 +2307,7 @@
         <v>20</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>15</v>
@@ -2318,7 +2318,7 @@
         <v>20</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -2340,7 +2340,7 @@
         <v>21</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7">
         <v>15</v>
@@ -2351,7 +2351,7 @@
         <v>21</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8">
         <v>15</v>
@@ -2362,7 +2362,7 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>15</v>
@@ -2373,7 +2373,7 @@
         <v>21</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C10">
         <v>20</v>
@@ -2395,7 +2395,7 @@
         <v>30</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12">
         <v>15</v>
@@ -2406,7 +2406,7 @@
         <v>30</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13">
         <v>15</v>
@@ -2417,7 +2417,7 @@
         <v>30</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C14">
         <v>15</v>
@@ -2428,7 +2428,7 @@
         <v>30</v>
       </c>
       <c r="B15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -2439,7 +2439,7 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -2450,7 +2450,7 @@
         <v>31</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17">
         <v>15</v>
@@ -2461,7 +2461,7 @@
         <v>31</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18">
         <v>15</v>
@@ -2472,7 +2472,7 @@
         <v>31</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>15</v>
@@ -2483,7 +2483,7 @@
         <v>31</v>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -2494,7 +2494,7 @@
         <v>31</v>
       </c>
       <c r="B21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C21">
         <v>20</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="4"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="100">
   <si>
     <t>Id</t>
   </si>
@@ -60,12 +60,27 @@
     <t>BackGround</t>
   </si>
   <si>
+    <t>BossImage</t>
+  </si>
+  <si>
+    <t>BossTroopId</t>
+  </si>
+  <si>
     <t>RockCave2</t>
   </si>
   <si>
+    <t>""</t>
+  </si>
+  <si>
+    <t>Bee</t>
+  </si>
+  <si>
     <t>002-Woods01</t>
   </si>
   <si>
+    <t>Ammon</t>
+  </si>
+  <si>
     <t>DirtCave</t>
   </si>
   <si>
@@ -127,9 +142,6 @@
   </si>
   <si>
     <t>準備画面</t>
-  </si>
-  <si>
-    <t>""</t>
   </si>
   <si>
     <t>始まりの時</t>
@@ -319,8 +331,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -343,16 +355,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -366,30 +370,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -403,17 +391,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -427,47 +414,25 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -486,6 +451,53 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -496,19 +508,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -526,25 +580,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -556,7 +658,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -568,115 +682,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -722,44 +734,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -783,7 +760,42 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -795,16 +807,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -813,127 +825,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1272,14 +1284,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="5"/>
   <cols>
     <col min="4" max="4" width="10.3636363636364" customWidth="1"/>
-    <col min="13" max="13" width="32" customWidth="1"/>
+    <col min="6" max="6" width="11.8181818181818" customWidth="1"/>
+    <col min="7" max="7" width="8.45454545454546" customWidth="1"/>
+    <col min="13" max="13" width="13.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1319,8 +1333,14 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>10</v>
       </c>
@@ -1358,10 +1378,16 @@
         <v>100</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>15</v>
+      </c>
+      <c r="N2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>20</v>
       </c>
@@ -1399,10 +1425,16 @@
         <v>100</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>15</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>21</v>
       </c>
@@ -1440,10 +1472,16 @@
         <v>100</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>15</v>
+      </c>
+      <c r="N4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>30</v>
       </c>
@@ -1481,10 +1519,16 @@
         <v>100</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>18</v>
+      </c>
+      <c r="N5" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>31</v>
       </c>
@@ -1522,7 +1566,13 @@
         <v>100</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="N6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1534,7 +1584,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
@@ -1546,34 +1596,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1584,7 +1634,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>3010</v>
@@ -1617,20 +1667,20 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>3010</v>
       </c>
       <c r="F3">
-        <v>5010</v>
+        <v>4020</v>
       </c>
       <c r="G3" t="str">
         <f>INDEX(Define!E:E,MATCH(F3,Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>選択して仲間を増やす</v>
       </c>
       <c r="H3">
-        <v>1010</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1650,20 +1700,20 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>3010</v>
       </c>
       <c r="F4">
-        <v>2010</v>
+        <v>5010</v>
       </c>
       <c r="G4" t="str">
         <f>INDEX(Define!E:E,MATCH(F4,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1672,31 +1722,31 @@
         <v>0</v>
       </c>
       <c r="K4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D5">
         <v>3010</v>
       </c>
       <c r="F5">
-        <v>6010</v>
+        <v>2010</v>
       </c>
       <c r="G5" t="str">
         <f>INDEX(Define!E:E,MATCH(F5,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H5">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1705,7 +1755,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1713,7 +1763,7 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>9</v>
@@ -1722,7 +1772,11 @@
         <v>3010</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>6010</v>
+      </c>
+      <c r="G6" t="str">
+        <f>INDEX(Define!E:E,MATCH(F6,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H6">
         <v>79</v>
@@ -1745,40 +1799,36 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>3010</v>
       </c>
       <c r="F7">
-        <v>2020</v>
-      </c>
-      <c r="G7" t="str">
-        <f>INDEX(Define!E:E,MATCH(F7,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>3010</v>
@@ -1791,13 +1841,13 @@
         <v>ダンジョン移動</v>
       </c>
       <c r="H8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -1808,32 +1858,32 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>3010</v>
       </c>
       <c r="F9">
-        <v>5020</v>
+        <v>2020</v>
       </c>
       <c r="G9" t="str">
         <f>INDEX(Define!E:E,MATCH(F9,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H9">
-        <v>1020</v>
+        <v>20</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1844,20 +1894,20 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <v>3010</v>
       </c>
       <c r="F10">
-        <v>3010</v>
+        <v>5020</v>
       </c>
       <c r="G10" t="str">
         <f>INDEX(Define!E:E,MATCH(F10,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H10">
-        <v>2010</v>
+        <v>1020</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1874,26 +1924,26 @@
         <v>21</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>3010</v>
       </c>
       <c r="F11">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="G11" t="str">
         <f>INDEX(Define!E:E,MATCH(F11,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H11">
-        <v>1000</v>
+        <v>2010</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1904,35 +1954,35 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>3010</v>
       </c>
       <c r="F12">
-        <v>2010</v>
+        <v>3020</v>
       </c>
       <c r="G12" t="str">
         <f>INDEX(Define!E:E,MATCH(F12,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1940,29 +1990,29 @@
         <v>30</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>3010</v>
       </c>
       <c r="F13">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="G13" t="str">
         <f>INDEX(Define!E:E,MATCH(F13,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H13">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -1973,7 +2023,7 @@
         <v>30</v>
       </c>
       <c r="B14">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -1992,7 +2042,7 @@
         <v>31</v>
       </c>
       <c r="I14">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -2006,32 +2056,32 @@
         <v>30</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15">
         <v>3010</v>
       </c>
       <c r="F15">
-        <v>6010</v>
+        <v>2020</v>
       </c>
       <c r="G15" t="str">
         <f>INDEX(Define!E:E,MATCH(F15,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H15">
-        <v>612</v>
+        <v>31</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2039,16 +2089,20 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D16">
         <v>3010</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>6010</v>
+      </c>
+      <c r="G16" t="str">
+        <f>INDEX(Define!E:E,MATCH(F16,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H16">
         <v>612</v>
@@ -2068,23 +2122,19 @@
         <v>30</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D17">
         <v>3010</v>
       </c>
       <c r="F17">
-        <v>6010</v>
-      </c>
-      <c r="G17" t="str">
-        <f>INDEX(Define!E:E,MATCH(F17,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>86</v>
+        <v>612</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -2101,16 +2151,20 @@
         <v>30</v>
       </c>
       <c r="B18">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D18">
         <v>3010</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>6010</v>
+      </c>
+      <c r="G18" t="str">
+        <f>INDEX(Define!E:E,MATCH(F18,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H18">
         <v>86</v>
@@ -2127,35 +2181,31 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <v>3010</v>
       </c>
       <c r="F19">
-        <v>2020</v>
-      </c>
-      <c r="G19" t="str">
-        <f>INDEX(Define!E:E,MATCH(F19,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2163,7 +2213,7 @@
         <v>31</v>
       </c>
       <c r="B20">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -2182,7 +2232,7 @@
         <v>30</v>
       </c>
       <c r="I20">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <v>2</v>
@@ -2196,32 +2246,32 @@
         <v>31</v>
       </c>
       <c r="B21">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D21">
         <v>3010</v>
       </c>
       <c r="F21">
-        <v>5020</v>
+        <v>2020</v>
       </c>
       <c r="G21" t="str">
         <f>INDEX(Define!E:E,MATCH(F21,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H21">
-        <v>2010</v>
+        <v>30</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2229,31 +2279,64 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C22">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <v>3010</v>
       </c>
       <c r="F22">
-        <v>3010</v>
+        <v>5020</v>
       </c>
       <c r="G22" t="str">
         <f>INDEX(Define!E:E,MATCH(F22,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H22">
+        <v>2010</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23">
+        <v>31</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+      <c r="C23">
+        <v>13</v>
+      </c>
+      <c r="D23">
+        <v>3010</v>
+      </c>
+      <c r="F23">
+        <v>3010</v>
+      </c>
+      <c r="G23" t="str">
+        <f>INDEX(Define!E:E,MATCH(F23,Define!D:D))</f>
         <v>アーティファクト取得</v>
       </c>
-      <c r="H22">
+      <c r="H23">
         <v>2020</v>
       </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22" t="b">
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2274,10 +2357,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2517,25 +2600,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2585,10 +2668,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2596,10 +2679,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2607,10 +2690,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -2619,10 +2702,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -2631,10 +2714,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -2643,10 +2726,10 @@
         <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -2655,10 +2738,10 @@
         <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D7" s="3"/>
     </row>
@@ -2667,10 +2750,10 @@
         <v>1010</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D8" s="3"/>
     </row>
@@ -2679,10 +2762,10 @@
         <v>1020</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D9" s="3"/>
     </row>
@@ -2691,10 +2774,10 @@
         <v>1030</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D10" s="3"/>
     </row>
@@ -2703,10 +2786,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D11" s="3"/>
     </row>
@@ -2739,19 +2822,19 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2759,31 +2842,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -2791,34 +2874,34 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D3">
         <v>1010</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -2826,34 +2909,34 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D4">
         <v>2010</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:15">
@@ -2861,34 +2944,34 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D5">
         <v>2020</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="M5">
         <v>30</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -2896,34 +2979,34 @@
         <v>3010</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="4:15">
@@ -2931,28 +3014,28 @@
         <v>3020</v>
       </c>
       <c r="E7" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" ht="39" spans="4:15">
@@ -2960,28 +3043,28 @@
         <v>4010</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="4:15">
@@ -2989,28 +3072,28 @@
         <v>4020</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M9">
         <v>70</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="4:15">
@@ -3018,28 +3101,28 @@
         <v>5010</v>
       </c>
       <c r="E10" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="4:12">
@@ -3047,19 +3130,19 @@
         <v>5020</v>
       </c>
       <c r="E11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="4:12">
@@ -3067,19 +3150,19 @@
         <v>6010</v>
       </c>
       <c r="E12" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K12">
         <v>90</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="9:12">
@@ -3087,13 +3170,13 @@
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="11:12">
@@ -3101,7 +3184,7 @@
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="5:5">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -329,10 +329,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -356,12 +356,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -369,15 +377,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -391,11 +393,80 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -414,55 +485,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -471,29 +494,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -508,7 +508,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -520,19 +580,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -544,7 +628,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -556,19 +664,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,115 +676,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -702,17 +702,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -735,8 +740,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -759,28 +764,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -807,145 +807,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1584,7 +1584,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
@@ -1763,23 +1763,23 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="F6">
-        <v>6010</v>
+        <v>2010</v>
       </c>
       <c r="G6" t="str">
         <f>INDEX(Define!E:E,MATCH(F6,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H6">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1788,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1796,7 +1796,7 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>9</v>
@@ -1805,7 +1805,11 @@
         <v>3010</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>6010</v>
+      </c>
+      <c r="G7" t="str">
+        <f>INDEX(Define!E:E,MATCH(F7,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H7">
         <v>79</v>
@@ -1828,40 +1832,36 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>3010</v>
       </c>
       <c r="F8">
-        <v>2020</v>
-      </c>
-      <c r="G8" t="str">
-        <f>INDEX(Define!E:E,MATCH(F8,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>3010</v>
@@ -1874,13 +1874,13 @@
         <v>ダンジョン移動</v>
       </c>
       <c r="H9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1891,32 +1891,32 @@
         <v>21</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>3010</v>
       </c>
       <c r="F10">
-        <v>5020</v>
+        <v>2020</v>
       </c>
       <c r="G10" t="str">
         <f>INDEX(Define!E:E,MATCH(F10,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H10">
-        <v>1020</v>
+        <v>20</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1927,20 +1927,20 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>3010</v>
       </c>
       <c r="F11">
-        <v>3010</v>
+        <v>5020</v>
       </c>
       <c r="G11" t="str">
         <f>INDEX(Define!E:E,MATCH(F11,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H11">
-        <v>2010</v>
+        <v>1020</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1957,26 +1957,26 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>3010</v>
       </c>
       <c r="F12">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="G12" t="str">
         <f>INDEX(Define!E:E,MATCH(F12,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H12">
-        <v>1000</v>
+        <v>2010</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1987,35 +1987,35 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B13">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C13">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>3010</v>
       </c>
       <c r="F13">
-        <v>2010</v>
+        <v>3020</v>
       </c>
       <c r="G13" t="str">
         <f>INDEX(Define!E:E,MATCH(F13,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2023,29 +2023,29 @@
         <v>30</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>3010</v>
       </c>
       <c r="F14">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="G14" t="str">
         <f>INDEX(Define!E:E,MATCH(F14,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H14">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -2056,7 +2056,7 @@
         <v>30</v>
       </c>
       <c r="B15">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -2075,7 +2075,7 @@
         <v>31</v>
       </c>
       <c r="I15">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -2089,32 +2089,32 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16">
         <v>3010</v>
       </c>
       <c r="F16">
-        <v>6010</v>
+        <v>2020</v>
       </c>
       <c r="G16" t="str">
         <f>INDEX(Define!E:E,MATCH(F16,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H16">
-        <v>612</v>
+        <v>31</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2122,16 +2122,20 @@
         <v>30</v>
       </c>
       <c r="B17">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D17">
         <v>3010</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>6010</v>
+      </c>
+      <c r="G17" t="str">
+        <f>INDEX(Define!E:E,MATCH(F17,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H17">
         <v>612</v>
@@ -2151,23 +2155,19 @@
         <v>30</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D18">
         <v>3010</v>
       </c>
       <c r="F18">
-        <v>6010</v>
-      </c>
-      <c r="G18" t="str">
-        <f>INDEX(Define!E:E,MATCH(F18,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>86</v>
+        <v>612</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -2184,16 +2184,20 @@
         <v>30</v>
       </c>
       <c r="B19">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19">
         <v>3010</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>6010</v>
+      </c>
+      <c r="G19" t="str">
+        <f>INDEX(Define!E:E,MATCH(F19,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H19">
         <v>86</v>
@@ -2210,35 +2214,31 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>3010</v>
       </c>
       <c r="F20">
-        <v>2020</v>
-      </c>
-      <c r="G20" t="str">
-        <f>INDEX(Define!E:E,MATCH(F20,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2246,7 +2246,7 @@
         <v>31</v>
       </c>
       <c r="B21">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -2265,7 +2265,7 @@
         <v>30</v>
       </c>
       <c r="I21">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <v>2</v>
@@ -2279,32 +2279,32 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D22">
         <v>3010</v>
       </c>
       <c r="F22">
-        <v>5020</v>
+        <v>2020</v>
       </c>
       <c r="G22" t="str">
         <f>INDEX(Define!E:E,MATCH(F22,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H22">
-        <v>2010</v>
+        <v>30</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2312,31 +2312,64 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C23">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>3010</v>
       </c>
       <c r="F23">
-        <v>3010</v>
+        <v>5020</v>
       </c>
       <c r="G23" t="str">
         <f>INDEX(Define!E:E,MATCH(F23,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H23">
+        <v>2010</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24">
+        <v>31</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <v>13</v>
+      </c>
+      <c r="D24">
+        <v>3010</v>
+      </c>
+      <c r="F24">
+        <v>3010</v>
+      </c>
+      <c r="G24" t="str">
+        <f>INDEX(Define!E:E,MATCH(F24,Define!D:D))</f>
         <v>アーティファクト取得</v>
       </c>
-      <c r="H23">
+      <c r="H24">
         <v>2020</v>
       </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23" t="b">
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -329,10 +329,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -356,30 +356,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -401,6 +392,66 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -410,7 +461,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -427,28 +478,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -456,29 +486,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -486,14 +494,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -508,19 +508,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -538,13 +586,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -556,13 +652,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,121 +682,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -702,22 +702,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -740,8 +735,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -764,23 +759,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -799,6 +788,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -807,145 +807,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1584,7 +1584,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
@@ -1960,20 +1960,20 @@
         <v>10</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>3010</v>
       </c>
       <c r="F12">
-        <v>3010</v>
+        <v>6010</v>
       </c>
       <c r="G12" t="str">
         <f>INDEX(Define!E:E,MATCH(F12,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H12">
-        <v>2010</v>
+        <v>23</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1990,26 +1990,22 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D13">
         <v>3010</v>
       </c>
       <c r="F13">
-        <v>3020</v>
-      </c>
-      <c r="G13" t="str">
-        <f>INDEX(Define!E:E,MATCH(F13,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2020,26 +2016,26 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>3010</v>
       </c>
       <c r="F14">
-        <v>2010</v>
+        <v>3010</v>
       </c>
       <c r="G14" t="str">
         <f>INDEX(Define!E:E,MATCH(F14,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>2010</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -2048,40 +2044,40 @@
         <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D15">
         <v>3010</v>
       </c>
       <c r="F15">
-        <v>2020</v>
+        <v>3020</v>
       </c>
       <c r="G15" t="str">
         <f>INDEX(Define!E:E,MATCH(F15,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H15">
-        <v>31</v>
+        <v>1000</v>
       </c>
       <c r="I15">
         <v>1</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2089,29 +2085,29 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>3010</v>
       </c>
       <c r="F16">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="G16" t="str">
         <f>INDEX(Define!E:E,MATCH(F16,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H16">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -2125,29 +2121,29 @@
         <v>1</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17">
         <v>3010</v>
       </c>
       <c r="F17">
-        <v>6010</v>
+        <v>2020</v>
       </c>
       <c r="G17" t="str">
         <f>INDEX(Define!E:E,MATCH(F17,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H17">
-        <v>612</v>
+        <v>31</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2155,28 +2151,32 @@
         <v>30</v>
       </c>
       <c r="B18">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D18">
         <v>3010</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>2020</v>
+      </c>
+      <c r="G18" t="str">
+        <f>INDEX(Define!E:E,MATCH(F18,Define!D:D))</f>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H18">
-        <v>612</v>
+        <v>31</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2187,7 +2187,7 @@
         <v>1</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19">
         <v>3010</v>
@@ -2200,7 +2200,7 @@
         <v>指定のイベントマスを消す</v>
       </c>
       <c r="H19">
-        <v>86</v>
+        <v>612</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -2217,10 +2217,10 @@
         <v>30</v>
       </c>
       <c r="B20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D20">
         <v>3010</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>86</v>
+        <v>612</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -2243,68 +2243,64 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21">
         <v>3010</v>
       </c>
       <c r="F21">
-        <v>2020</v>
+        <v>6010</v>
       </c>
       <c r="G21" t="str">
         <f>INDEX(Define!E:E,MATCH(F21,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H21">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>3010</v>
       </c>
       <c r="F22">
-        <v>2020</v>
-      </c>
-      <c r="G22" t="str">
-        <f>INDEX(Define!E:E,MATCH(F22,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="I22">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2312,32 +2308,32 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D23">
         <v>3010</v>
       </c>
       <c r="F23">
-        <v>5020</v>
+        <v>2020</v>
       </c>
       <c r="G23" t="str">
         <f>INDEX(Define!E:E,MATCH(F23,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H23">
-        <v>2010</v>
+        <v>30</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2345,31 +2341,97 @@
         <v>31</v>
       </c>
       <c r="B24">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C24">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <v>3010</v>
       </c>
       <c r="F24">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="G24" t="str">
         <f>INDEX(Define!E:E,MATCH(F24,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H24">
+        <v>30</v>
+      </c>
+      <c r="I24">
+        <v>14</v>
+      </c>
+      <c r="J24">
+        <v>2</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25">
+        <v>31</v>
+      </c>
+      <c r="B25">
+        <v>11</v>
+      </c>
+      <c r="C25">
+        <v>7</v>
+      </c>
+      <c r="D25">
+        <v>3010</v>
+      </c>
+      <c r="F25">
+        <v>5020</v>
+      </c>
+      <c r="G25" t="str">
+        <f>INDEX(Define!E:E,MATCH(F25,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H25">
+        <v>2010</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26">
+        <v>31</v>
+      </c>
+      <c r="B26">
+        <v>8</v>
+      </c>
+      <c r="C26">
+        <v>13</v>
+      </c>
+      <c r="D26">
+        <v>3010</v>
+      </c>
+      <c r="F26">
+        <v>3010</v>
+      </c>
+      <c r="G26" t="str">
+        <f>INDEX(Define!E:E,MATCH(F26,Define!D:D))</f>
         <v>アーティファクト取得</v>
       </c>
-      <c r="H24">
+      <c r="H26">
         <v>2020</v>
       </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24" t="b">
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -329,10 +329,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -356,14 +356,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -376,24 +376,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -407,16 +400,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -429,8 +421,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -441,6 +434,14 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -461,18 +462,17 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -484,16 +484,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -508,7 +508,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -520,7 +520,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -538,145 +658,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -692,6 +680,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -699,6 +699,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -717,17 +732,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -752,15 +761,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -807,145 +807,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1410,10 +1410,10 @@
         <v>30</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J3">
         <v>1010</v>
@@ -1457,10 +1457,10 @@
         <v>30</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J4">
         <v>1010</v>
@@ -1504,10 +1504,10 @@
         <v>30</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J5">
         <v>1020</v>
@@ -1551,10 +1551,10 @@
         <v>30</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J6">
         <v>1020</v>
@@ -1957,10 +1957,10 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>3010</v>
@@ -1973,7 +1973,7 @@
         <v>指定のイベントマスを消す</v>
       </c>
       <c r="H12">
-        <v>23</v>
+        <v>213</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>2</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D13">
         <v>3010</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>23</v>
+        <v>213</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2019,10 +2019,10 @@
         <v>21</v>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>3010</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="101">
   <si>
     <t>Id</t>
   </si>
@@ -157,6 +157,9 @@
   </si>
   <si>
     <t>月影の森・地下洞窟</t>
+  </si>
+  <si>
+    <t>月影の森・採掘上跡</t>
   </si>
   <si>
     <t>ゲームの流れ</t>
@@ -329,10 +332,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -355,8 +358,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,18 +373,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -392,9 +396,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -414,6 +433,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -423,31 +450,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -469,16 +472,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -486,6 +482,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -508,7 +511,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -520,25 +535,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,13 +547,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -568,25 +571,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,49 +583,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -658,13 +613,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,13 +673,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -703,16 +706,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -728,6 +731,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -750,30 +768,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -791,6 +785,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -807,145 +810,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1284,8 +1287,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="5"/>
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="6"/>
   <cols>
     <col min="4" max="4" width="10.3636363636364" customWidth="1"/>
     <col min="6" max="6" width="11.8181818181818" customWidth="1"/>
@@ -1495,7 +1498,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -1542,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1572,6 +1575,53 @@
         <v>19</v>
       </c>
       <c r="O6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7">
+        <v>32</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>30</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>12</v>
+      </c>
+      <c r="J7">
+        <v>1020</v>
+      </c>
+      <c r="K7">
+        <v>3010</v>
+      </c>
+      <c r="L7">
+        <v>100</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
         <v>0</v>
       </c>
     </row>
@@ -1584,7 +1634,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
@@ -2088,7 +2138,7 @@
         <v>8</v>
       </c>
       <c r="C16">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D16">
         <v>3010</v>
@@ -2151,10 +2201,10 @@
         <v>30</v>
       </c>
       <c r="B18">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D18">
         <v>3010</v>
@@ -2170,10 +2220,10 @@
         <v>31</v>
       </c>
       <c r="I18">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
@@ -2184,32 +2234,32 @@
         <v>30</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>3010</v>
       </c>
       <c r="F19">
-        <v>6010</v>
+        <v>2020</v>
       </c>
       <c r="G19" t="str">
         <f>INDEX(Define!E:E,MATCH(F19,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H19">
-        <v>612</v>
+        <v>32</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2217,7 +2267,7 @@
         <v>30</v>
       </c>
       <c r="B20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>12</v>
@@ -2226,7 +2276,11 @@
         <v>3010</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>6010</v>
+      </c>
+      <c r="G20" t="str">
+        <f>INDEX(Define!E:E,MATCH(F20,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H20">
         <v>612</v>
@@ -2246,23 +2300,19 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D21">
         <v>3010</v>
       </c>
       <c r="F21">
-        <v>6010</v>
-      </c>
-      <c r="G21" t="str">
-        <f>INDEX(Define!E:E,MATCH(F21,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>86</v>
+        <v>612</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -2276,31 +2326,35 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
+        <v>31</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>3010</v>
+      </c>
+      <c r="F22">
+        <v>2020</v>
+      </c>
+      <c r="G22" t="str">
+        <f>INDEX(Define!E:E,MATCH(F22,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H22">
         <v>30</v>
       </c>
-      <c r="B22">
-        <v>8</v>
-      </c>
-      <c r="C22">
-        <v>6</v>
-      </c>
-      <c r="D22">
-        <v>3010</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>86</v>
-      </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2308,7 +2362,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -2327,10 +2381,10 @@
         <v>30</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -2341,32 +2395,32 @@
         <v>31</v>
       </c>
       <c r="B24">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D24">
         <v>3010</v>
       </c>
       <c r="F24">
-        <v>2020</v>
+        <v>6010</v>
       </c>
       <c r="G24" t="str">
         <f>INDEX(Define!E:E,MATCH(F24,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H24">
-        <v>30</v>
+        <v>1310</v>
       </c>
       <c r="I24">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2374,23 +2428,19 @@
         <v>31</v>
       </c>
       <c r="B25">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25">
         <v>3010</v>
       </c>
       <c r="F25">
-        <v>5020</v>
-      </c>
-      <c r="G25" t="str">
-        <f>INDEX(Define!E:E,MATCH(F25,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>2010</v>
+        <v>1310</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -2410,28 +2460,127 @@
         <v>8</v>
       </c>
       <c r="C26">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D26">
         <v>3010</v>
       </c>
       <c r="F26">
-        <v>3010</v>
+        <v>5020</v>
       </c>
       <c r="G26" t="str">
         <f>INDEX(Define!E:E,MATCH(F26,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H26">
+        <v>2010</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27">
+        <v>31</v>
+      </c>
+      <c r="B27">
+        <v>8</v>
+      </c>
+      <c r="C27">
+        <v>13</v>
+      </c>
+      <c r="D27">
+        <v>3010</v>
+      </c>
+      <c r="F27">
+        <v>3010</v>
+      </c>
+      <c r="G27" t="str">
+        <f>INDEX(Define!E:E,MATCH(F27,Define!D:D))</f>
         <v>アーティファクト取得</v>
       </c>
-      <c r="H26">
+      <c r="H27">
         <v>2020</v>
       </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26" t="b">
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28">
+        <v>32</v>
+      </c>
+      <c r="B28">
+        <v>4</v>
+      </c>
+      <c r="C28">
+        <v>9</v>
+      </c>
+      <c r="D28">
+        <v>3010</v>
+      </c>
+      <c r="F28">
+        <v>2020</v>
+      </c>
+      <c r="G28" t="str">
+        <f>INDEX(Define!E:E,MATCH(F28,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H28">
+        <v>30</v>
+      </c>
+      <c r="I28">
+        <v>4</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29">
+        <v>32</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29">
+        <v>3010</v>
+      </c>
+      <c r="F29">
+        <v>3010</v>
+      </c>
+      <c r="G29" t="str">
+        <f>INDEX(Define!E:E,MATCH(F29,Define!D:D))</f>
+        <v>アーティファクト取得</v>
+      </c>
+      <c r="H29">
+        <v>2030</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2444,7 +2593,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2573,7 +2722,7 @@
         <v>30</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <v>15</v>
@@ -2584,7 +2733,7 @@
         <v>30</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13">
         <v>15</v>
@@ -2606,7 +2755,7 @@
         <v>30</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -2628,7 +2777,7 @@
         <v>31</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17">
         <v>15</v>
@@ -2639,7 +2788,7 @@
         <v>31</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18">
         <v>15</v>
@@ -2672,9 +2821,64 @@
         <v>31</v>
       </c>
       <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>32</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>32</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>32</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>32</v>
+      </c>
+      <c r="B25">
+        <v>7</v>
+      </c>
+      <c r="C25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>32</v>
+      </c>
+      <c r="B26">
         <v>9</v>
       </c>
-      <c r="C21">
+      <c r="C26">
         <v>20</v>
       </c>
     </row>
@@ -2751,7 +2955,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="34.1818181818182" customWidth="1"/>
@@ -2842,19 +3046,19 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>1010</v>
+        <v>32</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>47</v>
@@ -2866,7 +3070,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>48</v>
@@ -2878,7 +3082,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
-        <v>10010</v>
+        <v>1030</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -2888,15 +3092,27 @@
       </c>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="3:4">
-      <c r="C12" s="3"/>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>10010</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="D12" s="3"/>
     </row>
-    <row r="13" spans="3:3">
+    <row r="13" spans="3:4">
       <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="3:3">
+      <c r="C15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2923,13 +3139,13 @@
         <v>25</v>
       </c>
       <c r="I1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2937,31 +3153,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -2969,34 +3185,34 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3">
         <v>1010</v>
       </c>
       <c r="E3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -3004,34 +3220,34 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D4">
         <v>2010</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:15">
@@ -3039,34 +3255,34 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D5">
         <v>2020</v>
       </c>
       <c r="E5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M5">
         <v>30</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -3074,34 +3290,34 @@
         <v>3010</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="4:15">
@@ -3109,28 +3325,28 @@
         <v>3020</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" ht="39" spans="4:15">
@@ -3138,28 +3354,28 @@
         <v>4010</v>
       </c>
       <c r="E8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="4:15">
@@ -3167,28 +3383,28 @@
         <v>4020</v>
       </c>
       <c r="E9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M9">
         <v>70</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="4:15">
@@ -3196,28 +3412,28 @@
         <v>5010</v>
       </c>
       <c r="E10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="4:12">
@@ -3225,19 +3441,19 @@
         <v>5020</v>
       </c>
       <c r="E11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="4:12">
@@ -3245,19 +3461,19 @@
         <v>6010</v>
       </c>
       <c r="E12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K12">
         <v>90</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="9:12">
@@ -3265,13 +3481,13 @@
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="11:12">
@@ -3279,7 +3495,7 @@
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="5:5">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="102">
   <si>
     <t>Id</t>
   </si>
@@ -162,7 +162,7 @@
     <t>月影の森・採掘上跡</t>
   </si>
   <si>
-    <t>ゲームの流れ</t>
+    <t>忘却の洞窟</t>
   </si>
   <si>
     <t>有利なバトルの進め方</t>
@@ -271,7 +271,7 @@
     <t>射程内に攻撃可能な敵がいれば攻撃、いなければ一定のルートを移動。</t>
   </si>
   <si>
-    <t>仲間を増やす</t>
+    <t>魔法入手</t>
   </si>
   <si>
     <t>Actor</t>
@@ -285,40 +285,43 @@
 隣接など攻撃可能でないと挑発は出来ない。</t>
   </si>
   <si>
+    <t>仲間を増やす</t>
+  </si>
+  <si>
+    <t>Rebirth</t>
+  </si>
+  <si>
+    <t>移動</t>
+  </si>
+  <si>
+    <t>特定の目標に向かって移動。攻撃してこない。</t>
+  </si>
+  <si>
     <t>選択して仲間を増やす</t>
   </si>
   <si>
-    <t>Rebirth</t>
-  </si>
-  <si>
-    <t>移動</t>
-  </si>
-  <si>
-    <t>特定の目標に向かって移動。攻撃してこない。</t>
+    <t>SelectActor</t>
+  </si>
+  <si>
+    <t>離脱</t>
+  </si>
+  <si>
+    <t>離脱ポイントへ向かう。攻撃してこない。</t>
   </si>
   <si>
     <t>強制戦闘</t>
   </si>
   <si>
-    <t>SelectActor</t>
-  </si>
-  <si>
-    <t>離脱</t>
-  </si>
-  <si>
-    <t>離脱ポイントへ向かう。攻撃してこない。</t>
+    <t>Shop</t>
   </si>
   <si>
     <t>強制ボス戦闘</t>
   </si>
   <si>
-    <t>Shop</t>
+    <t>Gacha</t>
   </si>
   <si>
     <t>指定のイベントマスを消す</t>
-  </si>
-  <si>
-    <t>Gacha</t>
   </si>
   <si>
     <t>Group</t>
@@ -332,10 +335,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -358,9 +361,29 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,15 +397,16 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -390,7 +414,14 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -405,43 +436,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -449,8 +443,16 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -465,7 +467,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -480,8 +482,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -511,19 +514,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,13 +538,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -559,7 +586,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,7 +658,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,49 +670,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -637,37 +682,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -679,19 +694,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -706,21 +709,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -731,6 +719,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -750,11 +747,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -764,6 +767,15 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -785,15 +797,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -810,16 +813,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -828,127 +831,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1287,8 +1290,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O7"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="6"/>
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="7"/>
   <cols>
     <col min="4" max="4" width="10.3636363636364" customWidth="1"/>
     <col min="6" max="6" width="11.8181818181818" customWidth="1"/>
@@ -1625,6 +1628,53 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8" spans="1:15">
+      <c r="A8">
+        <v>1010</v>
+      </c>
+      <c r="B8">
+        <v>1010</v>
+      </c>
+      <c r="C8">
+        <v>101</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>30</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>1210</v>
+      </c>
+      <c r="K8">
+        <v>3010</v>
+      </c>
+      <c r="L8">
+        <v>100</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1634,7 +1684,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
@@ -2460,20 +2510,20 @@
         <v>8</v>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D26">
         <v>3010</v>
       </c>
       <c r="F26">
-        <v>5020</v>
+        <v>3010</v>
       </c>
       <c r="G26" t="str">
         <f>INDEX(Define!E:E,MATCH(F26,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H26">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -2487,35 +2537,35 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C27">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D27">
         <v>3010</v>
       </c>
       <c r="F27">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="G27" t="str">
         <f>INDEX(Define!E:E,MATCH(F27,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H27">
-        <v>2020</v>
+        <v>30</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2526,29 +2576,29 @@
         <v>4</v>
       </c>
       <c r="C28">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D28">
         <v>3010</v>
       </c>
       <c r="F28">
-        <v>2020</v>
+        <v>5020</v>
       </c>
       <c r="G28" t="str">
         <f>INDEX(Define!E:E,MATCH(F28,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H28">
-        <v>30</v>
+        <v>2010</v>
       </c>
       <c r="I28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2581,6 +2631,39 @@
         <v>0</v>
       </c>
       <c r="K29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30">
+        <v>1010</v>
+      </c>
+      <c r="B30">
+        <v>10</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="D30">
+        <v>3010</v>
+      </c>
+      <c r="F30">
+        <v>3030</v>
+      </c>
+      <c r="G30" t="str">
+        <f>INDEX(Define!E:E,MATCH(F30,Define!D:D))</f>
+        <v>魔法入手</v>
+      </c>
+      <c r="H30">
+        <v>30010</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2593,7 +2676,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2879,6 +2962,50 @@
         <v>9</v>
       </c>
       <c r="C26">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>1010</v>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+      <c r="C27">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>1010</v>
+      </c>
+      <c r="B28">
+        <v>6</v>
+      </c>
+      <c r="C28">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>1010</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>1010</v>
+      </c>
+      <c r="B30">
+        <v>7</v>
+      </c>
+      <c r="C30">
         <v>20</v>
       </c>
     </row>
@@ -3351,7 +3478,7 @@
     </row>
     <row r="8" ht="39" spans="4:15">
       <c r="D8">
-        <v>4010</v>
+        <v>3030</v>
       </c>
       <c r="E8" t="s">
         <v>83</v>
@@ -3380,7 +3507,7 @@
     </row>
     <row r="9" spans="4:15">
       <c r="D9">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="E9" t="s">
         <v>87</v>
@@ -3409,7 +3536,7 @@
     </row>
     <row r="10" spans="4:15">
       <c r="D10">
-        <v>5010</v>
+        <v>4020</v>
       </c>
       <c r="E10" t="s">
         <v>91</v>
@@ -3438,7 +3565,7 @@
     </row>
     <row r="11" spans="4:12">
       <c r="D11">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="E11" t="s">
         <v>95</v>
@@ -3458,7 +3585,7 @@
     </row>
     <row r="12" spans="4:12">
       <c r="D12">
-        <v>6010</v>
+        <v>5020</v>
       </c>
       <c r="E12" t="s">
         <v>97</v>
@@ -3476,18 +3603,24 @@
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="9:12">
+    <row r="13" spans="4:12">
+      <c r="D13">
+        <v>6010</v>
+      </c>
+      <c r="E13" t="s">
+        <v>99</v>
+      </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="11:12">
@@ -3495,7 +3628,7 @@
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="5:5">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="104">
   <si>
     <t>Id</t>
   </si>
@@ -33,6 +33,9 @@
     <t>Selectable</t>
   </si>
   <si>
+    <t>Chapter</t>
+  </si>
+  <si>
     <t>StageLv</t>
   </si>
   <si>
@@ -84,6 +87,9 @@
     <t>DirtCave</t>
   </si>
   <si>
+    <t>NA_Background image_Fantasy_027</t>
+  </si>
+  <si>
     <t>PositionX</t>
   </si>
   <si>
@@ -162,10 +168,10 @@
     <t>月影の森・採掘上跡</t>
   </si>
   <si>
+    <t>亡国の廃墟宮殿</t>
+  </si>
+  <si>
     <t>忘却の洞窟</t>
-  </si>
-  <si>
-    <t>有利なバトルの進め方</t>
   </si>
   <si>
     <t>ユニットの強化</t>
@@ -335,9 +341,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
@@ -361,13 +367,7 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -376,7 +376,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -390,17 +390,39 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -412,9 +434,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -428,22 +449,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -458,25 +472,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -490,8 +487,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -499,7 +505,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -514,7 +520,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -526,13 +544,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -544,13 +556,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -562,43 +610,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -616,31 +640,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,7 +664,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -670,31 +694,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -705,6 +711,17 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -727,7 +744,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -743,39 +769,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -797,11 +790,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -813,133 +819,124 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -948,10 +945,19 @@
     <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1290,16 +1296,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="7"/>
+  <dimension ref="A1:P10"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
-    <col min="4" max="4" width="10.3636363636364" customWidth="1"/>
-    <col min="6" max="6" width="11.8181818181818" customWidth="1"/>
-    <col min="7" max="7" width="8.45454545454546" customWidth="1"/>
-    <col min="13" max="13" width="13.2727272727273" customWidth="1"/>
+    <col min="4" max="5" width="10.3636363636364" customWidth="1"/>
+    <col min="7" max="7" width="11.8181818181818" customWidth="1"/>
+    <col min="8" max="8" width="8.45454545454546" customWidth="1"/>
+    <col min="14" max="14" width="13.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1315,10 +1321,10 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
@@ -1345,8 +1351,11 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>10</v>
       </c>
@@ -1360,17 +1369,17 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>30</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
       <c r="I2">
         <v>0</v>
       </c>
@@ -1378,22 +1387,25 @@
         <v>0</v>
       </c>
       <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>2010</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>100</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="N2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="O2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>20</v>
       </c>
@@ -1410,37 +1422,40 @@
         <v>1</v>
       </c>
       <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>30</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>6</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>12</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>1010</v>
       </c>
-      <c r="K3">
-        <v>3010</v>
-      </c>
       <c r="L3">
+        <v>3010</v>
+      </c>
+      <c r="M3">
         <v>100</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N3" t="s">
-        <v>17</v>
-      </c>
-      <c r="O3">
+      <c r="N3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3">
         <v>1020</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>21</v>
       </c>
@@ -1457,37 +1472,40 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>30</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>6</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>12</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>1010</v>
       </c>
-      <c r="K4">
-        <v>3010</v>
-      </c>
       <c r="L4">
+        <v>3010</v>
+      </c>
+      <c r="M4">
         <v>100</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" t="s">
+        <v>18</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>30</v>
       </c>
@@ -1501,40 +1519,43 @@
         <v>1</v>
       </c>
       <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>5</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>30</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>6</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>12</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>1020</v>
       </c>
-      <c r="K5">
-        <v>3010</v>
-      </c>
       <c r="L5">
+        <v>3010</v>
+      </c>
+      <c r="M5">
         <v>100</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="N5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P5">
         <v>2010</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>31</v>
       </c>
@@ -1548,40 +1569,43 @@
         <v>0</v>
       </c>
       <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>5</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>30</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>6</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>12</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>1020</v>
       </c>
-      <c r="K6">
-        <v>3010</v>
-      </c>
       <c r="L6">
+        <v>3010</v>
+      </c>
+      <c r="M6">
         <v>100</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="N6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O6" t="s">
         <v>20</v>
       </c>
-      <c r="N6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>32</v>
       </c>
@@ -1595,83 +1619,189 @@
         <v>0</v>
       </c>
       <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
         <v>5</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>30</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>6</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>12</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>1020</v>
       </c>
-      <c r="K7">
-        <v>3010</v>
-      </c>
       <c r="L7">
+        <v>3010</v>
+      </c>
+      <c r="M7">
         <v>100</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="N7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" t="s">
+        <v>20</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>40</v>
+      </c>
+      <c r="B8">
+        <v>40</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>30</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>1030</v>
+      </c>
+      <c r="L8">
+        <v>3010</v>
+      </c>
+      <c r="M8">
+        <v>100</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O8" t="s">
+        <v>20</v>
+      </c>
+      <c r="P8">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>1010</v>
+      </c>
+      <c r="B9">
+        <v>1010</v>
+      </c>
+      <c r="C9">
+        <v>101</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>30</v>
+      </c>
+      <c r="I9">
+        <v>6</v>
+      </c>
+      <c r="J9">
+        <v>12</v>
+      </c>
+      <c r="K9">
+        <v>1210</v>
+      </c>
+      <c r="L9">
+        <v>3010</v>
+      </c>
+      <c r="M9">
+        <v>100</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O9" t="s">
         <v>18</v>
       </c>
-      <c r="N7" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8">
-        <v>1010</v>
-      </c>
-      <c r="B8">
-        <v>1010</v>
-      </c>
-      <c r="C8">
-        <v>101</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>1020</v>
+      </c>
+      <c r="B10">
+        <v>1020</v>
+      </c>
+      <c r="C10">
+        <v>102</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
         <v>2</v>
       </c>
-      <c r="G8">
+      <c r="F10">
+        <v>6</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
         <v>30</v>
       </c>
-      <c r="H8">
+      <c r="I10">
         <v>6</v>
       </c>
-      <c r="I8">
+      <c r="J10">
         <v>12</v>
       </c>
-      <c r="J8">
+      <c r="K10">
         <v>1210</v>
       </c>
-      <c r="K8">
-        <v>3010</v>
-      </c>
-      <c r="L8">
+      <c r="L10">
+        <v>3010</v>
+      </c>
+      <c r="M10">
         <v>100</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N8" t="s">
-        <v>17</v>
-      </c>
-      <c r="O8">
+      <c r="N10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P10">
         <v>0</v>
       </c>
     </row>
@@ -1684,7 +1814,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
@@ -1696,34 +1826,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2507,10 +2637,10 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D26">
         <v>3010</v>
@@ -2636,34 +2766,265 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30">
-        <v>1010</v>
+        <v>40</v>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D30">
         <v>3010</v>
       </c>
       <c r="F30">
-        <v>3030</v>
+        <v>2010</v>
       </c>
       <c r="G30" t="str">
         <f>INDEX(Define!E:E,MATCH(F30,Define!D:D))</f>
+        <v>ダンジョンから出る</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31">
+        <v>1010</v>
+      </c>
+      <c r="B31">
+        <v>13</v>
+      </c>
+      <c r="C31">
+        <v>13</v>
+      </c>
+      <c r="D31">
+        <v>3010</v>
+      </c>
+      <c r="F31">
+        <v>2010</v>
+      </c>
+      <c r="G31" t="str">
+        <f>INDEX(Define!E:E,MATCH(F31,Define!D:D))</f>
+        <v>ダンジョンから出る</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32">
+        <v>1010</v>
+      </c>
+      <c r="B32">
+        <v>10</v>
+      </c>
+      <c r="C32">
+        <v>4</v>
+      </c>
+      <c r="D32">
+        <v>3010</v>
+      </c>
+      <c r="F32">
+        <v>3030</v>
+      </c>
+      <c r="G32" t="str">
+        <f>INDEX(Define!E:E,MATCH(F32,Define!D:D))</f>
         <v>魔法入手</v>
       </c>
-      <c r="H30">
+      <c r="H32">
         <v>30010</v>
       </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30" t="b">
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33">
+        <v>1020</v>
+      </c>
+      <c r="B33">
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <v>8</v>
+      </c>
+      <c r="D33">
+        <v>3010</v>
+      </c>
+      <c r="F33">
+        <v>2010</v>
+      </c>
+      <c r="G33" t="str">
+        <f>INDEX(Define!E:E,MATCH(F33,Define!D:D))</f>
+        <v>ダンジョンから出る</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34">
+        <v>1020</v>
+      </c>
+      <c r="B34">
+        <v>12</v>
+      </c>
+      <c r="C34">
+        <v>12</v>
+      </c>
+      <c r="D34">
+        <v>3010</v>
+      </c>
+      <c r="F34">
+        <v>3030</v>
+      </c>
+      <c r="G34" t="str">
+        <f>INDEX(Define!E:E,MATCH(F34,Define!D:D))</f>
+        <v>魔法入手</v>
+      </c>
+      <c r="H34">
+        <v>30020</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35">
+        <v>1020</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>3010</v>
+      </c>
+      <c r="F35">
+        <v>3020</v>
+      </c>
+      <c r="G35" t="str">
+        <f>INDEX(Define!E:E,MATCH(F35,Define!D:D))</f>
+        <v>アイテム取得</v>
+      </c>
+      <c r="H35">
+        <v>11010</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36">
+        <v>1020</v>
+      </c>
+      <c r="B36">
+        <v>9</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+      <c r="D36">
+        <v>3010</v>
+      </c>
+      <c r="F36">
+        <v>3020</v>
+      </c>
+      <c r="G36" t="str">
+        <f>INDEX(Define!E:E,MATCH(F36,Define!D:D))</f>
+        <v>アイテム取得</v>
+      </c>
+      <c r="H36">
+        <v>11020</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37">
+        <v>1020</v>
+      </c>
+      <c r="B37">
+        <v>10</v>
+      </c>
+      <c r="C37">
+        <v>12</v>
+      </c>
+      <c r="D37">
+        <v>3010</v>
+      </c>
+      <c r="F37">
+        <v>3020</v>
+      </c>
+      <c r="G37" t="str">
+        <f>INDEX(Define!E:E,MATCH(F37,Define!D:D))</f>
+        <v>アイテム取得</v>
+      </c>
+      <c r="H37">
+        <v>11030</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2676,7 +3037,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2684,10 +3045,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2967,10 +3328,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>1010</v>
+        <v>40</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27">
         <v>15</v>
@@ -2981,7 +3342,7 @@
         <v>1010</v>
       </c>
       <c r="B28">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C28">
         <v>15</v>
@@ -2992,10 +3353,10 @@
         <v>1010</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C29">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -3003,9 +3364,64 @@
         <v>1010</v>
       </c>
       <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>1010</v>
+      </c>
+      <c r="B31">
         <v>7</v>
       </c>
-      <c r="C30">
+      <c r="C31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>1020</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>1020</v>
+      </c>
+      <c r="B33">
+        <v>6</v>
+      </c>
+      <c r="C33">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>1020</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>1020</v>
+      </c>
+      <c r="B35">
+        <v>7</v>
+      </c>
+      <c r="C35">
         <v>20</v>
       </c>
     </row>
@@ -3026,25 +3442,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3082,7 +3498,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="34.1818181818182" customWidth="1"/>
@@ -3094,10 +3510,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3105,10 +3521,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3116,10 +3532,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3128,10 +3544,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="3"/>
     </row>
@@ -3140,10 +3556,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -3152,10 +3568,10 @@
         <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -3164,10 +3580,10 @@
         <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="3"/>
     </row>
@@ -3176,70 +3592,82 @@
         <v>32</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>1010</v>
+        <v>40</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>16</v>
+        <v>49</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="D9" s="3"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
+        <v>1030</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
         <v>10010</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="3:4">
-      <c r="C13" s="3"/>
+      <c r="B13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" spans="3:3">
+    <row r="14" spans="3:4">
       <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" spans="3:3">
       <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3260,19 +3688,19 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -3280,31 +3708,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -3312,34 +3740,34 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D3">
         <v>1010</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -3347,34 +3775,34 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D4">
         <v>2010</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:15">
@@ -3382,34 +3810,34 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D5">
         <v>2020</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M5">
         <v>30</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -3417,34 +3845,34 @@
         <v>3010</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="4:15">
@@ -3452,28 +3880,28 @@
         <v>3020</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" ht="39" spans="4:15">
@@ -3481,28 +3909,28 @@
         <v>3030</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="4:15">
@@ -3510,28 +3938,28 @@
         <v>4010</v>
       </c>
       <c r="E9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M9">
         <v>70</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="4:15">
@@ -3539,28 +3967,28 @@
         <v>4020</v>
       </c>
       <c r="E10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="4:12">
@@ -3568,19 +3996,19 @@
         <v>5010</v>
       </c>
       <c r="E11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="4:12">
@@ -3588,19 +4016,19 @@
         <v>5020</v>
       </c>
       <c r="E12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K12">
         <v>90</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="4:12">
@@ -3608,19 +4036,19 @@
         <v>6010</v>
       </c>
       <c r="E13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="11:12">
@@ -3628,7 +4056,7 @@
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="5:5">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -341,10 +341,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -367,9 +367,77 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -383,52 +451,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -441,23 +464,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -472,21 +480,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -496,8 +489,15 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -505,7 +505,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -520,13 +520,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -544,19 +670,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -568,139 +694,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -711,17 +711,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -744,16 +733,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -788,15 +768,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -811,6 +782,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -819,145 +819,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="105">
   <si>
     <t>Id</t>
   </si>
@@ -175,6 +175,9 @@
   </si>
   <si>
     <t>ユニットの強化</t>
+  </si>
+  <si>
+    <t>荒野の戦い</t>
   </si>
   <si>
     <t>敵拠点を制圧する</t>
@@ -341,10 +344,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -368,7 +371,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -376,6 +402,28 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -391,22 +439,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -421,51 +461,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -481,10 +484,25 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -493,21 +511,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -520,7 +523,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -532,13 +547,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,25 +607,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,79 +691,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -664,43 +703,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -715,6 +718,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -725,30 +743,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -768,35 +762,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -811,6 +781,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -819,145 +822,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1296,7 +1299,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="4" max="5" width="10.3636363636364" customWidth="1"/>
@@ -1702,7 +1705,7 @@
         <v>20</v>
       </c>
       <c r="P8">
-        <v>2010</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1802,6 +1805,156 @@
         <v>18</v>
       </c>
       <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>2010</v>
+      </c>
+      <c r="B11">
+        <v>2010</v>
+      </c>
+      <c r="C11">
+        <v>201</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>30</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>3020</v>
+      </c>
+      <c r="L11">
+        <v>3020</v>
+      </c>
+      <c r="M11">
+        <v>100</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>2011</v>
+      </c>
+      <c r="B12">
+        <v>2010</v>
+      </c>
+      <c r="C12">
+        <v>201</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>30</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>3020</v>
+      </c>
+      <c r="L12">
+        <v>3020</v>
+      </c>
+      <c r="M12">
+        <v>100</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O12" t="s">
+        <v>18</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>2012</v>
+      </c>
+      <c r="B13">
+        <v>2010</v>
+      </c>
+      <c r="C13">
+        <v>201</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>30</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>3020</v>
+      </c>
+      <c r="L13">
+        <v>3020</v>
+      </c>
+      <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O13" t="s">
+        <v>18</v>
+      </c>
+      <c r="P13">
         <v>0</v>
       </c>
     </row>
@@ -1814,7 +1967,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
@@ -3025,6 +3178,171 @@
         <v>0</v>
       </c>
       <c r="K37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38">
+        <v>2010</v>
+      </c>
+      <c r="B38">
+        <v>7</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>3010</v>
+      </c>
+      <c r="F38">
+        <v>2020</v>
+      </c>
+      <c r="G38" t="str">
+        <f>INDEX(Define!E:E,MATCH(F38,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H38">
+        <v>2011</v>
+      </c>
+      <c r="I38">
+        <v>7</v>
+      </c>
+      <c r="J38">
+        <v>12</v>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39">
+        <v>2010</v>
+      </c>
+      <c r="B39">
+        <v>7</v>
+      </c>
+      <c r="C39">
+        <v>7</v>
+      </c>
+      <c r="D39">
+        <v>3010</v>
+      </c>
+      <c r="F39">
+        <v>5020</v>
+      </c>
+      <c r="G39" t="str">
+        <f>INDEX(Define!E:E,MATCH(F39,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H39">
+        <v>20010</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40">
+        <v>2011</v>
+      </c>
+      <c r="B40">
+        <v>7</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>3010</v>
+      </c>
+      <c r="F40">
+        <v>2020</v>
+      </c>
+      <c r="G40" t="str">
+        <f>INDEX(Define!E:E,MATCH(F40,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H40">
+        <v>2012</v>
+      </c>
+      <c r="I40">
+        <v>7</v>
+      </c>
+      <c r="J40">
+        <v>12</v>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41">
+        <v>2011</v>
+      </c>
+      <c r="B41">
+        <v>7</v>
+      </c>
+      <c r="C41">
+        <v>7</v>
+      </c>
+      <c r="D41">
+        <v>3010</v>
+      </c>
+      <c r="F41">
+        <v>5020</v>
+      </c>
+      <c r="G41" t="str">
+        <f>INDEX(Define!E:E,MATCH(F41,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H41">
+        <v>20020</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42">
+        <v>2012</v>
+      </c>
+      <c r="B42">
+        <v>7</v>
+      </c>
+      <c r="C42">
+        <v>7</v>
+      </c>
+      <c r="D42">
+        <v>3010</v>
+      </c>
+      <c r="F42">
+        <v>5020</v>
+      </c>
+      <c r="G42" t="str">
+        <f>INDEX(Define!E:E,MATCH(F42,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H42">
+        <v>20030</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3037,7 +3355,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3331,7 +3649,7 @@
         <v>40</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <v>15</v>
@@ -3339,10 +3657,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1010</v>
+        <v>40</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C28">
         <v>15</v>
@@ -3350,10 +3668,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1010</v>
+        <v>40</v>
       </c>
       <c r="B29">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C29">
         <v>15</v>
@@ -3364,10 +3682,10 @@
         <v>1010</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -3375,32 +3693,32 @@
         <v>1010</v>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -3408,10 +3726,10 @@
         <v>1020</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -3419,9 +3737,31 @@
         <v>1020</v>
       </c>
       <c r="B35">
+        <v>6</v>
+      </c>
+      <c r="C35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>1020</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>1020</v>
+      </c>
+      <c r="B37">
         <v>7</v>
       </c>
-      <c r="C35">
+      <c r="C37">
         <v>20</v>
       </c>
     </row>
@@ -3498,7 +3838,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="34.1818181818182" customWidth="1"/>
@@ -3649,7 +3989,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
-        <v>10010</v>
+        <v>2010</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>52</v>
@@ -3659,15 +3999,27 @@
       </c>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" spans="3:4">
-      <c r="C14" s="3"/>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>10010</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" spans="3:3">
+    <row r="15" spans="3:4">
       <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
     </row>
     <row r="16" spans="3:3">
       <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3694,13 +4046,13 @@
         <v>27</v>
       </c>
       <c r="I1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -3708,31 +4060,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -3740,34 +4092,34 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3">
         <v>1010</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -3775,34 +4127,34 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4">
         <v>2010</v>
       </c>
       <c r="E4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:15">
@@ -3810,34 +4162,34 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D5">
         <v>2020</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M5">
         <v>30</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -3845,34 +4197,34 @@
         <v>3010</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="4:15">
@@ -3880,28 +4232,28 @@
         <v>3020</v>
       </c>
       <c r="E7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" ht="39" spans="4:15">
@@ -3909,28 +4261,28 @@
         <v>3030</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="4:15">
@@ -3938,28 +4290,28 @@
         <v>4010</v>
       </c>
       <c r="E9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M9">
         <v>70</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="4:15">
@@ -3967,28 +4319,28 @@
         <v>4020</v>
       </c>
       <c r="E10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="4:12">
@@ -3996,19 +4348,19 @@
         <v>5010</v>
       </c>
       <c r="E11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="4:12">
@@ -4016,19 +4368,19 @@
         <v>5020</v>
       </c>
       <c r="E12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K12">
         <v>90</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="4:12">
@@ -4036,19 +4388,19 @@
         <v>6010</v>
       </c>
       <c r="E13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="11:12">
@@ -4056,7 +4408,7 @@
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="5:5">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -344,10 +344,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -371,6 +371,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -378,7 +392,99 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -394,44 +500,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -444,75 +513,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -523,7 +523,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,43 +643,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,67 +673,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -667,43 +691,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -714,6 +714,54 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -732,17 +780,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -764,15 +806,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -781,39 +814,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -822,145 +822,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1728,7 +1728,7 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9">
         <v>30</v>
@@ -1778,7 +1778,7 @@
         <v>6</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10">
         <v>30</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -344,10 +344,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -370,8 +370,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -385,6 +386,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -392,7 +400,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -406,24 +429,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -437,6 +445,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -444,18 +482,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -474,45 +513,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -523,13 +523,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -541,7 +685,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,157 +697,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -732,17 +732,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -759,32 +764,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -804,13 +800,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -822,145 +822,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1725,7 +1725,7 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9">
         <v>3</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -345,8 +345,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
@@ -370,9 +370,23 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -386,13 +400,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -400,22 +407,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -429,9 +421,62 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -446,39 +491,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -490,27 +506,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -523,7 +523,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,25 +643,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -565,13 +673,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,121 +691,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -714,6 +714,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -732,22 +756,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -770,21 +789,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -800,17 +804,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -822,7 +822,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -831,7 +831,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -840,127 +840,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3520,7 +3520,7 @@
         <v>7</v>
       </c>
       <c r="C15">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3531,7 +3531,7 @@
         <v>9</v>
       </c>
       <c r="C16">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3575,7 +3575,7 @@
         <v>1</v>
       </c>
       <c r="C20">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3586,7 +3586,7 @@
         <v>4</v>
       </c>
       <c r="C21">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3630,7 +3630,7 @@
         <v>7</v>
       </c>
       <c r="C25">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3641,7 +3641,7 @@
         <v>9</v>
       </c>
       <c r="C26">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3707,7 +3707,7 @@
         <v>1</v>
       </c>
       <c r="C32">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -3718,7 +3718,7 @@
         <v>7</v>
       </c>
       <c r="C33">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -3751,7 +3751,7 @@
         <v>1</v>
       </c>
       <c r="C36">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -3762,7 +3762,7 @@
         <v>7</v>
       </c>
       <c r="C37">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="802" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="106">
   <si>
     <t>Id</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t>Group</t>
+  </si>
+  <si>
+    <t>ダメージ床</t>
   </si>
   <si>
     <t>Battler</t>
@@ -345,9 +348,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -370,16 +373,23 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -400,12 +410,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -429,16 +440,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -459,9 +478,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -475,8 +501,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -489,30 +516,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -523,25 +526,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -559,7 +556,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,13 +598,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,55 +628,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -655,37 +670,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,13 +700,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -714,6 +717,80 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -735,81 +812,7 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -822,145 +825,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1675,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -1725,7 +1728,7 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G9">
         <v>3</v>
@@ -1775,7 +1778,7 @@
         <v>2</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>4</v>
@@ -1967,7 +1970,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
@@ -2600,32 +2603,32 @@
         <v>30</v>
       </c>
       <c r="B20">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>3010</v>
       </c>
       <c r="F20">
-        <v>6010</v>
+        <v>2020</v>
       </c>
       <c r="G20" t="str">
         <f>INDEX(Define!E:E,MATCH(F20,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H20">
-        <v>612</v>
+        <v>32</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2636,16 +2639,20 @@
         <v>6</v>
       </c>
       <c r="C21">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <v>3010</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>6010</v>
+      </c>
+      <c r="G21" t="str">
+        <f>INDEX(Define!E:E,MATCH(F21,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H21">
-        <v>612</v>
+        <v>71</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -2659,92 +2666,88 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22">
         <v>3010</v>
       </c>
       <c r="F22">
-        <v>2020</v>
-      </c>
-      <c r="G22" t="str">
-        <f>INDEX(Define!E:E,MATCH(F22,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23">
         <v>3010</v>
       </c>
       <c r="F23">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="G23" t="str">
         <f>INDEX(Define!E:E,MATCH(F23,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>Adv再生</v>
       </c>
       <c r="H23">
-        <v>30</v>
+        <v>1030</v>
       </c>
       <c r="I23">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C24">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <v>3010</v>
       </c>
       <c r="F24">
-        <v>6010</v>
+        <v>7010</v>
       </c>
       <c r="G24" t="str">
         <f>INDEX(Define!E:E,MATCH(F24,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>ダメージ床</v>
       </c>
       <c r="H24">
-        <v>1310</v>
+        <v>20</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -2753,27 +2756,31 @@
         <v>0</v>
       </c>
       <c r="K24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D25">
         <v>3010</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>7010</v>
+      </c>
+      <c r="G25" t="str">
+        <f>INDEX(Define!E:E,MATCH(F25,Define!D:D))</f>
+        <v>ダメージ床</v>
       </c>
       <c r="H25">
-        <v>1310</v>
+        <v>20</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -2782,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2793,40 +2800,40 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D26">
         <v>3010</v>
       </c>
       <c r="F26">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="G26" t="str">
         <f>INDEX(Define!E:E,MATCH(F26,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H26">
-        <v>2020</v>
+        <v>30</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D27">
         <v>3010</v>
@@ -2842,10 +2849,10 @@
         <v>30</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -2853,26 +2860,26 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D28">
         <v>3010</v>
       </c>
       <c r="F28">
-        <v>5020</v>
+        <v>6010</v>
       </c>
       <c r="G28" t="str">
         <f>INDEX(Define!E:E,MATCH(F28,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H28">
-        <v>2010</v>
+        <v>1310</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -2886,26 +2893,22 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D29">
         <v>3010</v>
       </c>
       <c r="F29">
-        <v>3010</v>
-      </c>
-      <c r="G29" t="str">
-        <f>INDEX(Define!E:E,MATCH(F29,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>2030</v>
+        <v>1310</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -2919,26 +2922,26 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D30">
         <v>3010</v>
       </c>
       <c r="F30">
-        <v>2010</v>
+        <v>3010</v>
       </c>
       <c r="G30" t="str">
         <f>INDEX(Define!E:E,MATCH(F30,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>2020</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -2947,34 +2950,34 @@
         <v>0</v>
       </c>
       <c r="K30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31">
-        <v>1010</v>
+        <v>32</v>
       </c>
       <c r="B31">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C31">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D31">
         <v>3010</v>
       </c>
       <c r="F31">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="G31" t="str">
         <f>INDEX(Define!E:E,MATCH(F31,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -2985,59 +2988,59 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32">
-        <v>1010</v>
+        <v>32</v>
       </c>
       <c r="B32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D32">
         <v>3010</v>
       </c>
       <c r="F32">
-        <v>3030</v>
+        <v>2020</v>
       </c>
       <c r="G32" t="str">
         <f>INDEX(Define!E:E,MATCH(F32,Define!D:D))</f>
-        <v>魔法入手</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H32">
-        <v>30010</v>
+        <v>30</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33">
-        <v>1020</v>
+        <v>32</v>
       </c>
       <c r="B33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D33">
         <v>3010</v>
       </c>
       <c r="F33">
-        <v>2010</v>
+        <v>5020</v>
       </c>
       <c r="G33" t="str">
         <f>INDEX(Define!E:E,MATCH(F33,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>2010</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -3046,31 +3049,31 @@
         <v>0</v>
       </c>
       <c r="K33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34">
-        <v>1020</v>
+        <v>32</v>
       </c>
       <c r="B34">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C34">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D34">
         <v>3010</v>
       </c>
       <c r="F34">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="G34" t="str">
         <f>INDEX(Define!E:E,MATCH(F34,Define!D:D))</f>
-        <v>魔法入手</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H34">
-        <v>30020</v>
+        <v>2030</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -3084,26 +3087,26 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35">
-        <v>1020</v>
+        <v>40</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D35">
         <v>3010</v>
       </c>
       <c r="F35">
-        <v>3020</v>
+        <v>2010</v>
       </c>
       <c r="G35" t="str">
         <f>INDEX(Define!E:E,MATCH(F35,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H35">
-        <v>11010</v>
+        <v>0</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -3112,31 +3115,31 @@
         <v>0</v>
       </c>
       <c r="K35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B36">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D36">
         <v>3010</v>
       </c>
       <c r="F36">
-        <v>3020</v>
+        <v>2010</v>
       </c>
       <c r="G36" t="str">
         <f>INDEX(Define!E:E,MATCH(F36,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H36">
-        <v>11020</v>
+        <v>0</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -3145,31 +3148,31 @@
         <v>0</v>
       </c>
       <c r="K36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B37">
         <v>10</v>
       </c>
       <c r="C37">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D37">
         <v>3010</v>
       </c>
       <c r="F37">
-        <v>3020</v>
+        <v>3030</v>
       </c>
       <c r="G37" t="str">
         <f>INDEX(Define!E:E,MATCH(F37,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>魔法入手</v>
       </c>
       <c r="H37">
-        <v>11030</v>
+        <v>30010</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -3183,32 +3186,32 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38">
-        <v>2010</v>
+        <v>1020</v>
       </c>
       <c r="B38">
         <v>7</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D38">
         <v>3010</v>
       </c>
       <c r="F38">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="G38" t="str">
         <f>INDEX(Define!E:E,MATCH(F38,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H38">
-        <v>2011</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -3216,26 +3219,26 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39">
-        <v>2010</v>
+        <v>1020</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D39">
         <v>3010</v>
       </c>
       <c r="F39">
-        <v>5020</v>
+        <v>3030</v>
       </c>
       <c r="G39" t="str">
         <f>INDEX(Define!E:E,MATCH(F39,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>魔法入手</v>
       </c>
       <c r="H39">
-        <v>20010</v>
+        <v>30020</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -3249,10 +3252,10 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40">
-        <v>2011</v>
+        <v>1020</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -3261,47 +3264,47 @@
         <v>3010</v>
       </c>
       <c r="F40">
-        <v>2020</v>
+        <v>3020</v>
       </c>
       <c r="G40" t="str">
         <f>INDEX(Define!E:E,MATCH(F40,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H40">
-        <v>2012</v>
+        <v>11010</v>
       </c>
       <c r="I40">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J40">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41">
-        <v>2011</v>
+        <v>1020</v>
       </c>
       <c r="B41">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D41">
         <v>3010</v>
       </c>
       <c r="F41">
-        <v>5020</v>
+        <v>3020</v>
       </c>
       <c r="G41" t="str">
         <f>INDEX(Define!E:E,MATCH(F41,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H41">
-        <v>20020</v>
+        <v>11020</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -3315,34 +3318,199 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42">
-        <v>2012</v>
+        <v>1020</v>
       </c>
       <c r="B42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D42">
         <v>3010</v>
       </c>
       <c r="F42">
-        <v>5020</v>
+        <v>3020</v>
       </c>
       <c r="G42" t="str">
         <f>INDEX(Define!E:E,MATCH(F42,Define!D:D))</f>
+        <v>アイテム取得</v>
+      </c>
+      <c r="H42">
+        <v>11030</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43">
+        <v>2010</v>
+      </c>
+      <c r="B43">
+        <v>7</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>3010</v>
+      </c>
+      <c r="F43">
+        <v>2020</v>
+      </c>
+      <c r="G43" t="str">
+        <f>INDEX(Define!E:E,MATCH(F43,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H43">
+        <v>2011</v>
+      </c>
+      <c r="I43">
+        <v>7</v>
+      </c>
+      <c r="J43">
+        <v>12</v>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44">
+        <v>2010</v>
+      </c>
+      <c r="B44">
+        <v>7</v>
+      </c>
+      <c r="C44">
+        <v>7</v>
+      </c>
+      <c r="D44">
+        <v>3010</v>
+      </c>
+      <c r="F44">
+        <v>5020</v>
+      </c>
+      <c r="G44" t="str">
+        <f>INDEX(Define!E:E,MATCH(F44,Define!D:D))</f>
         <v>強制ボス戦闘</v>
       </c>
-      <c r="H42">
+      <c r="H44">
+        <v>20010</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45">
+        <v>2011</v>
+      </c>
+      <c r="B45">
+        <v>7</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>3010</v>
+      </c>
+      <c r="F45">
+        <v>2020</v>
+      </c>
+      <c r="G45" t="str">
+        <f>INDEX(Define!E:E,MATCH(F45,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H45">
+        <v>2012</v>
+      </c>
+      <c r="I45">
+        <v>7</v>
+      </c>
+      <c r="J45">
+        <v>12</v>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46">
+        <v>2011</v>
+      </c>
+      <c r="B46">
+        <v>7</v>
+      </c>
+      <c r="C46">
+        <v>7</v>
+      </c>
+      <c r="D46">
+        <v>3010</v>
+      </c>
+      <c r="F46">
+        <v>5020</v>
+      </c>
+      <c r="G46" t="str">
+        <f>INDEX(Define!E:E,MATCH(F46,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H46">
+        <v>20020</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47">
+        <v>2012</v>
+      </c>
+      <c r="B47">
+        <v>7</v>
+      </c>
+      <c r="C47">
+        <v>7</v>
+      </c>
+      <c r="D47">
+        <v>3010</v>
+      </c>
+      <c r="F47">
+        <v>5020</v>
+      </c>
+      <c r="G47" t="str">
+        <f>INDEX(Define!E:E,MATCH(F47,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H47">
         <v>20030</v>
       </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42" t="b">
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3685,7 +3853,7 @@
         <v>3</v>
       </c>
       <c r="C30">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -3696,7 +3864,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -3707,7 +3875,7 @@
         <v>1</v>
       </c>
       <c r="C32">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -3718,7 +3886,7 @@
         <v>7</v>
       </c>
       <c r="C33">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -4403,12 +4571,18 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="11:12">
+    <row r="14" spans="4:12">
+      <c r="D14">
+        <v>7010</v>
+      </c>
+      <c r="E14" t="s">
+        <v>104</v>
+      </c>
       <c r="K14">
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="5:5">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -347,10 +347,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -373,21 +373,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -395,8 +380,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -409,16 +395,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -440,41 +433,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -485,7 +448,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -494,7 +456,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -510,10 +472,48 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -526,13 +526,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -544,91 +688,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -640,73 +700,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -717,6 +717,32 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -735,11 +761,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -759,27 +791,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -793,30 +817,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -825,7 +825,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -834,7 +834,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -843,127 +843,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="109">
   <si>
     <t>Id</t>
   </si>
@@ -87,7 +87,7 @@
     <t>DirtCave</t>
   </si>
   <si>
-    <t>NA_Background image_Fantasy_027</t>
+    <t>042-EvilCastle02</t>
   </si>
   <si>
     <t>PositionX</t>
@@ -168,7 +168,13 @@
     <t>月影の森・採掘上跡</t>
   </si>
   <si>
-    <t>亡国の廃墟宮殿</t>
+    <t>亡国の廃墟宮殿・城門</t>
+  </si>
+  <si>
+    <t>亡国の廃墟宮殿・館内</t>
+  </si>
+  <si>
+    <t>亡国の廃墟宮殿・王室</t>
   </si>
   <si>
     <t>忘却の洞窟</t>
@@ -336,10 +342,13 @@
     <t>Group</t>
   </si>
   <si>
+    <t>同フロアの強制戦闘が終わってたらイベントマスを消す</t>
+  </si>
+  <si>
+    <t>Battler</t>
+  </si>
+  <si>
     <t>ダメージ床</t>
-  </si>
-  <si>
-    <t>Battler</t>
   </si>
 </sst>
 </file>
@@ -382,7 +391,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -395,16 +404,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -419,15 +444,21 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -435,14 +466,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -487,26 +511,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -526,7 +535,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -538,13 +559,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -556,127 +619,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,7 +643,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -706,7 +685,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -720,13 +729,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -746,6 +759,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -757,36 +785,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -817,6 +815,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -825,7 +834,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -834,7 +843,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -846,124 +855,124 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1302,7 +1311,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="4" max="5" width="10.3636363636364" customWidth="1"/>
@@ -1713,25 +1722,25 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9">
-        <v>1010</v>
+        <v>41</v>
       </c>
       <c r="B9">
-        <v>1010</v>
+        <v>41</v>
       </c>
       <c r="C9">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9">
         <v>30</v>
@@ -1743,7 +1752,7 @@
         <v>12</v>
       </c>
       <c r="K9">
-        <v>1210</v>
+        <v>1030</v>
       </c>
       <c r="L9">
         <v>3010</v>
@@ -1752,10 +1761,10 @@
         <v>100</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="O9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1763,22 +1772,22 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10">
-        <v>1020</v>
+        <v>42</v>
       </c>
       <c r="B10">
-        <v>1020</v>
+        <v>42</v>
       </c>
       <c r="C10">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>4</v>
@@ -1793,7 +1802,7 @@
         <v>12</v>
       </c>
       <c r="K10">
-        <v>1210</v>
+        <v>1030</v>
       </c>
       <c r="L10">
         <v>3010</v>
@@ -1802,10 +1811,10 @@
         <v>100</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="O10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -1813,40 +1822,40 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11">
-        <v>2010</v>
+        <v>1010</v>
       </c>
       <c r="B11">
-        <v>2010</v>
+        <v>1010</v>
       </c>
       <c r="C11">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11">
         <v>30</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K11">
-        <v>3020</v>
+        <v>1210</v>
       </c>
       <c r="L11">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -1863,16 +1872,16 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12">
-        <v>2011</v>
+        <v>1020</v>
       </c>
       <c r="B12">
-        <v>2010</v>
+        <v>1020</v>
       </c>
       <c r="C12">
-        <v>201</v>
+        <v>102</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1881,22 +1890,22 @@
         <v>10</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12">
         <v>30</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K12">
-        <v>3020</v>
+        <v>1210</v>
       </c>
       <c r="L12">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -1913,7 +1922,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B13">
         <v>2010</v>
@@ -1958,6 +1967,106 @@
         <v>18</v>
       </c>
       <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>2011</v>
+      </c>
+      <c r="B14">
+        <v>2010</v>
+      </c>
+      <c r="C14">
+        <v>201</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>30</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>3020</v>
+      </c>
+      <c r="L14">
+        <v>3020</v>
+      </c>
+      <c r="M14">
+        <v>100</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O14" t="s">
+        <v>18</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>2012</v>
+      </c>
+      <c r="B15">
+        <v>2010</v>
+      </c>
+      <c r="C15">
+        <v>201</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>30</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>3020</v>
+      </c>
+      <c r="L15">
+        <v>3020</v>
+      </c>
+      <c r="M15">
+        <v>100</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O15" t="s">
+        <v>18</v>
+      </c>
+      <c r="P15">
         <v>0</v>
       </c>
     </row>
@@ -1970,7 +2079,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
@@ -3120,32 +3229,32 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36">
-        <v>1010</v>
+        <v>40</v>
       </c>
       <c r="B36">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C36">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>3010</v>
       </c>
       <c r="F36">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="G36" t="str">
         <f>INDEX(Define!E:E,MATCH(F36,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -3153,26 +3262,26 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37">
-        <v>1010</v>
+        <v>40</v>
       </c>
       <c r="B37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D37">
         <v>3010</v>
       </c>
       <c r="F37">
-        <v>3030</v>
+        <v>6010</v>
       </c>
       <c r="G37" t="str">
         <f>INDEX(Define!E:E,MATCH(F37,Define!D:D))</f>
-        <v>魔法入手</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H37">
-        <v>30010</v>
+        <v>45</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -3186,26 +3295,22 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38">
-        <v>1020</v>
+        <v>40</v>
       </c>
       <c r="B38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D38">
         <v>3010</v>
       </c>
       <c r="F38">
-        <v>2010</v>
-      </c>
-      <c r="G38" t="str">
-        <f>INDEX(Define!E:E,MATCH(F38,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -3214,97 +3319,97 @@
         <v>0</v>
       </c>
       <c r="K38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39">
-        <v>1020</v>
+        <v>41</v>
       </c>
       <c r="B39">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D39">
         <v>3010</v>
       </c>
       <c r="F39">
-        <v>3030</v>
+        <v>2020</v>
       </c>
       <c r="G39" t="str">
         <f>INDEX(Define!E:E,MATCH(F39,Define!D:D))</f>
-        <v>魔法入手</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H39">
-        <v>30020</v>
+        <v>40</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40">
-        <v>1020</v>
+        <v>41</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D40">
         <v>3010</v>
       </c>
       <c r="F40">
-        <v>3020</v>
+        <v>2020</v>
       </c>
       <c r="G40" t="str">
         <f>INDEX(Define!E:E,MATCH(F40,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H40">
-        <v>11010</v>
+        <v>42</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41">
-        <v>1020</v>
+        <v>41</v>
       </c>
       <c r="B41">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D41">
         <v>3010</v>
       </c>
       <c r="F41">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="G41" t="str">
         <f>INDEX(Define!E:E,MATCH(F41,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H41">
-        <v>11020</v>
+        <v>2130</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -3318,13 +3423,13 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42">
-        <v>1020</v>
+        <v>41</v>
       </c>
       <c r="B42">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D42">
         <v>3010</v>
@@ -3337,7 +3442,7 @@
         <v>アイテム取得</v>
       </c>
       <c r="H42">
-        <v>11030</v>
+        <v>11010</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -3351,10 +3456,10 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43">
-        <v>2010</v>
+        <v>41</v>
       </c>
       <c r="B43">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -3363,47 +3468,47 @@
         <v>3010</v>
       </c>
       <c r="F43">
-        <v>2020</v>
+        <v>3020</v>
       </c>
       <c r="G43" t="str">
         <f>INDEX(Define!E:E,MATCH(F43,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H43">
-        <v>2011</v>
+        <v>11010</v>
       </c>
       <c r="I43">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44">
-        <v>2010</v>
+        <v>41</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D44">
         <v>3010</v>
       </c>
       <c r="F44">
-        <v>5020</v>
+        <v>3020</v>
       </c>
       <c r="G44" t="str">
         <f>INDEX(Define!E:E,MATCH(F44,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H44">
-        <v>20010</v>
+        <v>11010</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -3417,59 +3522,59 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45">
-        <v>2011</v>
+        <v>41</v>
       </c>
       <c r="B45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D45">
         <v>3010</v>
       </c>
       <c r="F45">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="G45" t="str">
         <f>INDEX(Define!E:E,MATCH(F45,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>Adv再生</v>
       </c>
       <c r="H45">
-        <v>2012</v>
+        <v>1040</v>
       </c>
       <c r="I45">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J45">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46">
-        <v>2011</v>
+        <v>41</v>
       </c>
       <c r="B46">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D46">
         <v>3010</v>
       </c>
       <c r="F46">
-        <v>5020</v>
+        <v>1010</v>
       </c>
       <c r="G46" t="str">
         <f>INDEX(Define!E:E,MATCH(F46,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>Adv再生</v>
       </c>
       <c r="H46">
-        <v>20020</v>
+        <v>100</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -3483,34 +3588,818 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47">
-        <v>2012</v>
+        <v>41</v>
       </c>
       <c r="B47">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D47">
         <v>3010</v>
       </c>
       <c r="F47">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="G47" t="str">
         <f>INDEX(Define!E:E,MATCH(F47,Define!D:D))</f>
+        <v>強制戦闘</v>
+      </c>
+      <c r="H47">
+        <v>3020</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48">
+        <v>41</v>
+      </c>
+      <c r="B48">
+        <v>4</v>
+      </c>
+      <c r="C48">
+        <v>4</v>
+      </c>
+      <c r="D48">
+        <v>3010</v>
+      </c>
+      <c r="F48">
+        <v>6010</v>
+      </c>
+      <c r="G48" t="str">
+        <f>INDEX(Define!E:E,MATCH(F48,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
+      </c>
+      <c r="H48">
+        <v>43</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49">
+        <v>41</v>
+      </c>
+      <c r="B49">
+        <v>4</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="D49">
+        <v>3010</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>43</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50">
+        <v>42</v>
+      </c>
+      <c r="B50">
+        <v>2</v>
+      </c>
+      <c r="C50">
+        <v>18</v>
+      </c>
+      <c r="D50">
+        <v>3010</v>
+      </c>
+      <c r="F50">
+        <v>2020</v>
+      </c>
+      <c r="G50" t="str">
+        <f>INDEX(Define!E:E,MATCH(F50,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H50">
+        <v>41</v>
+      </c>
+      <c r="I50">
+        <v>9</v>
+      </c>
+      <c r="J50">
+        <v>4</v>
+      </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51">
+        <v>42</v>
+      </c>
+      <c r="B51">
+        <v>8</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>3010</v>
+      </c>
+      <c r="F51">
+        <v>3010</v>
+      </c>
+      <c r="G51" t="str">
+        <f>INDEX(Define!E:E,MATCH(F51,Define!D:D))</f>
+        <v>アーティファクト取得</v>
+      </c>
+      <c r="H51">
+        <v>2020</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52">
+        <v>42</v>
+      </c>
+      <c r="B52">
+        <v>8</v>
+      </c>
+      <c r="C52">
+        <v>8</v>
+      </c>
+      <c r="D52">
+        <v>3010</v>
+      </c>
+      <c r="F52">
+        <v>5020</v>
+      </c>
+      <c r="G52" t="str">
+        <f>INDEX(Define!E:E,MATCH(F52,Define!D:D))</f>
         <v>強制ボス戦闘</v>
       </c>
-      <c r="H47">
+      <c r="H52">
+        <v>3010</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53">
+        <v>42</v>
+      </c>
+      <c r="B53">
+        <v>4</v>
+      </c>
+      <c r="C53">
+        <v>8</v>
+      </c>
+      <c r="D53">
+        <v>3010</v>
+      </c>
+      <c r="F53">
+        <v>1010</v>
+      </c>
+      <c r="G53" t="str">
+        <f>INDEX(Define!E:E,MATCH(F53,Define!D:D))</f>
+        <v>Adv再生</v>
+      </c>
+      <c r="H53">
+        <v>100</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54">
+        <v>42</v>
+      </c>
+      <c r="B54">
+        <v>4</v>
+      </c>
+      <c r="C54">
+        <v>8</v>
+      </c>
+      <c r="D54">
+        <v>3010</v>
+      </c>
+      <c r="F54">
+        <v>5010</v>
+      </c>
+      <c r="G54" t="str">
+        <f>INDEX(Define!E:E,MATCH(F54,Define!D:D))</f>
+        <v>強制戦闘</v>
+      </c>
+      <c r="H54">
+        <v>3030</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55">
+        <v>42</v>
+      </c>
+      <c r="B55">
+        <v>12</v>
+      </c>
+      <c r="C55">
+        <v>8</v>
+      </c>
+      <c r="D55">
+        <v>3010</v>
+      </c>
+      <c r="F55">
+        <v>1010</v>
+      </c>
+      <c r="G55" t="str">
+        <f>INDEX(Define!E:E,MATCH(F55,Define!D:D))</f>
+        <v>Adv再生</v>
+      </c>
+      <c r="H55">
+        <v>100</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56">
+        <v>42</v>
+      </c>
+      <c r="B56">
+        <v>12</v>
+      </c>
+      <c r="C56">
+        <v>8</v>
+      </c>
+      <c r="D56">
+        <v>3010</v>
+      </c>
+      <c r="F56">
+        <v>5010</v>
+      </c>
+      <c r="G56" t="str">
+        <f>INDEX(Define!E:E,MATCH(F56,Define!D:D))</f>
+        <v>強制戦闘</v>
+      </c>
+      <c r="H56">
+        <v>3040</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57">
+        <v>42</v>
+      </c>
+      <c r="B57">
+        <v>8</v>
+      </c>
+      <c r="C57">
+        <v>10</v>
+      </c>
+      <c r="D57">
+        <v>3010</v>
+      </c>
+      <c r="F57">
+        <v>1010</v>
+      </c>
+      <c r="G57" t="str">
+        <f>INDEX(Define!E:E,MATCH(F57,Define!D:D))</f>
+        <v>Adv再生</v>
+      </c>
+      <c r="H57">
+        <v>1030</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58">
+        <v>42</v>
+      </c>
+      <c r="B58">
+        <v>8</v>
+      </c>
+      <c r="C58">
+        <v>10</v>
+      </c>
+      <c r="D58">
+        <v>3010</v>
+      </c>
+      <c r="F58">
+        <v>6020</v>
+      </c>
+      <c r="G58" t="str">
+        <f>INDEX(Define!E:E,MATCH(F58,Define!D:D))</f>
+        <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+      </c>
+      <c r="H58">
+        <v>89</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59">
+        <v>42</v>
+      </c>
+      <c r="B59">
+        <v>8</v>
+      </c>
+      <c r="C59">
+        <v>9</v>
+      </c>
+      <c r="D59">
+        <v>3010</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>89</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60">
+        <v>1010</v>
+      </c>
+      <c r="B60">
+        <v>13</v>
+      </c>
+      <c r="C60">
+        <v>13</v>
+      </c>
+      <c r="D60">
+        <v>3010</v>
+      </c>
+      <c r="F60">
+        <v>2010</v>
+      </c>
+      <c r="G60" t="str">
+        <f>INDEX(Define!E:E,MATCH(F60,Define!D:D))</f>
+        <v>ダンジョンから出る</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61">
+        <v>1010</v>
+      </c>
+      <c r="B61">
+        <v>10</v>
+      </c>
+      <c r="C61">
+        <v>4</v>
+      </c>
+      <c r="D61">
+        <v>3010</v>
+      </c>
+      <c r="F61">
+        <v>3030</v>
+      </c>
+      <c r="G61" t="str">
+        <f>INDEX(Define!E:E,MATCH(F61,Define!D:D))</f>
+        <v>魔法入手</v>
+      </c>
+      <c r="H61">
+        <v>30010</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62">
+        <v>1020</v>
+      </c>
+      <c r="B62">
+        <v>7</v>
+      </c>
+      <c r="C62">
+        <v>8</v>
+      </c>
+      <c r="D62">
+        <v>3010</v>
+      </c>
+      <c r="F62">
+        <v>2010</v>
+      </c>
+      <c r="G62" t="str">
+        <f>INDEX(Define!E:E,MATCH(F62,Define!D:D))</f>
+        <v>ダンジョンから出る</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63">
+        <v>1020</v>
+      </c>
+      <c r="B63">
+        <v>12</v>
+      </c>
+      <c r="C63">
+        <v>12</v>
+      </c>
+      <c r="D63">
+        <v>3010</v>
+      </c>
+      <c r="F63">
+        <v>3030</v>
+      </c>
+      <c r="G63" t="str">
+        <f>INDEX(Define!E:E,MATCH(F63,Define!D:D))</f>
+        <v>魔法入手</v>
+      </c>
+      <c r="H63">
+        <v>30020</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64">
+        <v>1020</v>
+      </c>
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="D64">
+        <v>3010</v>
+      </c>
+      <c r="F64">
+        <v>3020</v>
+      </c>
+      <c r="G64" t="str">
+        <f>INDEX(Define!E:E,MATCH(F64,Define!D:D))</f>
+        <v>アイテム取得</v>
+      </c>
+      <c r="H64">
+        <v>11010</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65">
+        <v>1020</v>
+      </c>
+      <c r="B65">
+        <v>9</v>
+      </c>
+      <c r="C65">
+        <v>4</v>
+      </c>
+      <c r="D65">
+        <v>3010</v>
+      </c>
+      <c r="F65">
+        <v>3020</v>
+      </c>
+      <c r="G65" t="str">
+        <f>INDEX(Define!E:E,MATCH(F65,Define!D:D))</f>
+        <v>アイテム取得</v>
+      </c>
+      <c r="H65">
+        <v>11020</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66">
+        <v>1020</v>
+      </c>
+      <c r="B66">
+        <v>10</v>
+      </c>
+      <c r="C66">
+        <v>12</v>
+      </c>
+      <c r="D66">
+        <v>3010</v>
+      </c>
+      <c r="F66">
+        <v>3020</v>
+      </c>
+      <c r="G66" t="str">
+        <f>INDEX(Define!E:E,MATCH(F66,Define!D:D))</f>
+        <v>アイテム取得</v>
+      </c>
+      <c r="H66">
+        <v>11030</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67">
+        <v>2010</v>
+      </c>
+      <c r="B67">
+        <v>7</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+      <c r="D67">
+        <v>3010</v>
+      </c>
+      <c r="F67">
+        <v>2020</v>
+      </c>
+      <c r="G67" t="str">
+        <f>INDEX(Define!E:E,MATCH(F67,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H67">
+        <v>2011</v>
+      </c>
+      <c r="I67">
+        <v>7</v>
+      </c>
+      <c r="J67">
+        <v>12</v>
+      </c>
+      <c r="K67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68">
+        <v>2010</v>
+      </c>
+      <c r="B68">
+        <v>7</v>
+      </c>
+      <c r="C68">
+        <v>7</v>
+      </c>
+      <c r="D68">
+        <v>3010</v>
+      </c>
+      <c r="F68">
+        <v>5020</v>
+      </c>
+      <c r="G68" t="str">
+        <f>INDEX(Define!E:E,MATCH(F68,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H68">
+        <v>20010</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69">
+        <v>2011</v>
+      </c>
+      <c r="B69">
+        <v>7</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69">
+        <v>3010</v>
+      </c>
+      <c r="F69">
+        <v>2020</v>
+      </c>
+      <c r="G69" t="str">
+        <f>INDEX(Define!E:E,MATCH(F69,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H69">
+        <v>2012</v>
+      </c>
+      <c r="I69">
+        <v>7</v>
+      </c>
+      <c r="J69">
+        <v>12</v>
+      </c>
+      <c r="K69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70">
+        <v>2011</v>
+      </c>
+      <c r="B70">
+        <v>7</v>
+      </c>
+      <c r="C70">
+        <v>7</v>
+      </c>
+      <c r="D70">
+        <v>3010</v>
+      </c>
+      <c r="F70">
+        <v>5020</v>
+      </c>
+      <c r="G70" t="str">
+        <f>INDEX(Define!E:E,MATCH(F70,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H70">
+        <v>20020</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71">
+        <v>2012</v>
+      </c>
+      <c r="B71">
+        <v>7</v>
+      </c>
+      <c r="C71">
+        <v>7</v>
+      </c>
+      <c r="D71">
+        <v>3010</v>
+      </c>
+      <c r="F71">
+        <v>5020</v>
+      </c>
+      <c r="G71" t="str">
+        <f>INDEX(Define!E:E,MATCH(F71,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H71">
         <v>20030</v>
       </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47" t="b">
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3523,7 +4412,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3847,54 +4736,54 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1010</v>
+        <v>41</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1010</v>
+        <v>41</v>
       </c>
       <c r="B31">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C31">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1010</v>
+        <v>41</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C32">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1010</v>
+        <v>42</v>
       </c>
       <c r="B33">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1020</v>
+        <v>42</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C34">
         <v>15</v>
@@ -3902,10 +4791,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1020</v>
+        <v>42</v>
       </c>
       <c r="B35">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C35">
         <v>15</v>
@@ -3913,10 +4802,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1020</v>
+        <v>42</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C36">
         <v>15</v>
@@ -3924,12 +4813,89 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
+        <v>1010</v>
+      </c>
+      <c r="B37">
+        <v>3</v>
+      </c>
+      <c r="C37">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>1010</v>
+      </c>
+      <c r="B38">
+        <v>6</v>
+      </c>
+      <c r="C38">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>1010</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>1010</v>
+      </c>
+      <c r="B40">
+        <v>7</v>
+      </c>
+      <c r="C40">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
         <v>1020</v>
       </c>
-      <c r="B37">
+      <c r="B41">
+        <v>2</v>
+      </c>
+      <c r="C41">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>1020</v>
+      </c>
+      <c r="B42">
+        <v>4</v>
+      </c>
+      <c r="C42">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>1020</v>
+      </c>
+      <c r="B43">
         <v>7</v>
       </c>
-      <c r="C37">
+      <c r="C43">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>1020</v>
+      </c>
+      <c r="B44">
+        <v>8</v>
+      </c>
+      <c r="C44">
         <v>15</v>
       </c>
     </row>
@@ -4006,7 +4972,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="34.1818181818182" customWidth="1"/>
@@ -4121,34 +5087,34 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>1010</v>
+        <v>41</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
-        <v>1020</v>
+        <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>17</v>
@@ -4157,7 +5123,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
-        <v>2010</v>
+        <v>1020</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>52</v>
@@ -4169,7 +5135,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
-        <v>10010</v>
+        <v>1030</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>53</v>
@@ -4179,15 +5145,39 @@
       </c>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" spans="3:4">
-      <c r="C15" s="3"/>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>2010</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="D15" s="3"/>
     </row>
-    <row r="16" spans="3:3">
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" spans="3:3">
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <v>10010</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="3:4">
       <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4214,13 +5204,13 @@
         <v>27</v>
       </c>
       <c r="I1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -4228,31 +5218,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -4260,34 +5250,34 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D3">
         <v>1010</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -4295,34 +5285,34 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D4">
         <v>2010</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:15">
@@ -4330,34 +5320,34 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D5">
         <v>2020</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M5">
         <v>30</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -4365,34 +5355,34 @@
         <v>3010</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="4:15">
@@ -4400,28 +5390,28 @@
         <v>3020</v>
       </c>
       <c r="E7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" ht="39" spans="4:15">
@@ -4429,28 +5419,28 @@
         <v>3030</v>
       </c>
       <c r="E8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="4:15">
@@ -4458,28 +5448,28 @@
         <v>4010</v>
       </c>
       <c r="E9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M9">
         <v>70</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="4:15">
@@ -4487,28 +5477,28 @@
         <v>4020</v>
       </c>
       <c r="E10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="4:12">
@@ -4516,19 +5506,19 @@
         <v>5010</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="4:12">
@@ -4536,19 +5526,19 @@
         <v>5020</v>
       </c>
       <c r="E12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K12">
         <v>90</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="4:12">
@@ -4556,33 +5546,41 @@
         <v>6010</v>
       </c>
       <c r="E13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="4:12">
       <c r="D14">
-        <v>7010</v>
+        <v>6020</v>
       </c>
       <c r="E14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K14">
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="4:5">
+      <c r="D15">
+        <v>7010</v>
+      </c>
+      <c r="E15" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="5:5">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="112">
   <si>
     <t>Id</t>
   </si>
@@ -342,13 +342,22 @@
     <t>Group</t>
   </si>
   <si>
+    <t>指定のイベントマスを表示する</t>
+  </si>
+  <si>
+    <t>Battler</t>
+  </si>
+  <si>
     <t>同フロアの強制戦闘が終わってたらイベントマスを消す</t>
   </si>
   <si>
-    <t>Battler</t>
-  </si>
-  <si>
     <t>ダメージ床</t>
+  </si>
+  <si>
+    <t>怨嗟床</t>
+  </si>
+  <si>
+    <t>怨嗟床解除</t>
   </si>
 </sst>
 </file>
@@ -356,10 +365,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -383,29 +392,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -419,24 +413,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -457,16 +458,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -496,6 +490,22 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -504,16 +514,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -521,6 +523,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -535,7 +544,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -547,67 +592,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -619,7 +610,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -637,7 +646,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -649,73 +724,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -730,16 +739,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -759,17 +768,55 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -788,44 +835,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -834,19 +843,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -855,124 +864,124 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2079,7 +2088,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
@@ -3683,32 +3692,32 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C50">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D50">
         <v>3010</v>
       </c>
       <c r="F50">
-        <v>2020</v>
+        <v>7010</v>
       </c>
       <c r="G50" t="str">
         <f>INDEX(Define!E:E,MATCH(F50,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>ダメージ床</v>
       </c>
       <c r="H50">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="I50">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -3716,26 +3725,26 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B51">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D51">
         <v>3010</v>
       </c>
       <c r="F51">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="G51" t="str">
         <f>INDEX(Define!E:E,MATCH(F51,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>ダメージ床</v>
       </c>
       <c r="H51">
-        <v>2020</v>
+        <v>20</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -3744,31 +3753,31 @@
         <v>0</v>
       </c>
       <c r="K51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B52">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C52">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D52">
         <v>3010</v>
       </c>
       <c r="F52">
-        <v>5020</v>
+        <v>7010</v>
       </c>
       <c r="G52" t="str">
         <f>INDEX(Define!E:E,MATCH(F52,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>ダメージ床</v>
       </c>
       <c r="H52">
-        <v>3010</v>
+        <v>20</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -3777,31 +3786,31 @@
         <v>0</v>
       </c>
       <c r="K52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C53">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D53">
         <v>3010</v>
       </c>
       <c r="F53">
-        <v>1010</v>
+        <v>6011</v>
       </c>
       <c r="G53" t="str">
         <f>INDEX(Define!E:E,MATCH(F53,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>指定のイベントマスを表示する</v>
       </c>
       <c r="H53">
-        <v>100</v>
+        <v>713</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -3815,26 +3824,22 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C54">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D54">
         <v>3010</v>
       </c>
       <c r="F54">
-        <v>5010</v>
-      </c>
-      <c r="G54" t="str">
-        <f>INDEX(Define!E:E,MATCH(F54,Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>0</v>
       </c>
       <c r="H54">
-        <v>3030</v>
+        <v>713</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -3848,13 +3853,13 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B55">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C55">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D55">
         <v>3010</v>
@@ -3867,7 +3872,7 @@
         <v>Adv再生</v>
       </c>
       <c r="H55">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -3881,26 +3886,26 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B56">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C56">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D56">
         <v>3010</v>
       </c>
       <c r="F56">
-        <v>5010</v>
+        <v>7020</v>
       </c>
       <c r="G56" t="str">
         <f>INDEX(Define!E:E,MATCH(F56,Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>怨嗟床</v>
       </c>
       <c r="H56">
-        <v>3040</v>
+        <v>0</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -3914,13 +3919,13 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C57">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D57">
         <v>3010</v>
@@ -3933,7 +3938,7 @@
         <v>Adv再生</v>
       </c>
       <c r="H57">
-        <v>1030</v>
+        <v>120</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -3947,26 +3952,26 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B58">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D58">
         <v>3010</v>
       </c>
       <c r="F58">
-        <v>6020</v>
+        <v>7021</v>
       </c>
       <c r="G58" t="str">
         <f>INDEX(Define!E:E,MATCH(F58,Define!D:D))</f>
-        <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+        <v>怨嗟床解除</v>
       </c>
       <c r="H58">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -3980,22 +3985,26 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B59">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D59">
         <v>3010</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>6010</v>
+      </c>
+      <c r="G59" t="str">
+        <f>INDEX(Define!E:E,MATCH(F59,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H59">
-        <v>89</v>
+        <v>813</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -4009,10 +4018,10 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60">
-        <v>1010</v>
+        <v>41</v>
       </c>
       <c r="B60">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C60">
         <v>13</v>
@@ -4021,14 +4030,10 @@
         <v>3010</v>
       </c>
       <c r="F60">
-        <v>2010</v>
-      </c>
-      <c r="G60" t="str">
-        <f>INDEX(Define!E:E,MATCH(F60,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>0</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>813</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -4037,31 +4042,31 @@
         <v>0</v>
       </c>
       <c r="K60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61">
-        <v>1010</v>
+        <v>42</v>
       </c>
       <c r="B61">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C61">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D61">
         <v>3010</v>
       </c>
       <c r="F61">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="G61" t="str">
         <f>INDEX(Define!E:E,MATCH(F61,Define!D:D))</f>
-        <v>魔法入手</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H61">
-        <v>30010</v>
+        <v>2020</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -4075,10 +4080,10 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62">
-        <v>1020</v>
+        <v>42</v>
       </c>
       <c r="B62">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C62">
         <v>8</v>
@@ -4087,14 +4092,14 @@
         <v>3010</v>
       </c>
       <c r="F62">
-        <v>2010</v>
+        <v>5020</v>
       </c>
       <c r="G62" t="str">
         <f>INDEX(Define!E:E,MATCH(F62,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>3010</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -4103,31 +4108,31 @@
         <v>0</v>
       </c>
       <c r="K62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63">
-        <v>1020</v>
+        <v>42</v>
       </c>
       <c r="B63">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C63">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D63">
         <v>3010</v>
       </c>
       <c r="F63">
-        <v>3030</v>
+        <v>1010</v>
       </c>
       <c r="G63" t="str">
         <f>INDEX(Define!E:E,MATCH(F63,Define!D:D))</f>
-        <v>魔法入手</v>
+        <v>Adv再生</v>
       </c>
       <c r="H63">
-        <v>30020</v>
+        <v>100</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -4141,26 +4146,26 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64">
-        <v>1020</v>
+        <v>42</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D64">
         <v>3010</v>
       </c>
       <c r="F64">
-        <v>3020</v>
+        <v>5010</v>
       </c>
       <c r="G64" t="str">
         <f>INDEX(Define!E:E,MATCH(F64,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H64">
-        <v>11010</v>
+        <v>3030</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -4174,26 +4179,26 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65">
-        <v>1020</v>
+        <v>42</v>
       </c>
       <c r="B65">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C65">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D65">
         <v>3010</v>
       </c>
       <c r="F65">
-        <v>3020</v>
+        <v>1010</v>
       </c>
       <c r="G65" t="str">
         <f>INDEX(Define!E:E,MATCH(F65,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>Adv再生</v>
       </c>
       <c r="H65">
-        <v>11020</v>
+        <v>100</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -4207,26 +4212,26 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66">
-        <v>1020</v>
+        <v>42</v>
       </c>
       <c r="B66">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C66">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D66">
         <v>3010</v>
       </c>
       <c r="F66">
-        <v>3020</v>
+        <v>5010</v>
       </c>
       <c r="G66" t="str">
         <f>INDEX(Define!E:E,MATCH(F66,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H66">
-        <v>11030</v>
+        <v>3040</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -4240,59 +4245,59 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67">
-        <v>2010</v>
+        <v>42</v>
       </c>
       <c r="B67">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D67">
         <v>3010</v>
       </c>
       <c r="F67">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="G67" t="str">
         <f>INDEX(Define!E:E,MATCH(F67,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>Adv再生</v>
       </c>
       <c r="H67">
-        <v>2011</v>
+        <v>1030</v>
       </c>
       <c r="I67">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J67">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68">
-        <v>2010</v>
+        <v>42</v>
       </c>
       <c r="B68">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D68">
         <v>3010</v>
       </c>
       <c r="F68">
-        <v>5020</v>
+        <v>6020</v>
       </c>
       <c r="G68" t="str">
         <f>INDEX(Define!E:E,MATCH(F68,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
       </c>
       <c r="H68">
-        <v>20010</v>
+        <v>89</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -4306,59 +4311,55 @@
     </row>
     <row r="69" spans="1:11">
       <c r="A69">
-        <v>2011</v>
+        <v>42</v>
       </c>
       <c r="B69">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D69">
         <v>3010</v>
       </c>
       <c r="F69">
-        <v>2020</v>
-      </c>
-      <c r="G69" t="str">
-        <f>INDEX(Define!E:E,MATCH(F69,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>0</v>
       </c>
       <c r="H69">
-        <v>2012</v>
+        <v>89</v>
       </c>
       <c r="I69">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J69">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70">
-        <v>2011</v>
+        <v>1010</v>
       </c>
       <c r="B70">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D70">
         <v>3010</v>
       </c>
       <c r="F70">
-        <v>5020</v>
+        <v>2010</v>
       </c>
       <c r="G70" t="str">
         <f>INDEX(Define!E:E,MATCH(F70,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H70">
-        <v>20020</v>
+        <v>0</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -4367,39 +4368,369 @@
         <v>0</v>
       </c>
       <c r="K70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71">
-        <v>2012</v>
+        <v>1010</v>
       </c>
       <c r="B71">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D71">
         <v>3010</v>
       </c>
       <c r="F71">
-        <v>5020</v>
+        <v>3030</v>
       </c>
       <c r="G71" t="str">
         <f>INDEX(Define!E:E,MATCH(F71,Define!D:D))</f>
+        <v>魔法入手</v>
+      </c>
+      <c r="H71">
+        <v>30010</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72">
+        <v>1020</v>
+      </c>
+      <c r="B72">
+        <v>7</v>
+      </c>
+      <c r="C72">
+        <v>8</v>
+      </c>
+      <c r="D72">
+        <v>3010</v>
+      </c>
+      <c r="F72">
+        <v>2010</v>
+      </c>
+      <c r="G72" t="str">
+        <f>INDEX(Define!E:E,MATCH(F72,Define!D:D))</f>
+        <v>ダンジョンから出る</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73">
+        <v>1020</v>
+      </c>
+      <c r="B73">
+        <v>12</v>
+      </c>
+      <c r="C73">
+        <v>12</v>
+      </c>
+      <c r="D73">
+        <v>3010</v>
+      </c>
+      <c r="F73">
+        <v>3030</v>
+      </c>
+      <c r="G73" t="str">
+        <f>INDEX(Define!E:E,MATCH(F73,Define!D:D))</f>
+        <v>魔法入手</v>
+      </c>
+      <c r="H73">
+        <v>30020</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74">
+        <v>1020</v>
+      </c>
+      <c r="B74">
+        <v>2</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74">
+        <v>3010</v>
+      </c>
+      <c r="F74">
+        <v>3020</v>
+      </c>
+      <c r="G74" t="str">
+        <f>INDEX(Define!E:E,MATCH(F74,Define!D:D))</f>
+        <v>アイテム取得</v>
+      </c>
+      <c r="H74">
+        <v>11010</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75">
+        <v>1020</v>
+      </c>
+      <c r="B75">
+        <v>9</v>
+      </c>
+      <c r="C75">
+        <v>4</v>
+      </c>
+      <c r="D75">
+        <v>3010</v>
+      </c>
+      <c r="F75">
+        <v>3020</v>
+      </c>
+      <c r="G75" t="str">
+        <f>INDEX(Define!E:E,MATCH(F75,Define!D:D))</f>
+        <v>アイテム取得</v>
+      </c>
+      <c r="H75">
+        <v>11020</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76">
+        <v>1020</v>
+      </c>
+      <c r="B76">
+        <v>10</v>
+      </c>
+      <c r="C76">
+        <v>12</v>
+      </c>
+      <c r="D76">
+        <v>3010</v>
+      </c>
+      <c r="F76">
+        <v>3020</v>
+      </c>
+      <c r="G76" t="str">
+        <f>INDEX(Define!E:E,MATCH(F76,Define!D:D))</f>
+        <v>アイテム取得</v>
+      </c>
+      <c r="H76">
+        <v>11030</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77">
+        <v>2010</v>
+      </c>
+      <c r="B77">
+        <v>7</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77">
+        <v>3010</v>
+      </c>
+      <c r="F77">
+        <v>2020</v>
+      </c>
+      <c r="G77" t="str">
+        <f>INDEX(Define!E:E,MATCH(F77,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H77">
+        <v>2011</v>
+      </c>
+      <c r="I77">
+        <v>7</v>
+      </c>
+      <c r="J77">
+        <v>12</v>
+      </c>
+      <c r="K77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78">
+        <v>2010</v>
+      </c>
+      <c r="B78">
+        <v>7</v>
+      </c>
+      <c r="C78">
+        <v>7</v>
+      </c>
+      <c r="D78">
+        <v>3010</v>
+      </c>
+      <c r="F78">
+        <v>5020</v>
+      </c>
+      <c r="G78" t="str">
+        <f>INDEX(Define!E:E,MATCH(F78,Define!D:D))</f>
         <v>強制ボス戦闘</v>
       </c>
-      <c r="H71">
+      <c r="H78">
+        <v>20010</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79">
+        <v>2011</v>
+      </c>
+      <c r="B79">
+        <v>7</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79">
+        <v>3010</v>
+      </c>
+      <c r="F79">
+        <v>2020</v>
+      </c>
+      <c r="G79" t="str">
+        <f>INDEX(Define!E:E,MATCH(F79,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H79">
+        <v>2012</v>
+      </c>
+      <c r="I79">
+        <v>7</v>
+      </c>
+      <c r="J79">
+        <v>12</v>
+      </c>
+      <c r="K79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80">
+        <v>2011</v>
+      </c>
+      <c r="B80">
+        <v>7</v>
+      </c>
+      <c r="C80">
+        <v>7</v>
+      </c>
+      <c r="D80">
+        <v>3010</v>
+      </c>
+      <c r="F80">
+        <v>5020</v>
+      </c>
+      <c r="G80" t="str">
+        <f>INDEX(Define!E:E,MATCH(F80,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H80">
+        <v>20020</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81">
+        <v>2012</v>
+      </c>
+      <c r="B81">
+        <v>7</v>
+      </c>
+      <c r="C81">
+        <v>7</v>
+      </c>
+      <c r="D81">
+        <v>3010</v>
+      </c>
+      <c r="F81">
+        <v>5020</v>
+      </c>
+      <c r="G81" t="str">
+        <f>INDEX(Define!E:E,MATCH(F81,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H81">
         <v>20030</v>
       </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71" t="b">
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5563,7 +5894,7 @@
     </row>
     <row r="14" spans="4:12">
       <c r="D14">
-        <v>6020</v>
+        <v>6011</v>
       </c>
       <c r="E14" t="s">
         <v>106</v>
@@ -5577,10 +5908,34 @@
     </row>
     <row r="15" spans="4:5">
       <c r="D15">
-        <v>7010</v>
+        <v>6020</v>
       </c>
       <c r="E15" t="s">
         <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="4:5">
+      <c r="D16">
+        <v>7010</v>
+      </c>
+      <c r="E16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5">
+      <c r="D17">
+        <v>7020</v>
+      </c>
+      <c r="E17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="4:5">
+      <c r="D18">
+        <v>7021</v>
+      </c>
+      <c r="E18" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="5:5">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="113">
   <si>
     <t>Id</t>
   </si>
@@ -358,6 +358,9 @@
   </si>
   <si>
     <t>怨嗟床解除</t>
+  </si>
+  <si>
+    <t>イベント終了明示</t>
   </si>
 </sst>
 </file>
@@ -365,10 +368,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -391,15 +394,33 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -414,6 +435,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -421,38 +449,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -466,24 +470,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -497,19 +493,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -522,7 +510,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -544,7 +547,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -556,37 +643,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,133 +721,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -738,60 +741,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -815,8 +768,49 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -835,6 +829,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -843,145 +846,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2088,7 +2091,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
@@ -2841,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2852,20 +2855,20 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24">
         <v>3010</v>
       </c>
       <c r="F24">
-        <v>7010</v>
+        <v>9010</v>
       </c>
       <c r="G24" t="str">
         <f>INDEX(Define!E:E,MATCH(F24,Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H24">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -2885,7 +2888,7 @@
         <v>8</v>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25">
         <v>3010</v>
@@ -2912,32 +2915,32 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26">
         <v>3010</v>
       </c>
       <c r="F26">
-        <v>2020</v>
+        <v>7010</v>
       </c>
       <c r="G26" t="str">
         <f>INDEX(Define!E:E,MATCH(F26,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>ダメージ床</v>
       </c>
       <c r="H26">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
@@ -2948,7 +2951,7 @@
         <v>31</v>
       </c>
       <c r="B27">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -2967,10 +2970,10 @@
         <v>30</v>
       </c>
       <c r="I27">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -2981,32 +2984,32 @@
         <v>31</v>
       </c>
       <c r="B28">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D28">
         <v>3010</v>
       </c>
       <c r="F28">
-        <v>6010</v>
+        <v>2020</v>
       </c>
       <c r="G28" t="str">
         <f>INDEX(Define!E:E,MATCH(F28,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H28">
-        <v>1310</v>
+        <v>30</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3017,13 +3020,17 @@
         <v>13</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D29">
         <v>3010</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>6010</v>
+      </c>
+      <c r="G29" t="str">
+        <f>INDEX(Define!E:E,MATCH(F29,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H29">
         <v>1310</v>
@@ -3043,23 +3050,19 @@
         <v>31</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D30">
         <v>3010</v>
       </c>
       <c r="F30">
-        <v>3010</v>
-      </c>
-      <c r="G30" t="str">
-        <f>INDEX(Define!E:E,MATCH(F30,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>2020</v>
+        <v>1310</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -3073,35 +3076,35 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D31">
         <v>3010</v>
       </c>
       <c r="F31">
-        <v>2020</v>
+        <v>3010</v>
       </c>
       <c r="G31" t="str">
         <f>INDEX(Define!E:E,MATCH(F31,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H31">
-        <v>30</v>
+        <v>2020</v>
       </c>
       <c r="I31">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3109,7 +3112,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C32">
         <v>9</v>
@@ -3128,7 +3131,7 @@
         <v>30</v>
       </c>
       <c r="I32">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -3142,32 +3145,32 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D33">
         <v>3010</v>
       </c>
       <c r="F33">
-        <v>5020</v>
+        <v>2020</v>
       </c>
       <c r="G33" t="str">
         <f>INDEX(Define!E:E,MATCH(F33,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H33">
-        <v>2010</v>
+        <v>30</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3178,20 +3181,20 @@
         <v>4</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>3010</v>
       </c>
       <c r="F34">
-        <v>3010</v>
+        <v>5020</v>
       </c>
       <c r="G34" t="str">
         <f>INDEX(Define!E:E,MATCH(F34,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H34">
-        <v>2030</v>
+        <v>2010</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -3205,26 +3208,26 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C35">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D35">
         <v>3010</v>
       </c>
       <c r="F35">
-        <v>2010</v>
+        <v>3010</v>
       </c>
       <c r="G35" t="str">
         <f>INDEX(Define!E:E,MATCH(F35,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>2030</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -3233,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3241,29 +3244,29 @@
         <v>40</v>
       </c>
       <c r="B36">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D36">
         <v>3010</v>
       </c>
       <c r="F36">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="G36" t="str">
         <f>INDEX(Define!E:E,MATCH(F36,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H36">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -3274,32 +3277,32 @@
         <v>40</v>
       </c>
       <c r="B37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C37">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D37">
         <v>3010</v>
       </c>
       <c r="F37">
-        <v>6010</v>
+        <v>2020</v>
       </c>
       <c r="G37" t="str">
         <f>INDEX(Define!E:E,MATCH(F37,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H37">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3307,16 +3310,20 @@
         <v>40</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D38">
         <v>3010</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>6010</v>
+      </c>
+      <c r="G38" t="str">
+        <f>INDEX(Define!E:E,MATCH(F38,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H38">
         <v>45</v>
@@ -3333,35 +3340,31 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C39">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D39">
         <v>3010</v>
       </c>
       <c r="F39">
-        <v>2020</v>
-      </c>
-      <c r="G39" t="str">
-        <f>INDEX(Define!E:E,MATCH(F39,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I39">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3369,10 +3372,10 @@
         <v>41</v>
       </c>
       <c r="B40">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D40">
         <v>3010</v>
@@ -3385,13 +3388,13 @@
         <v>ダンジョン移動</v>
       </c>
       <c r="H40">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I40">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J40">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -3402,32 +3405,32 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C41">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D41">
         <v>3010</v>
       </c>
       <c r="F41">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="G41" t="str">
         <f>INDEX(Define!E:E,MATCH(F41,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H41">
-        <v>2130</v>
+        <v>42</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -3435,23 +3438,23 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D42">
         <v>3010</v>
       </c>
       <c r="F42">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="G42" t="str">
         <f>INDEX(Define!E:E,MATCH(F42,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H42">
-        <v>11010</v>
+        <v>2130</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -3468,7 +3471,7 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -3501,7 +3504,7 @@
         <v>41</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -3534,23 +3537,23 @@
         <v>41</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D45">
         <v>3010</v>
       </c>
       <c r="F45">
-        <v>1010</v>
+        <v>3020</v>
       </c>
       <c r="G45" t="str">
         <f>INDEX(Define!E:E,MATCH(F45,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H45">
-        <v>1040</v>
+        <v>11010</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -3570,7 +3573,7 @@
         <v>4</v>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D46">
         <v>3010</v>
@@ -3583,7 +3586,7 @@
         <v>Adv再生</v>
       </c>
       <c r="H46">
-        <v>100</v>
+        <v>1040</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -3609,14 +3612,14 @@
         <v>3010</v>
       </c>
       <c r="F47">
-        <v>5010</v>
+        <v>1010</v>
       </c>
       <c r="G47" t="str">
         <f>INDEX(Define!E:E,MATCH(F47,Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>Adv再生</v>
       </c>
       <c r="H47">
-        <v>3020</v>
+        <v>100</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -3642,14 +3645,14 @@
         <v>3010</v>
       </c>
       <c r="F48">
-        <v>6010</v>
+        <v>5010</v>
       </c>
       <c r="G48" t="str">
         <f>INDEX(Define!E:E,MATCH(F48,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H48">
-        <v>43</v>
+        <v>3020</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -3669,13 +3672,17 @@
         <v>4</v>
       </c>
       <c r="C49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49">
         <v>3010</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>6010</v>
+      </c>
+      <c r="G49" t="str">
+        <f>INDEX(Define!E:E,MATCH(F49,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H49">
         <v>43</v>
@@ -3698,20 +3705,16 @@
         <v>4</v>
       </c>
       <c r="C50">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D50">
         <v>3010</v>
       </c>
       <c r="F50">
-        <v>7010</v>
-      </c>
-      <c r="G50" t="str">
-        <f>INDEX(Define!E:E,MATCH(F50,Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>0</v>
       </c>
       <c r="H50">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -3720,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -3728,7 +3731,7 @@
         <v>41</v>
       </c>
       <c r="B51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C51">
         <v>13</v>
@@ -3761,7 +3764,7 @@
         <v>41</v>
       </c>
       <c r="B52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C52">
         <v>13</v>
@@ -3794,7 +3797,7 @@
         <v>41</v>
       </c>
       <c r="B53">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C53">
         <v>13</v>
@@ -3803,14 +3806,14 @@
         <v>3010</v>
       </c>
       <c r="F53">
-        <v>6011</v>
+        <v>7010</v>
       </c>
       <c r="G53" t="str">
         <f>INDEX(Define!E:E,MATCH(F53,Define!D:D))</f>
-        <v>指定のイベントマスを表示する</v>
+        <v>ダメージ床</v>
       </c>
       <c r="H53">
-        <v>713</v>
+        <v>20</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -3819,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -3827,7 +3830,7 @@
         <v>41</v>
       </c>
       <c r="B54">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C54">
         <v>13</v>
@@ -3836,7 +3839,11 @@
         <v>3010</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>6011</v>
+      </c>
+      <c r="G54" t="str">
+        <f>INDEX(Define!E:E,MATCH(F54,Define!D:D))</f>
+        <v>指定のイベントマスを表示する</v>
       </c>
       <c r="H54">
         <v>713</v>
@@ -3856,7 +3863,7 @@
         <v>41</v>
       </c>
       <c r="B55">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C55">
         <v>13</v>
@@ -3865,14 +3872,10 @@
         <v>3010</v>
       </c>
       <c r="F55">
-        <v>1010</v>
-      </c>
-      <c r="G55" t="str">
-        <f>INDEX(Define!E:E,MATCH(F55,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>0</v>
       </c>
       <c r="H55">
-        <v>110</v>
+        <v>713</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -3898,14 +3901,14 @@
         <v>3010</v>
       </c>
       <c r="F56">
-        <v>7020</v>
+        <v>1010</v>
       </c>
       <c r="G56" t="str">
         <f>INDEX(Define!E:E,MATCH(F56,Define!D:D))</f>
-        <v>怨嗟床</v>
+        <v>Adv再生</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -3931,14 +3934,14 @@
         <v>3010</v>
       </c>
       <c r="F57">
-        <v>1010</v>
+        <v>7020</v>
       </c>
       <c r="G57" t="str">
         <f>INDEX(Define!E:E,MATCH(F57,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>怨嗟床</v>
       </c>
       <c r="H57">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -3955,7 +3958,7 @@
         <v>41</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C58">
         <v>13</v>
@@ -3964,14 +3967,14 @@
         <v>3010</v>
       </c>
       <c r="F58">
-        <v>7021</v>
+        <v>1010</v>
       </c>
       <c r="G58" t="str">
         <f>INDEX(Define!E:E,MATCH(F58,Define!D:D))</f>
-        <v>怨嗟床解除</v>
+        <v>Adv再生</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -3988,7 +3991,7 @@
         <v>41</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C59">
         <v>13</v>
@@ -3997,14 +4000,14 @@
         <v>3010</v>
       </c>
       <c r="F59">
-        <v>6010</v>
+        <v>9010</v>
       </c>
       <c r="G59" t="str">
         <f>INDEX(Define!E:E,MATCH(F59,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H59">
-        <v>813</v>
+        <v>0</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -4021,7 +4024,7 @@
         <v>41</v>
       </c>
       <c r="B60">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C60">
         <v>13</v>
@@ -4030,10 +4033,14 @@
         <v>3010</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>1010</v>
+      </c>
+      <c r="G60" t="str">
+        <f>INDEX(Define!E:E,MATCH(F60,Define!D:D))</f>
+        <v>Adv再生</v>
       </c>
       <c r="H60">
-        <v>813</v>
+        <v>130</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -4047,26 +4054,26 @@
     </row>
     <row r="61" spans="1:11">
       <c r="A61">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B61">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D61">
         <v>3010</v>
       </c>
       <c r="F61">
-        <v>3010</v>
+        <v>7021</v>
       </c>
       <c r="G61" t="str">
         <f>INDEX(Define!E:E,MATCH(F61,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>怨嗟床解除</v>
       </c>
       <c r="H61">
-        <v>2020</v>
+        <v>0</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -4080,26 +4087,26 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B62">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D62">
         <v>3010</v>
       </c>
       <c r="F62">
-        <v>5020</v>
+        <v>6010</v>
       </c>
       <c r="G62" t="str">
         <f>INDEX(Define!E:E,MATCH(F62,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H62">
-        <v>3010</v>
+        <v>813</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -4113,26 +4120,22 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C63">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D63">
         <v>3010</v>
       </c>
       <c r="F63">
-        <v>1010</v>
-      </c>
-      <c r="G63" t="str">
-        <f>INDEX(Define!E:E,MATCH(F63,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>0</v>
       </c>
       <c r="H63">
-        <v>100</v>
+        <v>813</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -4149,23 +4152,23 @@
         <v>42</v>
       </c>
       <c r="B64">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C64">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D64">
         <v>3010</v>
       </c>
       <c r="F64">
-        <v>5010</v>
+        <v>3010</v>
       </c>
       <c r="G64" t="str">
         <f>INDEX(Define!E:E,MATCH(F64,Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H64">
-        <v>3030</v>
+        <v>2020</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -4182,7 +4185,7 @@
         <v>42</v>
       </c>
       <c r="B65">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C65">
         <v>8</v>
@@ -4191,14 +4194,14 @@
         <v>3010</v>
       </c>
       <c r="F65">
-        <v>1010</v>
+        <v>5020</v>
       </c>
       <c r="G65" t="str">
         <f>INDEX(Define!E:E,MATCH(F65,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H65">
-        <v>100</v>
+        <v>3010</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -4215,7 +4218,7 @@
         <v>42</v>
       </c>
       <c r="B66">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C66">
         <v>8</v>
@@ -4224,14 +4227,14 @@
         <v>3010</v>
       </c>
       <c r="F66">
-        <v>5010</v>
+        <v>1010</v>
       </c>
       <c r="G66" t="str">
         <f>INDEX(Define!E:E,MATCH(F66,Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>Adv再生</v>
       </c>
       <c r="H66">
-        <v>3040</v>
+        <v>100</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -4248,23 +4251,23 @@
         <v>42</v>
       </c>
       <c r="B67">
+        <v>4</v>
+      </c>
+      <c r="C67">
         <v>8</v>
       </c>
-      <c r="C67">
-        <v>10</v>
-      </c>
       <c r="D67">
         <v>3010</v>
       </c>
       <c r="F67">
-        <v>1010</v>
+        <v>5010</v>
       </c>
       <c r="G67" t="str">
         <f>INDEX(Define!E:E,MATCH(F67,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H67">
-        <v>1030</v>
+        <v>3030</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -4281,23 +4284,23 @@
         <v>42</v>
       </c>
       <c r="B68">
+        <v>12</v>
+      </c>
+      <c r="C68">
         <v>8</v>
       </c>
-      <c r="C68">
-        <v>10</v>
-      </c>
       <c r="D68">
         <v>3010</v>
       </c>
       <c r="F68">
-        <v>6020</v>
+        <v>1010</v>
       </c>
       <c r="G68" t="str">
         <f>INDEX(Define!E:E,MATCH(F68,Define!D:D))</f>
-        <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+        <v>Adv再生</v>
       </c>
       <c r="H68">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -4314,19 +4317,23 @@
         <v>42</v>
       </c>
       <c r="B69">
+        <v>12</v>
+      </c>
+      <c r="C69">
         <v>8</v>
       </c>
-      <c r="C69">
-        <v>9</v>
-      </c>
       <c r="D69">
         <v>3010</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>5010</v>
+      </c>
+      <c r="G69" t="str">
+        <f>INDEX(Define!E:E,MATCH(F69,Define!D:D))</f>
+        <v>強制戦闘</v>
       </c>
       <c r="H69">
-        <v>89</v>
+        <v>3040</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -4340,26 +4347,26 @@
     </row>
     <row r="70" spans="1:11">
       <c r="A70">
+        <v>42</v>
+      </c>
+      <c r="B70">
+        <v>8</v>
+      </c>
+      <c r="C70">
+        <v>10</v>
+      </c>
+      <c r="D70">
+        <v>3010</v>
+      </c>
+      <c r="F70">
         <v>1010</v>
-      </c>
-      <c r="B70">
-        <v>13</v>
-      </c>
-      <c r="C70">
-        <v>13</v>
-      </c>
-      <c r="D70">
-        <v>3010</v>
-      </c>
-      <c r="F70">
-        <v>2010</v>
       </c>
       <c r="G70" t="str">
         <f>INDEX(Define!E:E,MATCH(F70,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>Adv再生</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -4368,31 +4375,31 @@
         <v>0</v>
       </c>
       <c r="K70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71">
-        <v>1010</v>
+        <v>42</v>
       </c>
       <c r="B71">
+        <v>8</v>
+      </c>
+      <c r="C71">
         <v>10</v>
       </c>
-      <c r="C71">
-        <v>4</v>
-      </c>
       <c r="D71">
         <v>3010</v>
       </c>
       <c r="F71">
-        <v>3030</v>
+        <v>6020</v>
       </c>
       <c r="G71" t="str">
         <f>INDEX(Define!E:E,MATCH(F71,Define!D:D))</f>
-        <v>魔法入手</v>
+        <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
       </c>
       <c r="H71">
-        <v>30010</v>
+        <v>89</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -4406,26 +4413,22 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72">
-        <v>1020</v>
+        <v>42</v>
       </c>
       <c r="B72">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C72">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D72">
         <v>3010</v>
       </c>
       <c r="F72">
-        <v>2010</v>
-      </c>
-      <c r="G72" t="str">
-        <f>INDEX(Define!E:E,MATCH(F72,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>0</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -4434,31 +4437,31 @@
         <v>0</v>
       </c>
       <c r="K72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B73">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C73">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D73">
         <v>3010</v>
       </c>
       <c r="F73">
-        <v>3030</v>
+        <v>2010</v>
       </c>
       <c r="G73" t="str">
         <f>INDEX(Define!E:E,MATCH(F73,Define!D:D))</f>
-        <v>魔法入手</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H73">
-        <v>30020</v>
+        <v>0</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -4467,31 +4470,31 @@
         <v>0</v>
       </c>
       <c r="K73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D74">
         <v>3010</v>
       </c>
       <c r="F74">
-        <v>3020</v>
+        <v>3030</v>
       </c>
       <c r="G74" t="str">
         <f>INDEX(Define!E:E,MATCH(F74,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>魔法入手</v>
       </c>
       <c r="H74">
-        <v>11010</v>
+        <v>30010</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -4508,23 +4511,23 @@
         <v>1020</v>
       </c>
       <c r="B75">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C75">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D75">
         <v>3010</v>
       </c>
       <c r="F75">
-        <v>3020</v>
+        <v>2010</v>
       </c>
       <c r="G75" t="str">
         <f>INDEX(Define!E:E,MATCH(F75,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H75">
-        <v>11020</v>
+        <v>0</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -4533,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -4541,7 +4544,7 @@
         <v>1020</v>
       </c>
       <c r="B76">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C76">
         <v>12</v>
@@ -4550,14 +4553,14 @@
         <v>3010</v>
       </c>
       <c r="F76">
-        <v>3020</v>
+        <v>3030</v>
       </c>
       <c r="G76" t="str">
         <f>INDEX(Define!E:E,MATCH(F76,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>魔法入手</v>
       </c>
       <c r="H76">
-        <v>11030</v>
+        <v>30020</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -4571,10 +4574,10 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77">
-        <v>2010</v>
+        <v>1020</v>
       </c>
       <c r="B77">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -4583,47 +4586,47 @@
         <v>3010</v>
       </c>
       <c r="F77">
-        <v>2020</v>
+        <v>3020</v>
       </c>
       <c r="G77" t="str">
         <f>INDEX(Define!E:E,MATCH(F77,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H77">
-        <v>2011</v>
+        <v>11010</v>
       </c>
       <c r="I77">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J77">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78">
-        <v>2010</v>
+        <v>1020</v>
       </c>
       <c r="B78">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C78">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D78">
         <v>3010</v>
       </c>
       <c r="F78">
-        <v>5020</v>
+        <v>3020</v>
       </c>
       <c r="G78" t="str">
         <f>INDEX(Define!E:E,MATCH(F78,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H78">
-        <v>20010</v>
+        <v>11020</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -4637,73 +4640,73 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79">
-        <v>2011</v>
+        <v>1020</v>
       </c>
       <c r="B79">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D79">
         <v>3010</v>
       </c>
       <c r="F79">
-        <v>2020</v>
+        <v>3020</v>
       </c>
       <c r="G79" t="str">
         <f>INDEX(Define!E:E,MATCH(F79,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H79">
-        <v>2012</v>
+        <v>11030</v>
       </c>
       <c r="I79">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J79">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B80">
         <v>7</v>
       </c>
       <c r="C80">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D80">
         <v>3010</v>
       </c>
       <c r="F80">
-        <v>5020</v>
+        <v>2020</v>
       </c>
       <c r="G80" t="str">
         <f>INDEX(Define!E:E,MATCH(F80,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H80">
-        <v>20020</v>
+        <v>2011</v>
       </c>
       <c r="I80">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J80">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B81">
         <v>7</v>
@@ -4722,15 +4725,114 @@
         <v>強制ボス戦闘</v>
       </c>
       <c r="H81">
+        <v>20010</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82">
+        <v>2011</v>
+      </c>
+      <c r="B82">
+        <v>7</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82">
+        <v>3010</v>
+      </c>
+      <c r="F82">
+        <v>2020</v>
+      </c>
+      <c r="G82" t="str">
+        <f>INDEX(Define!E:E,MATCH(F82,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H82">
+        <v>2012</v>
+      </c>
+      <c r="I82">
+        <v>7</v>
+      </c>
+      <c r="J82">
+        <v>12</v>
+      </c>
+      <c r="K82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83">
+        <v>2011</v>
+      </c>
+      <c r="B83">
+        <v>7</v>
+      </c>
+      <c r="C83">
+        <v>7</v>
+      </c>
+      <c r="D83">
+        <v>3010</v>
+      </c>
+      <c r="F83">
+        <v>5020</v>
+      </c>
+      <c r="G83" t="str">
+        <f>INDEX(Define!E:E,MATCH(F83,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H83">
+        <v>20020</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84">
+        <v>2012</v>
+      </c>
+      <c r="B84">
+        <v>7</v>
+      </c>
+      <c r="C84">
+        <v>7</v>
+      </c>
+      <c r="D84">
+        <v>3010</v>
+      </c>
+      <c r="F84">
+        <v>5020</v>
+      </c>
+      <c r="G84" t="str">
+        <f>INDEX(Define!E:E,MATCH(F84,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
+      </c>
+      <c r="H84">
         <v>20030</v>
       </c>
-      <c r="I81">
-        <v>0</v>
-      </c>
-      <c r="J81">
-        <v>0</v>
-      </c>
-      <c r="K81" t="b">
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5938,6 +6040,14 @@
         <v>111</v>
       </c>
     </row>
+    <row r="19" spans="4:5">
+      <c r="D19">
+        <v>9010</v>
+      </c>
+      <c r="E19" t="s">
+        <v>112</v>
+      </c>
+    </row>
     <row r="27" spans="5:5">
       <c r="E27" s="1"/>
     </row>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -368,10 +368,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -394,8 +394,106 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -410,30 +508,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -442,44 +517,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -493,46 +531,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -547,7 +547,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -559,25 +583,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,25 +595,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -631,7 +619,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -643,91 +727,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -738,39 +738,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -785,17 +752,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -833,8 +789,52 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -846,145 +846,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2091,7 +2091,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
@@ -2141,7 +2141,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>3010</v>
@@ -2174,20 +2174,20 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>3010</v>
       </c>
       <c r="F3">
-        <v>4020</v>
+        <v>5010</v>
       </c>
       <c r="G3" t="str">
         <f>INDEX(Define!E:E,MATCH(F3,Define!D:D))</f>
-        <v>選択して仲間を増やす</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2207,20 +2207,20 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>3010</v>
       </c>
       <c r="F4">
-        <v>5010</v>
+        <v>2010</v>
       </c>
       <c r="G4" t="str">
         <f>INDEX(Define!E:E,MATCH(F4,Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H4">
-        <v>1010</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2229,18 +2229,18 @@
         <v>0</v>
       </c>
       <c r="K4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>3010</v>
@@ -2270,23 +2270,23 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="F6">
-        <v>2010</v>
+        <v>6010</v>
       </c>
       <c r="G6" t="str">
         <f>INDEX(Define!E:E,MATCH(F6,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2303,7 +2303,7 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <v>9</v>
@@ -2312,11 +2312,7 @@
         <v>3010</v>
       </c>
       <c r="F7">
-        <v>6010</v>
-      </c>
-      <c r="G7" t="str">
-        <f>INDEX(Define!E:E,MATCH(F7,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>79</v>
@@ -2339,36 +2335,40 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>3010</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>2020</v>
+      </c>
+      <c r="G8" t="str">
+        <f>INDEX(Define!E:E,MATCH(F8,Define!D:D))</f>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H8">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>3010</v>
@@ -2381,13 +2381,13 @@
         <v>ダンジョン移動</v>
       </c>
       <c r="H9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -2398,32 +2398,32 @@
         <v>21</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <v>3010</v>
       </c>
       <c r="F10">
-        <v>2020</v>
+        <v>5020</v>
       </c>
       <c r="G10" t="str">
         <f>INDEX(Define!E:E,MATCH(F10,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H10">
-        <v>20</v>
+        <v>1020</v>
       </c>
       <c r="I10">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2431,23 +2431,23 @@
         <v>21</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>3010</v>
       </c>
       <c r="F11">
-        <v>5020</v>
+        <v>6010</v>
       </c>
       <c r="G11" t="str">
         <f>INDEX(Define!E:E,MATCH(F11,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H11">
-        <v>1020</v>
+        <v>213</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2464,20 +2464,16 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D12">
         <v>3010</v>
       </c>
       <c r="F12">
-        <v>6010</v>
-      </c>
-      <c r="G12" t="str">
-        <f>INDEX(Define!E:E,MATCH(F12,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>213</v>
@@ -2497,19 +2493,23 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C13">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>3010</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>3010</v>
+      </c>
+      <c r="G13" t="str">
+        <f>INDEX(Define!E:E,MATCH(F13,Define!D:D))</f>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H13">
-        <v>213</v>
+        <v>2010</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2526,26 +2526,26 @@
         <v>21</v>
       </c>
       <c r="B14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D14">
         <v>3010</v>
       </c>
       <c r="F14">
-        <v>3010</v>
+        <v>3020</v>
       </c>
       <c r="G14" t="str">
         <f>INDEX(Define!E:E,MATCH(F14,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H14">
-        <v>2010</v>
+        <v>1000</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2556,35 +2556,35 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D15">
         <v>3010</v>
       </c>
       <c r="F15">
-        <v>3020</v>
+        <v>2010</v>
       </c>
       <c r="G15" t="str">
         <f>INDEX(Define!E:E,MATCH(F15,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2592,29 +2592,29 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D16">
         <v>3010</v>
       </c>
       <c r="F16">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="G16" t="str">
         <f>INDEX(Define!E:E,MATCH(F16,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -2625,10 +2625,10 @@
         <v>30</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D17">
         <v>3010</v>
@@ -2644,10 +2644,10 @@
         <v>31</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -2658,10 +2658,10 @@
         <v>30</v>
       </c>
       <c r="B18">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C18">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>3010</v>
@@ -2674,13 +2674,13 @@
         <v>ダンジョン移動</v>
       </c>
       <c r="H18">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I18">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J18">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>30</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>32</v>
       </c>
       <c r="I19">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J19">
         <v>9</v>
@@ -2724,32 +2724,32 @@
         <v>30</v>
       </c>
       <c r="B20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
         <v>3010</v>
       </c>
       <c r="F20">
-        <v>2020</v>
+        <v>6010</v>
       </c>
       <c r="G20" t="str">
         <f>INDEX(Define!E:E,MATCH(F20,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H20">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="I20">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2757,7 +2757,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -2766,11 +2766,7 @@
         <v>3010</v>
       </c>
       <c r="F21">
-        <v>6010</v>
-      </c>
-      <c r="G21" t="str">
-        <f>INDEX(Define!E:E,MATCH(F21,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>71</v>
@@ -2790,19 +2786,23 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D22">
         <v>3010</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1010</v>
+      </c>
+      <c r="G22" t="str">
+        <f>INDEX(Define!E:E,MATCH(F22,Define!D:D))</f>
+        <v>Adv再生</v>
       </c>
       <c r="H22">
-        <v>71</v>
+        <v>1030</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -2811,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2828,14 +2828,14 @@
         <v>3010</v>
       </c>
       <c r="F23">
-        <v>1010</v>
+        <v>9010</v>
       </c>
       <c r="G23" t="str">
         <f>INDEX(Define!E:E,MATCH(F23,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H23">
-        <v>1030</v>
+        <v>0</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -2855,20 +2855,20 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <v>3010</v>
       </c>
       <c r="F24">
-        <v>9010</v>
+        <v>7010</v>
       </c>
       <c r="G24" t="str">
         <f>INDEX(Define!E:E,MATCH(F24,Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>ダメージ床</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -2888,7 +2888,7 @@
         <v>8</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25">
         <v>3010</v>
@@ -2915,32 +2915,32 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26">
         <v>3010</v>
       </c>
       <c r="F26">
-        <v>7010</v>
+        <v>2020</v>
       </c>
       <c r="G26" t="str">
         <f>INDEX(Define!E:E,MATCH(F26,Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H26">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
@@ -2951,7 +2951,7 @@
         <v>31</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -2970,10 +2970,10 @@
         <v>30</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -2984,32 +2984,32 @@
         <v>31</v>
       </c>
       <c r="B28">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D28">
         <v>3010</v>
       </c>
       <c r="F28">
-        <v>2020</v>
+        <v>6010</v>
       </c>
       <c r="G28" t="str">
         <f>INDEX(Define!E:E,MATCH(F28,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H28">
-        <v>30</v>
+        <v>1310</v>
       </c>
       <c r="I28">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3020,17 +3020,13 @@
         <v>13</v>
       </c>
       <c r="C29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D29">
         <v>3010</v>
       </c>
       <c r="F29">
-        <v>6010</v>
-      </c>
-      <c r="G29" t="str">
-        <f>INDEX(Define!E:E,MATCH(F29,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>1310</v>
@@ -3050,19 +3046,23 @@
         <v>31</v>
       </c>
       <c r="B30">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D30">
         <v>3010</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>3010</v>
+      </c>
+      <c r="G30" t="str">
+        <f>INDEX(Define!E:E,MATCH(F30,Define!D:D))</f>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H30">
-        <v>1310</v>
+        <v>2020</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -3076,35 +3076,35 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D31">
         <v>3010</v>
       </c>
       <c r="F31">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="G31" t="str">
         <f>INDEX(Define!E:E,MATCH(F31,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H31">
-        <v>2020</v>
+        <v>30</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3112,7 +3112,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C32">
         <v>9</v>
@@ -3131,7 +3131,7 @@
         <v>30</v>
       </c>
       <c r="I32">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -3145,32 +3145,32 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C33">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D33">
         <v>3010</v>
       </c>
       <c r="F33">
-        <v>2020</v>
+        <v>5020</v>
       </c>
       <c r="G33" t="str">
         <f>INDEX(Define!E:E,MATCH(F33,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H33">
-        <v>30</v>
+        <v>2010</v>
       </c>
       <c r="I33">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3181,20 +3181,20 @@
         <v>4</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D34">
         <v>3010</v>
       </c>
       <c r="F34">
-        <v>5020</v>
+        <v>3010</v>
       </c>
       <c r="G34" t="str">
         <f>INDEX(Define!E:E,MATCH(F34,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H34">
-        <v>2010</v>
+        <v>2030</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -3208,26 +3208,26 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D35">
         <v>3010</v>
       </c>
       <c r="F35">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="G35" t="str">
         <f>INDEX(Define!E:E,MATCH(F35,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H35">
-        <v>2030</v>
+        <v>0</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -3236,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3244,29 +3244,29 @@
         <v>40</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C36">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>3010</v>
       </c>
       <c r="F36">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="G36" t="str">
         <f>INDEX(Define!E:E,MATCH(F36,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -3277,32 +3277,32 @@
         <v>40</v>
       </c>
       <c r="B37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D37">
         <v>3010</v>
       </c>
       <c r="F37">
-        <v>2020</v>
+        <v>6010</v>
       </c>
       <c r="G37" t="str">
         <f>INDEX(Define!E:E,MATCH(F37,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H37">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I37">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J37">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3310,20 +3310,16 @@
         <v>40</v>
       </c>
       <c r="B38">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D38">
         <v>3010</v>
       </c>
       <c r="F38">
-        <v>6010</v>
-      </c>
-      <c r="G38" t="str">
-        <f>INDEX(Define!E:E,MATCH(F38,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>0</v>
       </c>
       <c r="H38">
         <v>45</v>
@@ -3340,31 +3336,35 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39">
+        <v>41</v>
+      </c>
+      <c r="B39">
+        <v>11</v>
+      </c>
+      <c r="C39">
+        <v>18</v>
+      </c>
+      <c r="D39">
+        <v>3010</v>
+      </c>
+      <c r="F39">
+        <v>2020</v>
+      </c>
+      <c r="G39" t="str">
+        <f>INDEX(Define!E:E,MATCH(F39,Define!D:D))</f>
+        <v>ダンジョン移動</v>
+      </c>
+      <c r="H39">
         <v>40</v>
       </c>
-      <c r="B39">
-        <v>4</v>
-      </c>
-      <c r="C39">
-        <v>5</v>
-      </c>
-      <c r="D39">
-        <v>3010</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>45</v>
-      </c>
       <c r="I39">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3372,10 +3372,10 @@
         <v>41</v>
       </c>
       <c r="B40">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C40">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D40">
         <v>3010</v>
@@ -3388,13 +3388,13 @@
         <v>ダンジョン移動</v>
       </c>
       <c r="H40">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I40">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J40">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -3405,32 +3405,32 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D41">
         <v>3010</v>
       </c>
       <c r="F41">
-        <v>2020</v>
+        <v>3010</v>
       </c>
       <c r="G41" t="str">
         <f>INDEX(Define!E:E,MATCH(F41,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H41">
-        <v>42</v>
+        <v>2130</v>
       </c>
       <c r="I41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -3438,23 +3438,23 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D42">
         <v>3010</v>
       </c>
       <c r="F42">
-        <v>3010</v>
+        <v>3020</v>
       </c>
       <c r="G42" t="str">
         <f>INDEX(Define!E:E,MATCH(F42,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H42">
-        <v>2130</v>
+        <v>11010</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -3471,7 +3471,7 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -3504,7 +3504,7 @@
         <v>41</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -3537,23 +3537,23 @@
         <v>41</v>
       </c>
       <c r="B45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D45">
         <v>3010</v>
       </c>
       <c r="F45">
-        <v>3020</v>
+        <v>1010</v>
       </c>
       <c r="G45" t="str">
         <f>INDEX(Define!E:E,MATCH(F45,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>Adv再生</v>
       </c>
       <c r="H45">
-        <v>11010</v>
+        <v>1040</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -3573,7 +3573,7 @@
         <v>4</v>
       </c>
       <c r="C46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D46">
         <v>3010</v>
@@ -3586,7 +3586,7 @@
         <v>Adv再生</v>
       </c>
       <c r="H46">
-        <v>1040</v>
+        <v>100</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -3612,14 +3612,14 @@
         <v>3010</v>
       </c>
       <c r="F47">
-        <v>1010</v>
+        <v>5010</v>
       </c>
       <c r="G47" t="str">
         <f>INDEX(Define!E:E,MATCH(F47,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H47">
-        <v>100</v>
+        <v>3020</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -3645,14 +3645,14 @@
         <v>3010</v>
       </c>
       <c r="F48">
-        <v>5010</v>
+        <v>6010</v>
       </c>
       <c r="G48" t="str">
         <f>INDEX(Define!E:E,MATCH(F48,Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H48">
-        <v>3020</v>
+        <v>43</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -3672,17 +3672,13 @@
         <v>4</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D49">
         <v>3010</v>
       </c>
       <c r="F49">
-        <v>6010</v>
-      </c>
-      <c r="G49" t="str">
-        <f>INDEX(Define!E:E,MATCH(F49,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>0</v>
       </c>
       <c r="H49">
         <v>43</v>
@@ -3705,16 +3701,20 @@
         <v>4</v>
       </c>
       <c r="C50">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D50">
         <v>3010</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>7010</v>
+      </c>
+      <c r="G50" t="str">
+        <f>INDEX(Define!E:E,MATCH(F50,Define!D:D))</f>
+        <v>ダメージ床</v>
       </c>
       <c r="H50">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -3723,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -3731,7 +3731,7 @@
         <v>41</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C51">
         <v>13</v>
@@ -3764,7 +3764,7 @@
         <v>41</v>
       </c>
       <c r="B52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C52">
         <v>13</v>
@@ -3797,7 +3797,7 @@
         <v>41</v>
       </c>
       <c r="B53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C53">
         <v>13</v>
@@ -3806,14 +3806,14 @@
         <v>3010</v>
       </c>
       <c r="F53">
-        <v>7010</v>
+        <v>6011</v>
       </c>
       <c r="G53" t="str">
         <f>INDEX(Define!E:E,MATCH(F53,Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>指定のイベントマスを表示する</v>
       </c>
       <c r="H53">
-        <v>20</v>
+        <v>713</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -3830,7 +3830,7 @@
         <v>41</v>
       </c>
       <c r="B54">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C54">
         <v>13</v>
@@ -3839,11 +3839,7 @@
         <v>3010</v>
       </c>
       <c r="F54">
-        <v>6011</v>
-      </c>
-      <c r="G54" t="str">
-        <f>INDEX(Define!E:E,MATCH(F54,Define!D:D))</f>
-        <v>指定のイベントマスを表示する</v>
+        <v>0</v>
       </c>
       <c r="H54">
         <v>713</v>
@@ -3863,7 +3859,7 @@
         <v>41</v>
       </c>
       <c r="B55">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C55">
         <v>13</v>
@@ -3872,10 +3868,14 @@
         <v>3010</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>1010</v>
+      </c>
+      <c r="G55" t="str">
+        <f>INDEX(Define!E:E,MATCH(F55,Define!D:D))</f>
+        <v>Adv再生</v>
       </c>
       <c r="H55">
-        <v>713</v>
+        <v>110</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -3901,14 +3901,14 @@
         <v>3010</v>
       </c>
       <c r="F56">
-        <v>1010</v>
+        <v>7020</v>
       </c>
       <c r="G56" t="str">
         <f>INDEX(Define!E:E,MATCH(F56,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>怨嗟床</v>
       </c>
       <c r="H56">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -3934,14 +3934,14 @@
         <v>3010</v>
       </c>
       <c r="F57">
-        <v>7020</v>
+        <v>1010</v>
       </c>
       <c r="G57" t="str">
         <f>INDEX(Define!E:E,MATCH(F57,Define!D:D))</f>
-        <v>怨嗟床</v>
+        <v>Adv再生</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -3967,14 +3967,14 @@
         <v>3010</v>
       </c>
       <c r="F58">
-        <v>1010</v>
+        <v>9010</v>
       </c>
       <c r="G58" t="str">
         <f>INDEX(Define!E:E,MATCH(F58,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H58">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -3991,7 +3991,7 @@
         <v>41</v>
       </c>
       <c r="B59">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C59">
         <v>13</v>
@@ -4000,14 +4000,14 @@
         <v>3010</v>
       </c>
       <c r="F59">
-        <v>9010</v>
+        <v>1010</v>
       </c>
       <c r="G59" t="str">
         <f>INDEX(Define!E:E,MATCH(F59,Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>Adv再生</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -4033,14 +4033,14 @@
         <v>3010</v>
       </c>
       <c r="F60">
-        <v>1010</v>
+        <v>7021</v>
       </c>
       <c r="G60" t="str">
         <f>INDEX(Define!E:E,MATCH(F60,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>怨嗟床解除</v>
       </c>
       <c r="H60">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -4066,14 +4066,14 @@
         <v>3010</v>
       </c>
       <c r="F61">
-        <v>7021</v>
+        <v>6010</v>
       </c>
       <c r="G61" t="str">
         <f>INDEX(Define!E:E,MATCH(F61,Define!D:D))</f>
-        <v>怨嗟床解除</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>813</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -4090,7 +4090,7 @@
         <v>41</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C62">
         <v>13</v>
@@ -4099,11 +4099,7 @@
         <v>3010</v>
       </c>
       <c r="F62">
-        <v>6010</v>
-      </c>
-      <c r="G62" t="str">
-        <f>INDEX(Define!E:E,MATCH(F62,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>0</v>
       </c>
       <c r="H62">
         <v>813</v>
@@ -4120,22 +4116,26 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B63">
         <v>8</v>
       </c>
       <c r="C63">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D63">
         <v>3010</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>3010</v>
+      </c>
+      <c r="G63" t="str">
+        <f>INDEX(Define!E:E,MATCH(F63,Define!D:D))</f>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H63">
-        <v>813</v>
+        <v>2020</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -4155,20 +4155,20 @@
         <v>8</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D64">
         <v>3010</v>
       </c>
       <c r="F64">
-        <v>3010</v>
+        <v>5020</v>
       </c>
       <c r="G64" t="str">
         <f>INDEX(Define!E:E,MATCH(F64,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H64">
-        <v>2020</v>
+        <v>3010</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -4185,7 +4185,7 @@
         <v>42</v>
       </c>
       <c r="B65">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C65">
         <v>8</v>
@@ -4194,14 +4194,14 @@
         <v>3010</v>
       </c>
       <c r="F65">
-        <v>5020</v>
+        <v>1010</v>
       </c>
       <c r="G65" t="str">
         <f>INDEX(Define!E:E,MATCH(F65,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>Adv再生</v>
       </c>
       <c r="H65">
-        <v>3010</v>
+        <v>100</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -4227,14 +4227,14 @@
         <v>3010</v>
       </c>
       <c r="F66">
-        <v>1010</v>
+        <v>5010</v>
       </c>
       <c r="G66" t="str">
         <f>INDEX(Define!E:E,MATCH(F66,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H66">
-        <v>100</v>
+        <v>3030</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -4251,7 +4251,7 @@
         <v>42</v>
       </c>
       <c r="B67">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C67">
         <v>8</v>
@@ -4260,14 +4260,14 @@
         <v>3010</v>
       </c>
       <c r="F67">
-        <v>5010</v>
+        <v>1010</v>
       </c>
       <c r="G67" t="str">
         <f>INDEX(Define!E:E,MATCH(F67,Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>Adv再生</v>
       </c>
       <c r="H67">
-        <v>3030</v>
+        <v>100</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -4293,14 +4293,14 @@
         <v>3010</v>
       </c>
       <c r="F68">
-        <v>1010</v>
+        <v>5010</v>
       </c>
       <c r="G68" t="str">
         <f>INDEX(Define!E:E,MATCH(F68,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H68">
-        <v>100</v>
+        <v>3040</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -4317,23 +4317,23 @@
         <v>42</v>
       </c>
       <c r="B69">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C69">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D69">
         <v>3010</v>
       </c>
       <c r="F69">
-        <v>5010</v>
+        <v>1010</v>
       </c>
       <c r="G69" t="str">
         <f>INDEX(Define!E:E,MATCH(F69,Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>Adv再生</v>
       </c>
       <c r="H69">
-        <v>3040</v>
+        <v>1030</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -4359,14 +4359,14 @@
         <v>3010</v>
       </c>
       <c r="F70">
-        <v>1010</v>
+        <v>6020</v>
       </c>
       <c r="G70" t="str">
         <f>INDEX(Define!E:E,MATCH(F70,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
       </c>
       <c r="H70">
-        <v>1030</v>
+        <v>89</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -4386,17 +4386,13 @@
         <v>8</v>
       </c>
       <c r="C71">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D71">
         <v>3010</v>
       </c>
       <c r="F71">
-        <v>6020</v>
-      </c>
-      <c r="G71" t="str">
-        <f>INDEX(Define!E:E,MATCH(F71,Define!D:D))</f>
-        <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+        <v>0</v>
       </c>
       <c r="H71">
         <v>89</v>
@@ -4413,22 +4409,26 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72">
-        <v>42</v>
+        <v>1010</v>
       </c>
       <c r="B72">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C72">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D72">
         <v>3010</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>2010</v>
+      </c>
+      <c r="G72" t="str">
+        <f>INDEX(Define!E:E,MATCH(F72,Define!D:D))</f>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H72">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -4437,7 +4437,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -4445,23 +4445,23 @@
         <v>1010</v>
       </c>
       <c r="B73">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C73">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D73">
         <v>3010</v>
       </c>
       <c r="F73">
-        <v>2010</v>
+        <v>3030</v>
       </c>
       <c r="G73" t="str">
         <f>INDEX(Define!E:E,MATCH(F73,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>魔法入手</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>30010</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -4470,31 +4470,31 @@
         <v>0</v>
       </c>
       <c r="K73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="B74">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C74">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D74">
         <v>3010</v>
       </c>
       <c r="F74">
-        <v>3030</v>
+        <v>2010</v>
       </c>
       <c r="G74" t="str">
         <f>INDEX(Define!E:E,MATCH(F74,Define!D:D))</f>
-        <v>魔法入手</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H74">
-        <v>30010</v>
+        <v>0</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -4511,23 +4511,23 @@
         <v>1020</v>
       </c>
       <c r="B75">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C75">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D75">
         <v>3010</v>
       </c>
       <c r="F75">
-        <v>2010</v>
+        <v>3030</v>
       </c>
       <c r="G75" t="str">
         <f>INDEX(Define!E:E,MATCH(F75,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>魔法入手</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>30020</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -4544,23 +4544,23 @@
         <v>1020</v>
       </c>
       <c r="B76">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D76">
         <v>3010</v>
       </c>
       <c r="F76">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="G76" t="str">
         <f>INDEX(Define!E:E,MATCH(F76,Define!D:D))</f>
-        <v>魔法入手</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H76">
-        <v>30020</v>
+        <v>11010</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -4577,10 +4577,10 @@
         <v>1020</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D77">
         <v>3010</v>
@@ -4593,7 +4593,7 @@
         <v>アイテム取得</v>
       </c>
       <c r="H77">
-        <v>11010</v>
+        <v>11020</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -4610,10 +4610,10 @@
         <v>1020</v>
       </c>
       <c r="B78">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C78">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D78">
         <v>3010</v>
@@ -4626,7 +4626,7 @@
         <v>アイテム取得</v>
       </c>
       <c r="H78">
-        <v>11020</v>
+        <v>11030</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -4640,35 +4640,35 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79">
-        <v>1020</v>
+        <v>2010</v>
       </c>
       <c r="B79">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C79">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D79">
         <v>3010</v>
       </c>
       <c r="F79">
-        <v>3020</v>
+        <v>2020</v>
       </c>
       <c r="G79" t="str">
         <f>INDEX(Define!E:E,MATCH(F79,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H79">
-        <v>11030</v>
+        <v>2011</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J79">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -4679,62 +4679,62 @@
         <v>7</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D80">
         <v>3010</v>
       </c>
       <c r="F80">
-        <v>2020</v>
+        <v>5020</v>
       </c>
       <c r="G80" t="str">
         <f>INDEX(Define!E:E,MATCH(F80,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H80">
-        <v>2011</v>
+        <v>20010</v>
       </c>
       <c r="I80">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J80">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B81">
         <v>7</v>
       </c>
       <c r="C81">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D81">
         <v>3010</v>
       </c>
       <c r="F81">
-        <v>5020</v>
+        <v>2020</v>
       </c>
       <c r="G81" t="str">
         <f>INDEX(Define!E:E,MATCH(F81,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H81">
-        <v>20010</v>
+        <v>2012</v>
       </c>
       <c r="I81">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -4745,34 +4745,34 @@
         <v>7</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D82">
         <v>3010</v>
       </c>
       <c r="F82">
-        <v>2020</v>
+        <v>5020</v>
       </c>
       <c r="G82" t="str">
         <f>INDEX(Define!E:E,MATCH(F82,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H82">
-        <v>2012</v>
+        <v>20020</v>
       </c>
       <c r="I82">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J82">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B83">
         <v>7</v>
@@ -4791,7 +4791,7 @@
         <v>強制ボス戦闘</v>
       </c>
       <c r="H83">
-        <v>20020</v>
+        <v>20030</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -4800,39 +4800,6 @@
         <v>0</v>
       </c>
       <c r="K83" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11">
-      <c r="A84">
-        <v>2012</v>
-      </c>
-      <c r="B84">
-        <v>7</v>
-      </c>
-      <c r="C84">
-        <v>7</v>
-      </c>
-      <c r="D84">
-        <v>3010</v>
-      </c>
-      <c r="F84">
-        <v>5020</v>
-      </c>
-      <c r="G84" t="str">
-        <f>INDEX(Define!E:E,MATCH(F84,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
-      </c>
-      <c r="H84">
-        <v>20030</v>
-      </c>
-      <c r="I84">
-        <v>0</v>
-      </c>
-      <c r="J84">
-        <v>0</v>
-      </c>
-      <c r="K84" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="114">
   <si>
     <t>Id</t>
   </si>
@@ -69,10 +69,13 @@
     <t>BossTroopId</t>
   </si>
   <si>
+    <t>Clouds</t>
+  </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
     <t>RockCave2</t>
-  </si>
-  <si>
-    <t>""</t>
   </si>
   <si>
     <t>Bee</t>
@@ -368,8 +371,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -394,10 +397,42 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -408,8 +443,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -419,6 +455,14 @@
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -437,9 +481,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -447,46 +490,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -500,17 +512,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -518,21 +536,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -547,19 +550,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,31 +580,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -613,13 +604,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -631,19 +694,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -655,79 +724,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -742,31 +745,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -789,41 +786,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -838,6 +817,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -846,16 +849,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -864,127 +867,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1473,10 +1476,10 @@
         <v>100</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P3">
         <v>1020</v>
@@ -1523,10 +1526,10 @@
         <v>100</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1573,10 +1576,10 @@
         <v>100</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P5">
         <v>2010</v>
@@ -1623,10 +1626,10 @@
         <v>100</v>
       </c>
       <c r="N6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" t="s">
         <v>21</v>
-      </c>
-      <c r="O6" t="s">
-        <v>20</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1673,10 +1676,10 @@
         <v>100</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1723,10 +1726,10 @@
         <v>100</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P8">
         <v>3010</v>
@@ -1773,10 +1776,10 @@
         <v>100</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1823,10 +1826,10 @@
         <v>100</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -1873,10 +1876,10 @@
         <v>100</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -1923,10 +1926,10 @@
         <v>100</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1973,10 +1976,10 @@
         <v>100</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2023,10 +2026,10 @@
         <v>100</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2073,10 +2076,10 @@
         <v>100</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2091,7 +2094,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
@@ -2103,34 +2106,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="H1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2279,14 +2282,14 @@
         <v>3010</v>
       </c>
       <c r="F6">
-        <v>6010</v>
+        <v>1010</v>
       </c>
       <c r="G6" t="str">
         <f>INDEX(Define!E:E,MATCH(F6,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>Adv再生</v>
       </c>
       <c r="H6">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2303,7 +2306,7 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>9</v>
@@ -2312,7 +2315,11 @@
         <v>3010</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>6010</v>
+      </c>
+      <c r="G7" t="str">
+        <f>INDEX(Define!E:E,MATCH(F7,Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H7">
         <v>79</v>
@@ -2335,59 +2342,55 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>3010</v>
       </c>
       <c r="F8">
-        <v>2020</v>
-      </c>
-      <c r="G8" t="str">
-        <f>INDEX(Define!E:E,MATCH(F8,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D9">
         <v>3010</v>
       </c>
       <c r="F9">
-        <v>2020</v>
+        <v>9010</v>
       </c>
       <c r="G9" t="str">
         <f>INDEX(Define!E:E,MATCH(F9,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -2395,35 +2398,35 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>3010</v>
       </c>
       <c r="F10">
-        <v>5020</v>
+        <v>2020</v>
       </c>
       <c r="G10" t="str">
         <f>INDEX(Define!E:E,MATCH(F10,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H10">
-        <v>1020</v>
+        <v>21</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2431,32 +2434,32 @@
         <v>21</v>
       </c>
       <c r="B11">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>3010</v>
       </c>
       <c r="F11">
-        <v>6010</v>
+        <v>2020</v>
       </c>
       <c r="G11" t="str">
         <f>INDEX(Define!E:E,MATCH(F11,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H11">
-        <v>213</v>
+        <v>20</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2464,19 +2467,23 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C12">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D12">
         <v>3010</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>5020</v>
+      </c>
+      <c r="G12" t="str">
+        <f>INDEX(Define!E:E,MATCH(F12,Define!D:D))</f>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H12">
-        <v>213</v>
+        <v>1020</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2493,7 +2500,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -2502,14 +2509,14 @@
         <v>3010</v>
       </c>
       <c r="F13">
-        <v>3010</v>
+        <v>1010</v>
       </c>
       <c r="G13" t="str">
         <f>INDEX(Define!E:E,MATCH(F13,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>Adv再生</v>
       </c>
       <c r="H13">
-        <v>2010</v>
+        <v>140</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2526,26 +2533,26 @@
         <v>21</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>3010</v>
       </c>
       <c r="F14">
-        <v>3020</v>
+        <v>6010</v>
       </c>
       <c r="G14" t="str">
         <f>INDEX(Define!E:E,MATCH(F14,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H14">
-        <v>1000</v>
+        <v>213</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2556,26 +2563,22 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D15">
         <v>3010</v>
       </c>
       <c r="F15">
-        <v>2010</v>
-      </c>
-      <c r="G15" t="str">
-        <f>INDEX(Define!E:E,MATCH(F15,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -2584,37 +2587,37 @@
         <v>0</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>3010</v>
       </c>
       <c r="F16">
-        <v>2020</v>
+        <v>9010</v>
       </c>
       <c r="G16" t="str">
         <f>INDEX(Define!E:E,MATCH(F16,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H16">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -2622,68 +2625,68 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B17">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C17">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>3010</v>
       </c>
       <c r="F17">
-        <v>2020</v>
+        <v>3010</v>
       </c>
       <c r="G17" t="str">
         <f>INDEX(Define!E:E,MATCH(F17,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H17">
-        <v>31</v>
+        <v>2010</v>
       </c>
       <c r="I17">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B18">
         <v>4</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D18">
         <v>3010</v>
       </c>
       <c r="F18">
-        <v>2020</v>
+        <v>3020</v>
       </c>
       <c r="G18" t="str">
         <f>INDEX(Define!E:E,MATCH(F18,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H18">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2691,29 +2694,29 @@
         <v>30</v>
       </c>
       <c r="B19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D19">
         <v>3010</v>
       </c>
       <c r="F19">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="G19" t="str">
         <f>INDEX(Define!E:E,MATCH(F19,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H19">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -2724,32 +2727,32 @@
         <v>30</v>
       </c>
       <c r="B20">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20">
         <v>3010</v>
       </c>
       <c r="F20">
-        <v>6010</v>
+        <v>2020</v>
       </c>
       <c r="G20" t="str">
         <f>INDEX(Define!E:E,MATCH(F20,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H20">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2757,28 +2760,32 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D21">
         <v>3010</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>2020</v>
+      </c>
+      <c r="G21" t="str">
+        <f>INDEX(Define!E:E,MATCH(F21,Define!D:D))</f>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H21">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2786,29 +2793,29 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>3010</v>
       </c>
       <c r="F22">
-        <v>1010</v>
+        <v>2020</v>
       </c>
       <c r="G22" t="str">
         <f>INDEX(Define!E:E,MATCH(F22,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H22">
-        <v>1030</v>
+        <v>32</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
@@ -2819,29 +2826,29 @@
         <v>30</v>
       </c>
       <c r="B23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>3010</v>
       </c>
       <c r="F23">
-        <v>9010</v>
+        <v>2020</v>
       </c>
       <c r="G23" t="str">
         <f>INDEX(Define!E:E,MATCH(F23,Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -2852,23 +2859,23 @@
         <v>30</v>
       </c>
       <c r="B24">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24">
         <v>3010</v>
       </c>
       <c r="F24">
-        <v>7010</v>
+        <v>6010</v>
       </c>
       <c r="G24" t="str">
         <f>INDEX(Define!E:E,MATCH(F24,Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H24">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -2877,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2885,23 +2892,19 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25">
         <v>3010</v>
       </c>
       <c r="F25">
-        <v>7010</v>
-      </c>
-      <c r="G25" t="str">
-        <f>INDEX(Define!E:E,MATCH(F25,Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -2910,37 +2913,37 @@
         <v>0</v>
       </c>
       <c r="K25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26">
         <v>3010</v>
       </c>
       <c r="F26">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="G26" t="str">
         <f>INDEX(Define!E:E,MATCH(F26,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>Adv再生</v>
       </c>
       <c r="H26">
-        <v>30</v>
+        <v>1030</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
@@ -2948,32 +2951,32 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27">
         <v>3010</v>
       </c>
       <c r="F27">
-        <v>2020</v>
+        <v>9010</v>
       </c>
       <c r="G27" t="str">
         <f>INDEX(Define!E:E,MATCH(F27,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H27">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -2981,26 +2984,26 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D28">
         <v>3010</v>
       </c>
       <c r="F28">
-        <v>6010</v>
+        <v>7010</v>
       </c>
       <c r="G28" t="str">
         <f>INDEX(Define!E:E,MATCH(F28,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>ダメージ床</v>
       </c>
       <c r="H28">
-        <v>1310</v>
+        <v>20</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -3009,27 +3012,31 @@
         <v>0</v>
       </c>
       <c r="K28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D29">
         <v>3010</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>7010</v>
+      </c>
+      <c r="G29" t="str">
+        <f>INDEX(Define!E:E,MATCH(F29,Define!D:D))</f>
+        <v>ダメージ床</v>
       </c>
       <c r="H29">
-        <v>1310</v>
+        <v>20</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -3038,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3049,40 +3056,40 @@
         <v>1</v>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D30">
         <v>3010</v>
       </c>
       <c r="F30">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="G30" t="str">
         <f>INDEX(Define!E:E,MATCH(F30,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H30">
-        <v>2020</v>
+        <v>30</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C31">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D31">
         <v>3010</v>
@@ -3098,10 +3105,10 @@
         <v>30</v>
       </c>
       <c r="I31">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -3109,59 +3116,55 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D32">
         <v>3010</v>
       </c>
       <c r="F32">
-        <v>2020</v>
+        <v>6010</v>
       </c>
       <c r="G32" t="str">
         <f>INDEX(Define!E:E,MATCH(F32,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H32">
-        <v>30</v>
+        <v>1310</v>
       </c>
       <c r="I32">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D33">
         <v>3010</v>
       </c>
       <c r="F33">
-        <v>5020</v>
-      </c>
-      <c r="G33" t="str">
-        <f>INDEX(Define!E:E,MATCH(F33,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>2010</v>
+        <v>1310</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -3175,13 +3178,13 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>3010</v>
@@ -3194,7 +3197,7 @@
         <v>アーティファクト取得</v>
       </c>
       <c r="H34">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -3208,29 +3211,29 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C35">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D35">
         <v>3010</v>
       </c>
       <c r="F35">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="G35" t="str">
         <f>INDEX(Define!E:E,MATCH(F35,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -3241,13 +3244,13 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B36">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D36">
         <v>3010</v>
@@ -3260,13 +3263,13 @@
         <v>ダンジョン移動</v>
       </c>
       <c r="H36">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I36">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J36">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -3274,26 +3277,26 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B37">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D37">
         <v>3010</v>
       </c>
       <c r="F37">
-        <v>6010</v>
+        <v>5020</v>
       </c>
       <c r="G37" t="str">
         <f>INDEX(Define!E:E,MATCH(F37,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H37">
-        <v>45</v>
+        <v>2010</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -3307,22 +3310,26 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B38">
         <v>4</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D38">
         <v>3010</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>3010</v>
+      </c>
+      <c r="G38" t="str">
+        <f>INDEX(Define!E:E,MATCH(F38,Define!D:D))</f>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H38">
-        <v>45</v>
+        <v>2030</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -3336,32 +3343,32 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D39">
         <v>3010</v>
       </c>
       <c r="F39">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="G39" t="str">
         <f>INDEX(Define!E:E,MATCH(F39,Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>ダンジョンから出る</v>
       </c>
       <c r="H39">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -3369,13 +3376,13 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D40">
         <v>3010</v>
@@ -3388,10 +3395,10 @@
         <v>ダンジョン移動</v>
       </c>
       <c r="H40">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I40">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J40">
         <v>18</v>
@@ -3402,26 +3409,26 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C41">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D41">
         <v>3010</v>
       </c>
       <c r="F41">
-        <v>3010</v>
+        <v>6010</v>
       </c>
       <c r="G41" t="str">
         <f>INDEX(Define!E:E,MATCH(F41,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H41">
-        <v>2130</v>
+        <v>45</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -3435,26 +3442,22 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D42">
         <v>3010</v>
       </c>
       <c r="F42">
-        <v>3020</v>
-      </c>
-      <c r="G42" t="str">
-        <f>INDEX(Define!E:E,MATCH(F42,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>11010</v>
+        <v>45</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -3471,32 +3474,32 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D43">
         <v>3010</v>
       </c>
       <c r="F43">
-        <v>3020</v>
+        <v>2020</v>
       </c>
       <c r="G43" t="str">
         <f>INDEX(Define!E:E,MATCH(F43,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H43">
-        <v>11010</v>
+        <v>40</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -3504,32 +3507,32 @@
         <v>41</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D44">
         <v>3010</v>
       </c>
       <c r="F44">
-        <v>3020</v>
+        <v>2020</v>
       </c>
       <c r="G44" t="str">
         <f>INDEX(Define!E:E,MATCH(F44,Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H44">
-        <v>11010</v>
+        <v>42</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -3537,23 +3540,23 @@
         <v>41</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D45">
         <v>3010</v>
       </c>
       <c r="F45">
-        <v>1010</v>
+        <v>3010</v>
       </c>
       <c r="G45" t="str">
         <f>INDEX(Define!E:E,MATCH(F45,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H45">
-        <v>1040</v>
+        <v>2130</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -3570,23 +3573,23 @@
         <v>41</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D46">
         <v>3010</v>
       </c>
       <c r="F46">
-        <v>1010</v>
+        <v>3020</v>
       </c>
       <c r="G46" t="str">
         <f>INDEX(Define!E:E,MATCH(F46,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H46">
-        <v>100</v>
+        <v>11010</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -3606,20 +3609,20 @@
         <v>4</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D47">
         <v>3010</v>
       </c>
       <c r="F47">
-        <v>5010</v>
+        <v>3020</v>
       </c>
       <c r="G47" t="str">
         <f>INDEX(Define!E:E,MATCH(F47,Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H47">
-        <v>3020</v>
+        <v>11010</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -3636,23 +3639,23 @@
         <v>41</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D48">
         <v>3010</v>
       </c>
       <c r="F48">
-        <v>6010</v>
+        <v>3020</v>
       </c>
       <c r="G48" t="str">
         <f>INDEX(Define!E:E,MATCH(F48,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H48">
-        <v>43</v>
+        <v>11010</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -3672,16 +3675,20 @@
         <v>4</v>
       </c>
       <c r="C49">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D49">
         <v>3010</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>1010</v>
+      </c>
+      <c r="G49" t="str">
+        <f>INDEX(Define!E:E,MATCH(F49,Define!D:D))</f>
+        <v>Adv再生</v>
       </c>
       <c r="H49">
-        <v>43</v>
+        <v>1040</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -3701,20 +3708,20 @@
         <v>4</v>
       </c>
       <c r="C50">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D50">
         <v>3010</v>
       </c>
       <c r="F50">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="G50" t="str">
         <f>INDEX(Define!E:E,MATCH(F50,Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>Adv再生</v>
       </c>
       <c r="H50">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -3723,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -3731,23 +3738,23 @@
         <v>41</v>
       </c>
       <c r="B51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C51">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D51">
         <v>3010</v>
       </c>
       <c r="F51">
-        <v>7010</v>
+        <v>5010</v>
       </c>
       <c r="G51" t="str">
         <f>INDEX(Define!E:E,MATCH(F51,Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H51">
-        <v>20</v>
+        <v>3020</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -3756,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -3764,23 +3771,23 @@
         <v>41</v>
       </c>
       <c r="B52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C52">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D52">
         <v>3010</v>
       </c>
       <c r="F52">
-        <v>7010</v>
+        <v>6010</v>
       </c>
       <c r="G52" t="str">
         <f>INDEX(Define!E:E,MATCH(F52,Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H52">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -3789,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -3797,23 +3804,19 @@
         <v>41</v>
       </c>
       <c r="B53">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C53">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D53">
         <v>3010</v>
       </c>
       <c r="F53">
-        <v>6011</v>
-      </c>
-      <c r="G53" t="str">
-        <f>INDEX(Define!E:E,MATCH(F53,Define!D:D))</f>
-        <v>指定のイベントマスを表示する</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>713</v>
+        <v>43</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -3830,7 +3833,7 @@
         <v>41</v>
       </c>
       <c r="B54">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C54">
         <v>13</v>
@@ -3839,10 +3842,14 @@
         <v>3010</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>7010</v>
+      </c>
+      <c r="G54" t="str">
+        <f>INDEX(Define!E:E,MATCH(F54,Define!D:D))</f>
+        <v>ダメージ床</v>
       </c>
       <c r="H54">
-        <v>713</v>
+        <v>20</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -3851,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -3859,7 +3866,7 @@
         <v>41</v>
       </c>
       <c r="B55">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C55">
         <v>13</v>
@@ -3868,14 +3875,14 @@
         <v>3010</v>
       </c>
       <c r="F55">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="G55" t="str">
         <f>INDEX(Define!E:E,MATCH(F55,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>ダメージ床</v>
       </c>
       <c r="H55">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -3884,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -3892,7 +3899,7 @@
         <v>41</v>
       </c>
       <c r="B56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56">
         <v>13</v>
@@ -3901,14 +3908,14 @@
         <v>3010</v>
       </c>
       <c r="F56">
-        <v>7020</v>
+        <v>7010</v>
       </c>
       <c r="G56" t="str">
         <f>INDEX(Define!E:E,MATCH(F56,Define!D:D))</f>
-        <v>怨嗟床</v>
+        <v>ダメージ床</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -3917,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -3934,14 +3941,14 @@
         <v>3010</v>
       </c>
       <c r="F57">
-        <v>1010</v>
+        <v>6011</v>
       </c>
       <c r="G57" t="str">
         <f>INDEX(Define!E:E,MATCH(F57,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>指定のイベントマスを表示する</v>
       </c>
       <c r="H57">
-        <v>120</v>
+        <v>713</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -3958,7 +3965,7 @@
         <v>41</v>
       </c>
       <c r="B58">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C58">
         <v>13</v>
@@ -3967,14 +3974,10 @@
         <v>3010</v>
       </c>
       <c r="F58">
-        <v>9010</v>
-      </c>
-      <c r="G58" t="str">
-        <f>INDEX(Define!E:E,MATCH(F58,Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>0</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>713</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -3991,7 +3994,7 @@
         <v>41</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C59">
         <v>13</v>
@@ -4007,7 +4010,7 @@
         <v>Adv再生</v>
       </c>
       <c r="H59">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -4024,7 +4027,7 @@
         <v>41</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C60">
         <v>13</v>
@@ -4033,11 +4036,11 @@
         <v>3010</v>
       </c>
       <c r="F60">
-        <v>7021</v>
+        <v>7020</v>
       </c>
       <c r="G60" t="str">
         <f>INDEX(Define!E:E,MATCH(F60,Define!D:D))</f>
-        <v>怨嗟床解除</v>
+        <v>怨嗟床</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -4057,7 +4060,7 @@
         <v>41</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C61">
         <v>13</v>
@@ -4066,14 +4069,14 @@
         <v>3010</v>
       </c>
       <c r="F61">
-        <v>6010</v>
+        <v>1010</v>
       </c>
       <c r="G61" t="str">
         <f>INDEX(Define!E:E,MATCH(F61,Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>Adv再生</v>
       </c>
       <c r="H61">
-        <v>813</v>
+        <v>120</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -4090,7 +4093,7 @@
         <v>41</v>
       </c>
       <c r="B62">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C62">
         <v>13</v>
@@ -4099,10 +4102,14 @@
         <v>3010</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>9010</v>
+      </c>
+      <c r="G62" t="str">
+        <f>INDEX(Define!E:E,MATCH(F62,Define!D:D))</f>
+        <v>イベント終了明示</v>
       </c>
       <c r="H62">
-        <v>813</v>
+        <v>0</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -4116,26 +4123,26 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D63">
         <v>3010</v>
       </c>
       <c r="F63">
-        <v>3010</v>
+        <v>1010</v>
       </c>
       <c r="G63" t="str">
         <f>INDEX(Define!E:E,MATCH(F63,Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>Adv再生</v>
       </c>
       <c r="H63">
-        <v>2020</v>
+        <v>130</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -4149,26 +4156,26 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B64">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D64">
         <v>3010</v>
       </c>
       <c r="F64">
-        <v>5020</v>
+        <v>7021</v>
       </c>
       <c r="G64" t="str">
         <f>INDEX(Define!E:E,MATCH(F64,Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>怨嗟床解除</v>
       </c>
       <c r="H64">
-        <v>3010</v>
+        <v>0</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -4182,26 +4189,26 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D65">
         <v>3010</v>
       </c>
       <c r="F65">
-        <v>1010</v>
+        <v>6010</v>
       </c>
       <c r="G65" t="str">
         <f>INDEX(Define!E:E,MATCH(F65,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H65">
-        <v>100</v>
+        <v>813</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -4215,26 +4222,22 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B66">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C66">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D66">
         <v>3010</v>
       </c>
       <c r="F66">
-        <v>5010</v>
-      </c>
-      <c r="G66" t="str">
-        <f>INDEX(Define!E:E,MATCH(F66,Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>0</v>
       </c>
       <c r="H66">
-        <v>3030</v>
+        <v>813</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -4251,23 +4254,23 @@
         <v>42</v>
       </c>
       <c r="B67">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C67">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D67">
         <v>3010</v>
       </c>
       <c r="F67">
-        <v>1010</v>
+        <v>3010</v>
       </c>
       <c r="G67" t="str">
         <f>INDEX(Define!E:E,MATCH(F67,Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H67">
-        <v>100</v>
+        <v>2020</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -4284,7 +4287,7 @@
         <v>42</v>
       </c>
       <c r="B68">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C68">
         <v>8</v>
@@ -4293,14 +4296,14 @@
         <v>3010</v>
       </c>
       <c r="F68">
-        <v>5010</v>
+        <v>5020</v>
       </c>
       <c r="G68" t="str">
         <f>INDEX(Define!E:E,MATCH(F68,Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H68">
-        <v>3040</v>
+        <v>3010</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -4317,10 +4320,10 @@
         <v>42</v>
       </c>
       <c r="B69">
+        <v>4</v>
+      </c>
+      <c r="C69">
         <v>8</v>
-      </c>
-      <c r="C69">
-        <v>10</v>
       </c>
       <c r="D69">
         <v>3010</v>
@@ -4333,7 +4336,7 @@
         <v>Adv再生</v>
       </c>
       <c r="H69">
-        <v>1030</v>
+        <v>100</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -4350,23 +4353,23 @@
         <v>42</v>
       </c>
       <c r="B70">
+        <v>4</v>
+      </c>
+      <c r="C70">
         <v>8</v>
       </c>
-      <c r="C70">
-        <v>10</v>
-      </c>
       <c r="D70">
         <v>3010</v>
       </c>
       <c r="F70">
-        <v>6020</v>
+        <v>5010</v>
       </c>
       <c r="G70" t="str">
         <f>INDEX(Define!E:E,MATCH(F70,Define!D:D))</f>
-        <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H70">
-        <v>89</v>
+        <v>3030</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -4383,19 +4386,23 @@
         <v>42</v>
       </c>
       <c r="B71">
+        <v>12</v>
+      </c>
+      <c r="C71">
         <v>8</v>
       </c>
-      <c r="C71">
-        <v>9</v>
-      </c>
       <c r="D71">
         <v>3010</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>1010</v>
+      </c>
+      <c r="G71" t="str">
+        <f>INDEX(Define!E:E,MATCH(F71,Define!D:D))</f>
+        <v>Adv再生</v>
       </c>
       <c r="H71">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -4409,26 +4416,26 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72">
-        <v>1010</v>
+        <v>42</v>
       </c>
       <c r="B72">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C72">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D72">
         <v>3010</v>
       </c>
       <c r="F72">
-        <v>2010</v>
+        <v>5010</v>
       </c>
       <c r="G72" t="str">
         <f>INDEX(Define!E:E,MATCH(F72,Define!D:D))</f>
-        <v>ダンジョンから出る</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>3040</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -4437,31 +4444,31 @@
         <v>0</v>
       </c>
       <c r="K72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73">
+        <v>42</v>
+      </c>
+      <c r="B73">
+        <v>8</v>
+      </c>
+      <c r="C73">
+        <v>10</v>
+      </c>
+      <c r="D73">
+        <v>3010</v>
+      </c>
+      <c r="F73">
         <v>1010</v>
-      </c>
-      <c r="B73">
-        <v>10</v>
-      </c>
-      <c r="C73">
-        <v>4</v>
-      </c>
-      <c r="D73">
-        <v>3010</v>
-      </c>
-      <c r="F73">
-        <v>3030</v>
       </c>
       <c r="G73" t="str">
         <f>INDEX(Define!E:E,MATCH(F73,Define!D:D))</f>
-        <v>魔法入手</v>
+        <v>Adv再生</v>
       </c>
       <c r="H73">
-        <v>30010</v>
+        <v>1030</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -4475,26 +4482,26 @@
     </row>
     <row r="74" span